--- a/Tabulado normas.xlsx
+++ b/Tabulado normas.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5A6CD5F1A234089A/Minmuj/Proy 005/Informatico/Pro aplicativo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\git_porjects\chatbot_normatividad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="989" documentId="8_{724CF714-55DC-4B7F-A79B-ADEA6B25935B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A0A8446-2C2A-49E6-9F21-E6A2280CC05A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AD87B9-8AA1-4049-BA6E-7D9031D8F059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="2535" windowWidth="14325" windowHeight="12855" xr2:uid="{A43CB7C4-613E-4394-9B0D-B8228CDDEEE6}"/>
+    <workbookView xWindow="12405" yWindow="165" windowWidth="15990" windowHeight="15315" xr2:uid="{A43CB7C4-613E-4394-9B0D-B8228CDDEEE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$I$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$I$178</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="621">
   <si>
     <t>Tema_CD</t>
   </si>
@@ -1873,6 +1873,39 @@
   </si>
   <si>
     <t>2002</t>
+  </si>
+  <si>
+    <t>https://spij.minjus.gob.pe/spij-ext-web/#/detallenorma/H1141065</t>
+  </si>
+  <si>
+    <t>Cambio a enlace directo (10-07)</t>
+  </si>
+  <si>
+    <t>4.02.01a</t>
+  </si>
+  <si>
+    <t>Evolución de la Ley N° 30364</t>
+  </si>
+  <si>
+    <t>https://www.gob.pe/74938-ley-n-30364-ley-para-prevenir-sancionar-y-erradicar-la-violencia-contra-las-mujeres-y-los-integrantes-del-grupo-familiar-evolucion-de-la-ley-n-30364</t>
+  </si>
+  <si>
+    <t>Contenido complementario adicional</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4.02.01b</t>
+  </si>
+  <si>
+    <t>Reglamento de la Ley N° 30364</t>
+  </si>
+  <si>
+    <t>4.02.01c</t>
+  </si>
+  <si>
+    <t>Datos generales de la Ley N° 30364</t>
   </si>
 </sst>
 </file>
@@ -2269,13 +2302,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{472FEE68-DD5E-4E49-A00A-14C0B59108D6}" name="Tabla1" displayName="Tabla1" ref="A1:J175" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J175" xr:uid="{9BA9B8BD-E9E1-4E15-8E96-D0397AE788CA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{472FEE68-DD5E-4E49-A00A-14C0B59108D6}" name="Tabla1" displayName="Tabla1" ref="A1:J178" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J178" xr:uid="{9BA9B8BD-E9E1-4E15-8E96-D0397AE788CA}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{7FE3D79C-8508-4D30-B806-8EFEABD24EF2}" name="Tema_CD" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{FBCC26B3-3774-4B76-9703-EE3DBD44E0E8}" name="Tema" dataDxfId="8"/>
@@ -2609,14 +2638,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA9B8BD-E9E1-4E15-8E96-D0397AE788CA}">
-  <dimension ref="A1:J176"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
     <col min="3" max="3" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="50.83203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="50.83203125" customWidth="1"/>
     <col min="7" max="7" width="20.83203125" customWidth="1"/>
     <col min="8" max="8" width="40.83203125" customWidth="1"/>
@@ -5804,7 +5833,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>4</v>
       </c>
@@ -5824,19 +5853,21 @@
         <v>345</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="I107" s="8"/>
+        <v>610</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>611</v>
+      </c>
       <c r="J107" s="9" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A108" s="3">
-        <v>4</v>
+    <row r="108" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A108" s="3" t="s">
+        <v>616</v>
       </c>
       <c r="B108" s="4" t="s">
         <v>341</v>
@@ -5848,80 +5879,86 @@
         <v>343</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>347</v>
+        <v>612</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>348</v>
+        <v>620</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>14</v>
+        <v>590</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="I108" s="8"/>
+        <v>346</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>615</v>
+      </c>
       <c r="J108" s="9" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A109" s="3">
-        <v>4</v>
+      <c r="A109" s="3" t="s">
+        <v>616</v>
       </c>
       <c r="B109" s="4" t="s">
         <v>341</v>
       </c>
       <c r="C109" s="5">
-        <v>4.03</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>351</v>
+        <v>617</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>352</v>
+        <v>613</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>43</v>
+        <v>590</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="I109" s="8"/>
+        <v>614</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>615</v>
+      </c>
       <c r="J109" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A110" s="3">
-        <v>4</v>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>616</v>
       </c>
       <c r="B110" s="4" t="s">
         <v>341</v>
       </c>
       <c r="C110" s="5">
-        <v>4.03</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>354</v>
+        <v>619</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>355</v>
+        <v>618</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>43</v>
+        <v>590</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="I110" s="8"/>
+        <v>353</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>615</v>
+      </c>
       <c r="J110" s="9" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -5932,29 +5969,29 @@
         <v>341</v>
       </c>
       <c r="C111" s="5">
-        <v>4.03</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>4</v>
       </c>
@@ -5968,113 +6005,113 @@
         <v>350</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="9" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C113" s="5">
-        <v>5.01</v>
+        <v>4.03</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="9" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C114" s="5">
-        <v>5.01</v>
+        <v>4.03</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
       <c r="G114" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C115" s="5">
-        <v>5.0199999999999996</v>
+        <v>4.03</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="I115" s="8"/>
       <c r="J115" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>5</v>
       </c>
@@ -6082,29 +6119,29 @@
         <v>363</v>
       </c>
       <c r="C116" s="5">
-        <v>5.0199999999999996</v>
+        <v>5.01</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="I116" s="8"/>
       <c r="J116" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>5</v>
       </c>
@@ -6112,29 +6149,29 @@
         <v>363</v>
       </c>
       <c r="C117" s="5">
-        <v>5.0199999999999996</v>
+        <v>5.01</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="I117" s="8"/>
       <c r="J117" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>5</v>
       </c>
@@ -6142,29 +6179,29 @@
         <v>363</v>
       </c>
       <c r="C118" s="5">
-        <v>5.03</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H118" s="7" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="I118" s="8"/>
       <c r="J118" s="9" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>5</v>
       </c>
@@ -6172,29 +6209,29 @@
         <v>363</v>
       </c>
       <c r="C119" s="5">
-        <v>5.03</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="9" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="72" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>5</v>
       </c>
@@ -6202,29 +6239,29 @@
         <v>363</v>
       </c>
       <c r="C120" s="5">
-        <v>5.03</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>5</v>
       </c>
@@ -6238,23 +6275,23 @@
         <v>381</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="9" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>5</v>
       </c>
@@ -6268,20 +6305,20 @@
         <v>381</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="G122" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H122" s="7" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="I122" s="8"/>
       <c r="J122" s="9" t="s">
-        <v>504</v>
+        <v>520</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6298,20 +6335,20 @@
         <v>381</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="G123" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="I123" s="8"/>
       <c r="J123" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -6328,23 +6365,23 @@
         <v>381</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="I124" s="8"/>
       <c r="J124" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" ht="72" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>5</v>
       </c>
@@ -6358,76 +6395,76 @@
         <v>381</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="I125" s="8"/>
       <c r="J125" s="9" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="C126" s="5">
-        <v>6.01</v>
+        <v>5.03</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="F126" s="8" t="s">
-        <v>373</v>
+        <v>398</v>
       </c>
       <c r="G126" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="I126" s="8"/>
       <c r="J126" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" ht="72" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="C127" s="5">
-        <v>6.01</v>
+        <v>5.03</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="I127" s="8"/>
       <c r="J127" s="9" t="s">
@@ -6436,30 +6473,32 @@
     </row>
     <row r="128" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="C128" s="5">
-        <v>6.02</v>
+        <v>5.03</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>595</v>
+        <v>403</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>594</v>
+        <v>404</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H128" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>405</v>
+      </c>
       <c r="I128" s="8"/>
       <c r="J128" s="9" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6470,26 +6509,26 @@
         <v>406</v>
       </c>
       <c r="C129" s="5">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>413</v>
+        <v>373</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>414</v>
+        <v>374</v>
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="9" t="s">
-        <v>609</v>
+        <v>508</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6500,29 +6539,29 @@
         <v>406</v>
       </c>
       <c r="C130" s="5">
-        <v>6.03</v>
+        <v>6.01</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="I130" s="8"/>
       <c r="J130" s="9" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>6</v>
       </c>
@@ -6530,117 +6569,117 @@
         <v>406</v>
       </c>
       <c r="C131" s="5">
-        <v>6.04</v>
+        <v>6.02</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>419</v>
+        <v>595</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>420</v>
+        <v>594</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H131" s="7" t="s">
-        <v>421</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="H131" s="7"/>
       <c r="I131" s="8"/>
       <c r="J131" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C132" s="5">
-        <v>7.01</v>
+        <v>6.03</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>596</v>
+        <v>411</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>412</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>555</v>
+        <v>413</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H132" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>414</v>
+      </c>
       <c r="I132" s="8"/>
       <c r="J132" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C133" s="5">
-        <v>7.02</v>
+        <v>6.03</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>425</v>
+        <v>411</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>415</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H133" s="7" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="I133" s="8"/>
       <c r="J133" s="9" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C134" s="5">
-        <v>7.02</v>
+        <v>6.04</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>428</v>
+        <v>418</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>419</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="I134" s="8"/>
       <c r="J134" s="9" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>7</v>
       </c>
@@ -6648,29 +6687,27 @@
         <v>422</v>
       </c>
       <c r="C135" s="5">
-        <v>7.02</v>
+        <v>7.01</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>431</v>
+        <v>596</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>432</v>
+        <v>555</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H135" s="7" t="s">
-        <v>433</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="H135" s="7"/>
       <c r="I135" s="8"/>
       <c r="J135" s="9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>7</v>
       </c>
@@ -6684,23 +6721,23 @@
         <v>424</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="G136" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="I136" s="8"/>
       <c r="J136" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>7</v>
       </c>
@@ -6714,23 +6751,23 @@
         <v>424</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="I137" s="8"/>
       <c r="J137" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="72" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>7</v>
       </c>
@@ -6744,23 +6781,23 @@
         <v>424</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="7" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="I138" s="8"/>
       <c r="J138" s="9" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>7</v>
       </c>
@@ -6768,29 +6805,29 @@
         <v>422</v>
       </c>
       <c r="C139" s="5">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H139" s="7" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="I139" s="8"/>
       <c r="J139" s="9" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>7</v>
       </c>
@@ -6798,29 +6835,29 @@
         <v>422</v>
       </c>
       <c r="C140" s="5">
-        <v>7.03</v>
+        <v>7.02</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H140" s="7" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="I140" s="8"/>
       <c r="J140" s="9" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>7</v>
       </c>
@@ -6828,29 +6865,29 @@
         <v>422</v>
       </c>
       <c r="C141" s="5">
-        <v>7.04</v>
+        <v>7.02</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="I141" s="8"/>
       <c r="J141" s="9" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>7</v>
       </c>
@@ -6858,29 +6895,29 @@
         <v>422</v>
       </c>
       <c r="C142" s="5">
-        <v>7.05</v>
+        <v>7.03</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="G142" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>7</v>
       </c>
@@ -6888,29 +6925,29 @@
         <v>422</v>
       </c>
       <c r="C143" s="5">
-        <v>7.05</v>
+        <v>7.03</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>535</v>
+        <v>447</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="I143" s="8"/>
       <c r="J143" s="9" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="84" x14ac:dyDescent="0.2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>7</v>
       </c>
@@ -6918,29 +6955,29 @@
         <v>422</v>
       </c>
       <c r="C144" s="5">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>536</v>
+        <v>451</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H144" s="7" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I144" s="8"/>
       <c r="J144" s="9" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>7</v>
       </c>
@@ -6948,26 +6985,26 @@
         <v>422</v>
       </c>
       <c r="C145" s="5">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>537</v>
+        <v>455</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="I145" s="8"/>
       <c r="J145" s="9" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6978,31 +7015,29 @@
         <v>422</v>
       </c>
       <c r="C146" s="5">
-        <v>7.07</v>
+        <v>7.05</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="G146" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="I146" s="8" t="s">
-        <v>599</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="I146" s="8"/>
       <c r="J146" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="84" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>7</v>
       </c>
@@ -7010,29 +7045,29 @@
         <v>422</v>
       </c>
       <c r="C147" s="5">
-        <v>7.07</v>
+        <v>7.05</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="G147" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="9" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>7</v>
       </c>
@@ -7040,29 +7075,29 @@
         <v>422</v>
       </c>
       <c r="C148" s="5">
-        <v>7.08</v>
+        <v>7.06</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="9" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>7</v>
       </c>
@@ -7070,29 +7105,31 @@
         <v>422</v>
       </c>
       <c r="C149" s="5">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="G149" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="I149" s="8"/>
+        <v>467</v>
+      </c>
+      <c r="I149" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="J149" s="9" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>7</v>
       </c>
@@ -7100,29 +7137,29 @@
         <v>422</v>
       </c>
       <c r="C150" s="5">
-        <v>7.08</v>
+        <v>7.07</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="I150" s="8"/>
       <c r="J150" s="9" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>7</v>
       </c>
@@ -7136,23 +7173,23 @@
         <v>470</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G151" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>7</v>
       </c>
@@ -7166,23 +7203,23 @@
         <v>470</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="I152" s="8"/>
       <c r="J152" s="9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>7</v>
       </c>
@@ -7196,23 +7233,23 @@
         <v>470</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="G153" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="I153" s="8"/>
       <c r="J153" s="9" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>7</v>
       </c>
@@ -7226,23 +7263,23 @@
         <v>470</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="9" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>7</v>
       </c>
@@ -7250,26 +7287,26 @@
         <v>422</v>
       </c>
       <c r="C155" s="5">
-        <v>7.09</v>
+        <v>7.08</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="I155" s="8"/>
       <c r="J155" s="9" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7279,86 +7316,90 @@
       <c r="B156" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C156" s="5" t="s">
-        <v>488</v>
+      <c r="C156" s="5">
+        <v>7.08</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>597</v>
+        <v>545</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>555</v>
+        <v>481</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H156" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>482</v>
+      </c>
       <c r="I156" s="8"/>
       <c r="J156" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>7</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C157" s="5" t="s">
-        <v>530</v>
+      <c r="C157" s="5">
+        <v>7.08</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>598</v>
+        <v>546</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>555</v>
+        <v>483</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H157" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>484</v>
+      </c>
       <c r="I157" s="8"/>
       <c r="J157" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="24" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>7</v>
       </c>
       <c r="B158" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="C158" s="5" t="s">
-        <v>531</v>
+      <c r="C158" s="5">
+        <v>7.09</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>532</v>
+        <v>486</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H158" s="7" t="s">
-        <v>548</v>
+        <v>487</v>
       </c>
       <c r="I158" s="8"/>
       <c r="J158" s="9" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="159" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>7</v>
       </c>
@@ -7366,29 +7407,27 @@
         <v>422</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>552</v>
+        <v>597</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>533</v>
+        <v>555</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H159" s="7" t="s">
-        <v>549</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="H159" s="7"/>
       <c r="I159" s="8"/>
       <c r="J159" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="160" spans="1:10" ht="108" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>7</v>
       </c>
@@ -7396,26 +7435,24 @@
         <v>422</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>553</v>
+        <v>598</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H160" s="7" t="s">
-        <v>550</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="H160" s="7"/>
       <c r="I160" s="8"/>
       <c r="J160" s="9" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7426,25 +7463,29 @@
         <v>422</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="E161" s="6"/>
+        <v>491</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>551</v>
+      </c>
       <c r="F161" s="8" t="s">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="G161" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H161" s="7"/>
+        <v>14</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>548</v>
+      </c>
       <c r="I161" s="8"/>
       <c r="J161" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="162" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>7</v>
       </c>
@@ -7452,29 +7493,29 @@
         <v>422</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>556</v>
+        <v>533</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="I162" s="8"/>
       <c r="J162" s="9" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="163" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" ht="108" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>7</v>
       </c>
@@ -7482,26 +7523,26 @@
         <v>422</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>581</v>
+        <v>531</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>557</v>
+        <v>534</v>
       </c>
       <c r="G163" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="I163" s="8"/>
       <c r="J163" s="9" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7512,14 +7553,12 @@
         <v>422</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>582</v>
+        <v>554</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>564</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="E164" s="6"/>
       <c r="F164" s="8" t="s">
         <v>555</v>
       </c>
@@ -7540,29 +7579,29 @@
         <v>422</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="G165" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="H165" s="7" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="I165" s="8"/>
       <c r="J165" s="9" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>7</v>
       </c>
@@ -7570,24 +7609,26 @@
         <v>422</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H166" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>561</v>
+      </c>
       <c r="I166" s="8"/>
       <c r="J166" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7598,13 +7639,13 @@
         <v>422</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="F167" s="8" t="s">
         <v>555</v>
@@ -7618,7 +7659,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>7</v>
       </c>
@@ -7626,26 +7667,26 @@
         <v>422</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="H168" s="7" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="I168" s="8"/>
       <c r="J168" s="9" t="s">
-        <v>601</v>
+        <v>518</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7656,13 +7697,13 @@
         <v>422</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="F169" s="8" t="s">
         <v>555</v>
@@ -7684,13 +7725,13 @@
         <v>422</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="F170" s="8" t="s">
         <v>555</v>
@@ -7704,7 +7745,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>7</v>
       </c>
@@ -7712,27 +7753,29 @@
         <v>422</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H171" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>571</v>
+      </c>
       <c r="I171" s="8"/>
       <c r="J171" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="172" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>7</v>
       </c>
@@ -7740,29 +7783,27 @@
         <v>422</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>464</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="H172" s="7"/>
       <c r="I172" s="8"/>
       <c r="J172" s="9" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="173" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>7</v>
       </c>
@@ -7770,16 +7811,16 @@
         <v>422</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="G173" s="6" t="s">
         <v>590</v>
@@ -7787,10 +7828,10 @@
       <c r="H173" s="7"/>
       <c r="I173" s="8"/>
       <c r="J173" s="9" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="174" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>7</v>
       </c>
@@ -7798,16 +7839,16 @@
         <v>422</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="G174" s="6" t="s">
         <v>590</v>
@@ -7815,10 +7856,10 @@
       <c r="H174" s="7"/>
       <c r="I174" s="8"/>
       <c r="J174" s="9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="175" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" ht="96" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>7</v>
       </c>
@@ -7826,29 +7867,115 @@
         <v>422</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="G175" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="H175" s="7"/>
+        <v>43</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>464</v>
+      </c>
       <c r="I175" s="8"/>
       <c r="J175" s="9" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+      <c r="A176" s="3">
+        <v>7</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="G176" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="H176" s="7"/>
+      <c r="I176" s="8"/>
+      <c r="J176" s="9" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+      <c r="A177" s="3">
+        <v>7</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="G177" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="H177" s="7"/>
+      <c r="I177" s="8"/>
+      <c r="J177" s="9" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+      <c r="A178" s="3">
+        <v>7</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="H178" s="7"/>
+      <c r="I178" s="8"/>
+      <c r="J178" s="9" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A179" s="1"/>
+      <c r="B179" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -7956,14 +8083,18 @@
     <hyperlink ref="H102" r:id="rId101" xr:uid="{5617433B-0321-4203-8D4E-EAD2EEEB1C77}"/>
     <hyperlink ref="H103" r:id="rId102" xr:uid="{AA0FAE12-D064-42BA-9572-F9CF50C33FCE}"/>
     <hyperlink ref="H104" r:id="rId103" xr:uid="{DAACD957-CFE6-444C-8A56-466141B26B96}"/>
-    <hyperlink ref="H158" r:id="rId104" location="/detallenorma/H1088463" xr:uid="{8EBF9CA3-DB23-40BD-A593-EBC1B8117F8E}"/>
-    <hyperlink ref="H159" r:id="rId105" xr:uid="{7C08EDB5-E571-4CAD-8243-550C11757BE2}"/>
-    <hyperlink ref="H160" r:id="rId106" xr:uid="{EB567D07-C77F-4A93-A42D-6F9252276305}"/>
+    <hyperlink ref="H161" r:id="rId104" location="/detallenorma/H1088463" xr:uid="{8EBF9CA3-DB23-40BD-A593-EBC1B8117F8E}"/>
+    <hyperlink ref="H162" r:id="rId105" xr:uid="{7C08EDB5-E571-4CAD-8243-550C11757BE2}"/>
+    <hyperlink ref="H163" r:id="rId106" xr:uid="{EB567D07-C77F-4A93-A42D-6F9252276305}"/>
+    <hyperlink ref="H107" r:id="rId107" location="/detallenorma/H1141065" xr:uid="{B0CB6F18-72F1-48BC-8D36-A46C5B119F25}"/>
+    <hyperlink ref="H109" r:id="rId108" xr:uid="{10D3EFA4-77EE-48A4-95DE-F3D6EA72E545}"/>
+    <hyperlink ref="H110" r:id="rId109" xr:uid="{DC07E4B2-9492-45BD-9C16-4D869CD05636}"/>
+    <hyperlink ref="H108" r:id="rId110" xr:uid="{09297BBE-789F-4040-A27A-CDBD6E16A9FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId107"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId111"/>
   <tableParts count="1">
-    <tablePart r:id="rId108"/>
+    <tablePart r:id="rId112"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Tabulado normas.xlsx
+++ b/Tabulado normas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\git_porjects\chatbot_normatividad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00AD87B9-8AA1-4049-BA6E-7D9031D8F059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EF7A8F-0F71-4CA2-8DE4-AC53ABC8D179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12405" yWindow="165" windowWidth="15990" windowHeight="15315" xr2:uid="{A43CB7C4-613E-4394-9B0D-B8228CDDEEE6}"/>
+    <workbookView xWindow="285" yWindow="30" windowWidth="15990" windowHeight="15315" xr2:uid="{A43CB7C4-613E-4394-9B0D-B8228CDDEEE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="620">
   <si>
     <t>Tema_CD</t>
   </si>
@@ -203,9 +203,6 @@
     <t>Declaración y la Plataforma de Acción de Beijing</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/sites/default/files/Headquarters/Attachments/Sections/CSW/BPA_S_Final_WEB.pdf</t>
-  </si>
-  <si>
     <t>Principios</t>
   </si>
   <si>
@@ -218,9 +215,6 @@
     <t>PDF anidado</t>
   </si>
   <si>
-    <t>https://www.refworld.org/es/leg/resol/cij/2007/es/58135</t>
-  </si>
-  <si>
     <t>Resoluciones aprobadas por la Asamblea General de las Naciones Unidas</t>
   </si>
   <si>
@@ -239,72 +233,48 @@
     <t>Resolución N° 77/193 (2024). Intensificación de los esfuerzos para eliminar todas las formas de violencia contra las mujeres y las niñas: Violencia contra las mujeres y las niñas facilitada por la tecnología</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2024/10/intensificacion-de-los-esfuerzos-para-eliminar-todas-las-formas-de-violencia-contra-las-mujeres-y-las-ninas-informe-del-secretario-general-2024</t>
-  </si>
-  <si>
     <t>1.03.03</t>
   </si>
   <si>
     <t>Resolución N° 77/194 (2024). Trata de mujeres y niñas: Fortalecimiento del acceso a la justicia de las víctimas supervivientes</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2024/10/trafficking-in-women-and-girls-report-of-the-secretary-general-2024</t>
-  </si>
-  <si>
     <t>1.03.04</t>
   </si>
   <si>
     <t>Resolución N° 75/161 (2022). Intensificación de los esfuerzos para eliminar todas las formas de violencia contra las mujeres y las niñas</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2022/10/intensificacion-de-los-esfuerzos-para-eliminar-todas-las-formas-de-violencia-contra-las-mujeres-y-las-ninas-informe-del-secretario-general-2022</t>
-  </si>
-  <si>
     <t>1.03.05</t>
   </si>
   <si>
     <t>Resolución N° 75/160 (2022). Intensificación de los esfuerzos mundiales para la eliminación de la mutilación genital femenina</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2022/10/intensificacion-de-los-esfuerzos-mundiales-para-la-eliminacion-de-la-mutilacion-genital-femenina-informe-del-secretario-general-2022</t>
-  </si>
-  <si>
     <t>1.03.06</t>
   </si>
   <si>
     <t>Resolución N° 73/146 (2020). Trata de mujeres y niñas</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2020/07/a-75-289-sg-report-trafficking</t>
-  </si>
-  <si>
     <t>1.03.07</t>
   </si>
   <si>
     <t>Resolución N° 73/149 (2020). Intensificación de los esfuerzos mundiales para la eliminación de la mutilación genital femenina</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2020/07/a-75-279-sg-report-female-genital-mutilation</t>
-  </si>
-  <si>
     <t>1.03.08</t>
   </si>
   <si>
     <t>Resolución N° 73/148 (2020). Intensificación de los esfuerzos para eliminar todas las formas de violencia contra las mujeres y las niñas</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2020/07/a-75-274-sg-report-ending-violence-against-women-and-girls</t>
-  </si>
-  <si>
     <t>1.03.09</t>
   </si>
   <si>
     <t>Resolución N° 72/148 (2019). Mejoramiento de la situación de la mujer y la niña en las zonas rurales: Informe del Secretario General</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2019/07/a-74-224-sg-report-women-and-girls-in-rural-areas</t>
-  </si>
-  <si>
     <t>1.03.10</t>
   </si>
   <si>
@@ -350,9 +320,6 @@
     <t>Resolución N° 2242 (2015). Relativa a la necesidad de que las mujeres participen activa y efectivamente en el establecimiento y la consolidación de la paz.</t>
   </si>
   <si>
-    <t>https://www.refworld.org/es/leg/resol/csonu/2015/es/107506</t>
-  </si>
-  <si>
     <t>1.04.04</t>
   </si>
   <si>
@@ -524,9 +491,6 @@
     <t>Recomendaciones sobre la protección de las defensoras de los derechos humanos de las personas en situación de riesgo en contextos de migración (2022)</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2022/11/recommendations-on-the-protection-of-migrant-women-human-rights-defenders</t>
-  </si>
-  <si>
     <t>1.05.14</t>
   </si>
   <si>
@@ -542,9 +506,6 @@
     <t>Informe del Grupo de Alto Nivel: Justicia para las mujeres (2020)</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2020/03/justice-for-women-high-level-group-report</t>
-  </si>
-  <si>
     <t>1.05.16</t>
   </si>
   <si>
@@ -587,21 +548,12 @@
     <t>Recomendaciones para la acción contra los asesinatos de mujeres y niñas por motivos de género (2015)</t>
   </si>
   <si>
-    <t>https://www.unwomen.org/es/digital-library/publications/2015/10/recommendations-for-action-against-gender-related-killing-of-women-and-girls</t>
-  </si>
-  <si>
     <t>1.05.21</t>
   </si>
   <si>
     <t>Informe del Alto comisionado de las Naciones Unidas para los Derechos Humanos: Las leyes y prácticas discriminatorias y actos de violencia cometidas contra personas por su orientación sexual e identidad de género (2011).</t>
   </si>
   <si>
-    <t>https://www.indh.cl/wp-content/uploads/2011/12/Informe-alta-comisionado-mujeres.pdf</t>
-  </si>
-  <si>
-    <t>Alerta de conexión no segura</t>
-  </si>
-  <si>
     <t>Observaciones y/o recomendaciones de órganos de las Naciones Unidas al Perú</t>
   </si>
   <si>
@@ -729,9 +681,6 @@
   </si>
   <si>
     <t>Convención Americana sobre Derechos Humanos (1969)</t>
-  </si>
-  <si>
-    <t>https://www.oas.org/dil/esp/tratados_B-32_Convencion_Americana_sobre_Derechos_Humanos.htm</t>
   </si>
   <si>
     <t>2.01.05</t>
@@ -1875,12 +1824,6 @@
     <t>2002</t>
   </si>
   <si>
-    <t>https://spij.minjus.gob.pe/spij-ext-web/#/detallenorma/H1141065</t>
-  </si>
-  <si>
-    <t>Cambio a enlace directo (10-07)</t>
-  </si>
-  <si>
     <t>4.02.01a</t>
   </si>
   <si>
@@ -1906,6 +1849,60 @@
   </si>
   <si>
     <t>Datos generales de la Ley N° 30364</t>
+  </si>
+  <si>
+    <t>Cambiado para tener enlace más directo</t>
+  </si>
+  <si>
+    <t>https://www.oas.org/dil/esp/tratados_B-32_Convencion_Americana_sobre_Derechos_Humanos.pdf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1AWG2-ptlfBYeywc-ycszhZVUgR2smNy1/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1z1XW3WDvkj4PEw0_YX7xUqo4333RhsXi/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15CfJ9bF7l0fAMF5wTiP--VWSs83y2onw/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1X746Bi1j_VcyfGJKka_xk_AXlPlZDEpK/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VI3BDQbkzrdjZBAWvl09c3CtY0JbWAjn/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NZxgSF7APoQxYfRsau4JSFz6n13jlj0O/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ddLuVL3TDkRlrsMQ5Ul3n-hV16WmjDT2/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kh6GHYmesfkHg_XoDxbacvilXWGW3791/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1E_edu5jvm0IEv4BHq2RsAyjNOXHCNWqV/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1E2U13qKsh3mIoqC5wOMQ0pIR-g3G0csw/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1PCBdCON3Ez3DNRTefzKec1R9vNi2ndej/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Od7WnrKqdrmHKbxox_astafmQU0rItMX/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mc4lYFsJOlkgfag3Cvs13sbyzVeWLKUy/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HyacR4POYQON8UIXMfFFUCEsLFaZWHft/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1R4ut7x1brama8_7gnSr3B7liCzqzCz0g/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1pudijQBFD7x2fvmPZdr-leSweoANrEEr/view?usp=sharing</t>
   </si>
 </sst>
 </file>
@@ -1944,12 +1941,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -1989,7 +1992,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2014,6 +2017,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2712,7 +2718,7 @@
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="9" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -2742,7 +2748,7 @@
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="9" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -2772,7 +2778,7 @@
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="9" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -2802,7 +2808,7 @@
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="9" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -2832,7 +2838,7 @@
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="9" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -2862,7 +2868,7 @@
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="9" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -2892,7 +2898,7 @@
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="9" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -2922,7 +2928,7 @@
       </c>
       <c r="I9" s="8"/>
       <c r="J9" s="9" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -2952,7 +2958,7 @@
       </c>
       <c r="I10" s="8"/>
       <c r="J10" s="9" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="84" x14ac:dyDescent="0.2">
@@ -2982,7 +2988,7 @@
       </c>
       <c r="I11" s="8"/>
       <c r="J11" s="9" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3012,7 +3018,7 @@
       </c>
       <c r="I12" s="8"/>
       <c r="J12" s="9" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3042,7 +3048,7 @@
       </c>
       <c r="I13" s="8"/>
       <c r="J13" s="9" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3067,12 +3073,14 @@
       <c r="G14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I14" s="8"/>
+      <c r="H14" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J14" s="9" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3086,23 +3094,25 @@
         <v>1.02</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I15" s="8"/>
+      <c r="H15" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J15" s="9" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3116,26 +3126,26 @@
         <v>1.03</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="G16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>63</v>
       </c>
       <c r="I16" s="8"/>
       <c r="J16" s="9" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>1</v>
       </c>
@@ -3146,26 +3156,28 @@
         <v>1.03</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="8"/>
+      <c r="H17" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J17" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>1</v>
       </c>
@@ -3176,26 +3188,28 @@
         <v>1.03</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="8"/>
+      <c r="H18" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J18" s="9" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3206,26 +3220,28 @@
         <v>1.03</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="8"/>
+      <c r="H19" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J19" s="9" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>1</v>
       </c>
@@ -3236,23 +3252,25 @@
         <v>1.03</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I20" s="8"/>
+      <c r="H20" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J20" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3266,23 +3284,25 @@
         <v>1.03</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I21" s="8"/>
+      <c r="H21" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J21" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3296,26 +3316,28 @@
         <v>1.03</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="I22" s="8"/>
+      <c r="H22" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J22" s="9" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>1</v>
       </c>
@@ -3326,23 +3348,25 @@
         <v>1.03</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="8"/>
+      <c r="H23" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J23" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3356,23 +3380,25 @@
         <v>1.03</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I24" s="8"/>
+      <c r="H24" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J24" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3386,23 +3412,23 @@
         <v>1.03</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I25" s="8"/>
       <c r="J25" s="9" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3416,23 +3442,23 @@
         <v>1.03</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="I26" s="8"/>
       <c r="J26" s="9" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3446,23 +3472,23 @@
         <v>1.04</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I27" s="8"/>
       <c r="J27" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3476,23 +3502,23 @@
         <v>1.04</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I28" s="8"/>
       <c r="J28" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3506,23 +3532,25 @@
         <v>1.04</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="I29" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J29" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3536,23 +3564,23 @@
         <v>1.04</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I30" s="8"/>
       <c r="J30" s="9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3566,23 +3594,23 @@
         <v>1.04</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="I31" s="8"/>
       <c r="J31" s="9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3596,23 +3624,23 @@
         <v>1.04</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I32" s="8"/>
       <c r="J32" s="9" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -3626,23 +3654,23 @@
         <v>1.04</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="9" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3656,23 +3684,23 @@
         <v>1.04</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="I34" s="8"/>
       <c r="J34" s="9" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3686,23 +3714,23 @@
         <v>1.04</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="I35" s="8"/>
       <c r="J35" s="9" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -3716,23 +3744,23 @@
         <v>1.05</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="I36" s="8"/>
       <c r="J36" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -3746,23 +3774,23 @@
         <v>1.05</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I37" s="8"/>
       <c r="J37" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3776,23 +3804,23 @@
         <v>1.05</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I38" s="8"/>
       <c r="J38" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -3806,23 +3834,23 @@
         <v>1.05</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>133</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="I39" s="8"/>
       <c r="J39" s="9" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3836,23 +3864,23 @@
         <v>1.05</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="I40" s="8"/>
       <c r="J40" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3866,23 +3894,23 @@
         <v>1.05</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="I41" s="8"/>
       <c r="J41" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -3896,23 +3924,23 @@
         <v>1.05</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I42" s="8"/>
       <c r="J42" s="9" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -3926,23 +3954,23 @@
         <v>1.05</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I43" s="8"/>
       <c r="J43" s="9" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -3956,23 +3984,23 @@
         <v>1.05</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I44" s="8"/>
       <c r="J44" s="9" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -3986,23 +4014,23 @@
         <v>1.05</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I45" s="8"/>
       <c r="J45" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4016,23 +4044,23 @@
         <v>1.05</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="I46" s="8"/>
       <c r="J46" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4046,23 +4074,23 @@
         <v>1.05</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="I47" s="8"/>
       <c r="J47" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4076,23 +4104,25 @@
         <v>1.05</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H48" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="I48" s="8"/>
+      <c r="H48" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J48" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -4106,23 +4136,23 @@
         <v>1.05</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="G49" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I49" s="8"/>
       <c r="J49" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4136,23 +4166,25 @@
         <v>1.05</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H50" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I50" s="8"/>
+      <c r="H50" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J50" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4166,23 +4198,23 @@
         <v>1.05</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I51" s="8"/>
       <c r="J51" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -4196,23 +4228,23 @@
         <v>1.05</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="I52" s="8"/>
       <c r="J52" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4226,23 +4258,23 @@
         <v>1.05</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I53" s="8"/>
       <c r="J53" s="9" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4256,26 +4288,26 @@
         <v>1.05</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I54" s="8"/>
       <c r="J54" s="9" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="36" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>1</v>
       </c>
@@ -4286,23 +4318,25 @@
         <v>1.05</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H55" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I55" s="8"/>
+      <c r="H55" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J55" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -4316,25 +4350,25 @@
         <v>1.05</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="G56" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H56" s="7" t="s">
-        <v>185</v>
+      <c r="H56" s="10" t="s">
+        <v>605</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>186</v>
+        <v>602</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4348,23 +4382,23 @@
         <v>1.06</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="G57" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="I57" s="8"/>
       <c r="J57" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4378,23 +4412,23 @@
         <v>1.06</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="I58" s="8"/>
       <c r="J58" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4408,23 +4442,23 @@
         <v>1.06</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="G59" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="I59" s="8"/>
       <c r="J59" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4438,23 +4472,23 @@
         <v>1.06</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="I60" s="8"/>
       <c r="J60" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4468,23 +4502,23 @@
         <v>1.06</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="G61" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="I61" s="8"/>
       <c r="J61" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4498,23 +4532,23 @@
         <v>1.07</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="I62" s="8"/>
       <c r="J62" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -4528,23 +4562,23 @@
         <v>1.07</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="G63" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="I63" s="8"/>
       <c r="J63" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4558,23 +4592,23 @@
         <v>1.07</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="I64" s="8"/>
       <c r="J64" s="9" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4588,23 +4622,23 @@
         <v>1.07</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="G65" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="I65" s="8"/>
       <c r="J65" s="9" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4612,29 +4646,29 @@
         <v>2</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C66" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="G66" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="I66" s="8"/>
       <c r="J66" s="9" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4642,29 +4676,29 @@
         <v>2</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C67" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="G67" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="I67" s="8"/>
       <c r="J67" s="9" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4672,29 +4706,29 @@
         <v>2</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C68" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="I68" s="8"/>
       <c r="J68" s="9" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4702,29 +4736,31 @@
         <v>2</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C69" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="G69" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H69" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I69" s="8"/>
+        <v>603</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="J69" s="9" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4732,29 +4768,29 @@
         <v>2</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C70" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="G70" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="I70" s="8"/>
       <c r="J70" s="9" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4762,29 +4798,29 @@
         <v>2</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C71" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D71" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>234</v>
-      </c>
       <c r="F71" s="8" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="G71" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="I71" s="8"/>
       <c r="J71" s="9" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4792,29 +4828,29 @@
         <v>2</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C72" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="G72" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="I72" s="8"/>
       <c r="J72" s="9" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4822,29 +4858,29 @@
         <v>2</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C73" s="5">
         <v>2.0099999999999998</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H73" s="7" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="I73" s="8"/>
       <c r="J73" s="9" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4852,29 +4888,29 @@
         <v>2</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C74" s="5">
         <v>2.02</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H74" s="7" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="I74" s="8"/>
       <c r="J74" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -4882,29 +4918,29 @@
         <v>2</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C75" s="5">
         <v>2.0299999999999998</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H75" s="7" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="I75" s="8"/>
       <c r="J75" s="9" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -4912,29 +4948,29 @@
         <v>2</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C76" s="5">
         <v>2.04</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H76" s="7" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="I76" s="8"/>
       <c r="J76" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4942,29 +4978,29 @@
         <v>2</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C77" s="5">
         <v>2.04</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="G77" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="I77" s="8"/>
       <c r="J77" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -4972,29 +5008,29 @@
         <v>2</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C78" s="5">
         <v>2.04</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H78" s="7" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="I78" s="8"/>
       <c r="J78" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5002,29 +5038,29 @@
         <v>2</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C79" s="5">
         <v>2.04</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="G79" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H79" s="7" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="I79" s="8"/>
       <c r="J79" s="9" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5032,29 +5068,29 @@
         <v>2</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C80" s="5">
         <v>2.04</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="G80" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H80" s="7" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="I80" s="8"/>
       <c r="J80" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5062,29 +5098,29 @@
         <v>2</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C81" s="5">
         <v>2.04</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="F81" s="8" t="s">
         <v>251</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="F81" s="8" t="s">
-        <v>268</v>
       </c>
       <c r="G81" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H81" s="7" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="I81" s="8"/>
       <c r="J81" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5092,29 +5128,29 @@
         <v>2</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C82" s="5">
         <v>2.04</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="F82" s="8" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="G82" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H82" s="7" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="I82" s="8"/>
       <c r="J82" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5122,29 +5158,29 @@
         <v>2</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C83" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="F83" s="8" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="G83" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H83" s="7" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="I83" s="8"/>
       <c r="J83" s="9" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5152,29 +5188,29 @@
         <v>2</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C84" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="F84" s="8" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="G84" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="I84" s="8"/>
       <c r="J84" s="9" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5182,29 +5218,29 @@
         <v>2</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C85" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="F85" s="8" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="G85" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H85" s="7" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="I85" s="8"/>
       <c r="J85" s="9" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5212,29 +5248,29 @@
         <v>2</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C86" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="F86" s="8" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="G86" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H86" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="I86" s="8"/>
       <c r="J86" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -5242,29 +5278,29 @@
         <v>2</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C87" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="G87" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H87" s="7" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="I87" s="8"/>
       <c r="J87" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5272,29 +5308,29 @@
         <v>2</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C88" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D88" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="F88" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F88" s="8" t="s">
-        <v>290</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H88" s="7" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="I88" s="8"/>
       <c r="J88" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5302,29 +5338,29 @@
         <v>2</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C89" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="F89" s="8" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="G89" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="I89" s="8"/>
       <c r="J89" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -5332,29 +5368,29 @@
         <v>2</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C90" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="F90" s="8" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="I90" s="8"/>
       <c r="J90" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5362,29 +5398,29 @@
         <v>2</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C91" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="F91" s="8" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="G91" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="I91" s="8"/>
       <c r="J91" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5392,29 +5428,29 @@
         <v>2</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C92" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="F92" s="8" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="I92" s="8"/>
       <c r="J92" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5422,29 +5458,29 @@
         <v>2</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C93" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="F93" s="8" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="G93" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="I93" s="8"/>
       <c r="J93" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5452,29 +5488,29 @@
         <v>2</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C94" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="F94" s="8" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="G94" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="I94" s="8"/>
       <c r="J94" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5482,29 +5518,29 @@
         <v>2</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C95" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="F95" s="8" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="G95" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="I95" s="8"/>
       <c r="J95" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5512,29 +5548,29 @@
         <v>2</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C96" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="F96" s="8" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="G96" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="I96" s="8"/>
       <c r="J96" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5542,29 +5578,29 @@
         <v>2</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C97" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="F97" s="8" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="G97" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="I97" s="8"/>
       <c r="J97" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5572,29 +5608,29 @@
         <v>2</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C98" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="G98" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="I98" s="8"/>
       <c r="J98" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5602,29 +5638,29 @@
         <v>2</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C99" s="5">
         <v>2.0499999999999998</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="F99" s="8" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="G99" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="I99" s="8"/>
       <c r="J99" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5632,29 +5668,29 @@
         <v>2</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C100" s="5">
         <v>2.06</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="F100" s="8" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="G100" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="I100" s="8"/>
       <c r="J100" s="9" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5662,29 +5698,29 @@
         <v>2</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C101" s="5">
         <v>2.06</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="F101" s="8" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="G101" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="I101" s="8"/>
       <c r="J101" s="9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5692,29 +5728,29 @@
         <v>2</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C102" s="5">
         <v>2.06</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="F102" s="8" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="I102" s="8"/>
       <c r="J102" s="9" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5722,29 +5758,29 @@
         <v>2</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="C103" s="5">
         <v>2.06</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="G103" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="I103" s="8"/>
       <c r="J103" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -5752,29 +5788,29 @@
         <v>3</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="C104" s="5">
         <v>3.01</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="F104" s="8" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="I104" s="8"/>
       <c r="J104" s="9" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5782,27 +5818,27 @@
         <v>4</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C105" s="5">
         <v>4.01</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="F105" s="8" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H105" s="7"/>
       <c r="I105" s="8"/>
       <c r="J105" s="9" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="156" x14ac:dyDescent="0.2">
@@ -5810,27 +5846,27 @@
         <v>4</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C106" s="5">
         <v>4.01</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="F106" s="8" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H106" s="7"/>
       <c r="I106" s="8"/>
       <c r="J106" s="9" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -5838,127 +5874,127 @@
         <v>4</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C107" s="5">
         <v>4.0199999999999996</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="G107" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H107" s="7" t="s">
-        <v>610</v>
+      <c r="H107" s="10" t="s">
+        <v>604</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="J107" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="48" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C108" s="5">
         <v>4.0199999999999996</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="J108" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C109" s="5">
         <v>4.0199999999999996</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="J109" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="60" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C110" s="5">
         <v>4.0199999999999996</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="J110" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -5966,29 +6002,29 @@
         <v>4</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C111" s="5">
         <v>4.0199999999999996</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="G111" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="I111" s="8"/>
       <c r="J111" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -5996,29 +6032,29 @@
         <v>4</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C112" s="5">
         <v>4.03</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="F112" s="8" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="G112" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="I112" s="8"/>
       <c r="J112" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -6026,29 +6062,29 @@
         <v>4</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C113" s="5">
         <v>4.03</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="F113" s="8" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="G113" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="I113" s="8"/>
       <c r="J113" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -6056,29 +6092,29 @@
         <v>4</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C114" s="5">
         <v>4.03</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="F114" s="8" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="G114" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="I114" s="8"/>
       <c r="J114" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6086,29 +6122,29 @@
         <v>4</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="C115" s="5">
         <v>4.03</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="F115" s="8" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="G115" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="I115" s="8"/>
       <c r="J115" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -6116,29 +6152,29 @@
         <v>5</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C116" s="5">
         <v>5.01</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="I116" s="8"/>
       <c r="J116" s="9" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6146,29 +6182,29 @@
         <v>5</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C117" s="5">
         <v>5.01</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="I117" s="8"/>
       <c r="J117" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6176,29 +6212,29 @@
         <v>5</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C118" s="5">
         <v>5.0199999999999996</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="F118" s="8" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H118" s="7" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="I118" s="8"/>
       <c r="J118" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6206,29 +6242,29 @@
         <v>5</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C119" s="5">
         <v>5.0199999999999996</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="F119" s="8" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="G119" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="I119" s="8"/>
       <c r="J119" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -6236,29 +6272,29 @@
         <v>5</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C120" s="5">
         <v>5.0199999999999996</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="F120" s="8" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="I120" s="8"/>
       <c r="J120" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6266,29 +6302,29 @@
         <v>5</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C121" s="5">
         <v>5.03</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="F121" s="8" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="G121" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="I121" s="8"/>
       <c r="J121" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6296,29 +6332,29 @@
         <v>5</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C122" s="5">
         <v>5.03</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="F122" s="8" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="G122" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H122" s="7" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="I122" s="8"/>
       <c r="J122" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6326,29 +6362,29 @@
         <v>5</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C123" s="5">
         <v>5.03</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="G123" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="I123" s="8"/>
       <c r="J123" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -6356,29 +6392,29 @@
         <v>5</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C124" s="5">
         <v>5.03</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="F124" s="8" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="G124" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H124" s="7" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="I124" s="8"/>
       <c r="J124" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -6386,29 +6422,29 @@
         <v>5</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C125" s="5">
         <v>5.03</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="F125" s="8" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="G125" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H125" s="7" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="I125" s="8"/>
       <c r="J125" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6416,29 +6452,29 @@
         <v>5</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C126" s="5">
         <v>5.03</v>
       </c>
       <c r="D126" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F126" s="8" t="s">
         <v>381</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="F126" s="8" t="s">
-        <v>398</v>
       </c>
       <c r="G126" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H126" s="7" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="I126" s="8"/>
       <c r="J126" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -6446,29 +6482,29 @@
         <v>5</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C127" s="5">
         <v>5.03</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="F127" s="8" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="G127" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H127" s="7" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="I127" s="8"/>
       <c r="J127" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6476,29 +6512,29 @@
         <v>5</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="C128" s="5">
         <v>5.03</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="F128" s="8" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="G128" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H128" s="7" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="I128" s="8"/>
       <c r="J128" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6506,29 +6542,29 @@
         <v>6</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C129" s="5">
         <v>6.01</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="F129" s="8" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="G129" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H129" s="7" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="I129" s="8"/>
       <c r="J129" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6536,29 +6572,29 @@
         <v>6</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C130" s="5">
         <v>6.01</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="G130" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H130" s="7" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="I130" s="8"/>
       <c r="J130" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6566,27 +6602,27 @@
         <v>6</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C131" s="5">
         <v>6.02</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H131" s="7"/>
       <c r="I131" s="8"/>
       <c r="J131" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6594,29 +6630,29 @@
         <v>6</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C132" s="5">
         <v>6.03</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="F132" s="8" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="G132" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H132" s="7" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="I132" s="8"/>
       <c r="J132" s="9" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6624,29 +6660,29 @@
         <v>6</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C133" s="5">
         <v>6.03</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="F133" s="8" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="G133" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H133" s="7" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="I133" s="8"/>
       <c r="J133" s="9" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6654,29 +6690,29 @@
         <v>6</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C134" s="5">
         <v>6.04</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="F134" s="8" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="G134" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H134" s="7" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="I134" s="8"/>
       <c r="J134" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6684,27 +6720,27 @@
         <v>7</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C135" s="5">
         <v>7.01</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="F135" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H135" s="7"/>
       <c r="I135" s="8"/>
       <c r="J135" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6712,29 +6748,29 @@
         <v>7</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C136" s="5">
         <v>7.02</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="F136" s="8" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="G136" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H136" s="7" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="I136" s="8"/>
       <c r="J136" s="9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6742,29 +6778,29 @@
         <v>7</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C137" s="5">
         <v>7.02</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="F137" s="8" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="G137" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="I137" s="8"/>
       <c r="J137" s="9" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="72" x14ac:dyDescent="0.2">
@@ -6772,29 +6808,29 @@
         <v>7</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C138" s="5">
         <v>7.02</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="F138" s="8" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="G138" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="7" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="I138" s="8"/>
       <c r="J138" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6802,29 +6838,29 @@
         <v>7</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C139" s="5">
         <v>7.02</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="F139" s="8" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="G139" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H139" s="7" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="I139" s="8"/>
       <c r="J139" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -6832,29 +6868,29 @@
         <v>7</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C140" s="5">
         <v>7.02</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="F140" s="8" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="G140" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H140" s="7" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="I140" s="8"/>
       <c r="J140" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6862,29 +6898,29 @@
         <v>7</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C141" s="5">
         <v>7.02</v>
       </c>
       <c r="D141" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F141" s="8" t="s">
         <v>424</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="F141" s="8" t="s">
-        <v>441</v>
       </c>
       <c r="G141" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H141" s="7" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="I141" s="8"/>
       <c r="J141" s="9" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -6892,29 +6928,29 @@
         <v>7</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C142" s="5">
         <v>7.03</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="F142" s="8" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="G142" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H142" s="7" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -6922,29 +6958,29 @@
         <v>7</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C143" s="5">
         <v>7.03</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="F143" s="8" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="G143" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H143" s="7" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="I143" s="8"/>
       <c r="J143" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -6952,29 +6988,29 @@
         <v>7</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C144" s="5">
         <v>7.04</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="F144" s="8" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="G144" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H144" s="7" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="I144" s="8"/>
       <c r="J144" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -6982,29 +7018,29 @@
         <v>7</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C145" s="5">
         <v>7.05</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="F145" s="8" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="G145" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="I145" s="8"/>
       <c r="J145" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7012,29 +7048,29 @@
         <v>7</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C146" s="5">
         <v>7.05</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="F146" s="8" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="G146" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H146" s="7" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="I146" s="8"/>
       <c r="J146" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="84" x14ac:dyDescent="0.2">
@@ -7042,29 +7078,29 @@
         <v>7</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C147" s="5">
         <v>7.05</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="G147" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="I147" s="8"/>
       <c r="J147" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="96" x14ac:dyDescent="0.2">
@@ -7072,29 +7108,29 @@
         <v>7</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C148" s="5">
         <v>7.06</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
       <c r="F148" s="8" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="G148" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="I148" s="8"/>
       <c r="J148" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7102,31 +7138,31 @@
         <v>7</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C149" s="5">
         <v>7.07</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="F149" s="8" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="G149" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="I149" s="8" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="J149" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7134,29 +7170,29 @@
         <v>7</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C150" s="5">
         <v>7.07</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="F150" s="8" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="G150" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H150" s="7" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="I150" s="8"/>
       <c r="J150" s="9" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -7164,29 +7200,29 @@
         <v>7</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C151" s="5">
         <v>7.08</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="G151" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H151" s="7" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="I151" s="8"/>
       <c r="J151" s="9" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7194,29 +7230,29 @@
         <v>7</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C152" s="5">
         <v>7.08</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="F152" s="8" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="G152" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="I152" s="8"/>
       <c r="J152" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -7224,29 +7260,29 @@
         <v>7</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C153" s="5">
         <v>7.08</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="F153" s="8" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="G153" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H153" s="7" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="I153" s="8"/>
       <c r="J153" s="9" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -7254,29 +7290,29 @@
         <v>7</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C154" s="5">
         <v>7.08</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="G154" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H154" s="7" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="I154" s="8"/>
       <c r="J154" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7284,29 +7320,29 @@
         <v>7</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C155" s="5">
         <v>7.08</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="F155" s="8" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="G155" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H155" s="7" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="I155" s="8"/>
       <c r="J155" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7314,29 +7350,29 @@
         <v>7</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C156" s="5">
         <v>7.08</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="F156" s="8" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="G156" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H156" s="7" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="I156" s="8"/>
       <c r="J156" s="9" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7344,29 +7380,29 @@
         <v>7</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C157" s="5">
         <v>7.08</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="F157" s="8" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="G157" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H157" s="7" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="I157" s="8"/>
       <c r="J157" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="24" x14ac:dyDescent="0.2">
@@ -7374,29 +7410,29 @@
         <v>7</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C158" s="5">
         <v>7.09</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
       <c r="F158" s="8" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="G158" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H158" s="7" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="I158" s="8"/>
       <c r="J158" s="9" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7404,27 +7440,27 @@
         <v>7</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="F159" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G159" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H159" s="7"/>
       <c r="I159" s="8"/>
       <c r="J159" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7432,27 +7468,27 @@
         <v>7</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="F160" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H160" s="7"/>
       <c r="I160" s="8"/>
       <c r="J160" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7460,29 +7496,29 @@
         <v>7</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="G161" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H161" s="7" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="I161" s="8"/>
       <c r="J161" s="9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="96" x14ac:dyDescent="0.2">
@@ -7490,29 +7526,29 @@
         <v>7</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="G162" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H162" s="7" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
       <c r="I162" s="8"/>
       <c r="J162" s="9" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="108" x14ac:dyDescent="0.2">
@@ -7520,29 +7556,29 @@
         <v>7</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="E163" s="6" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
       <c r="F163" s="8" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="G163" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H163" s="7" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="I163" s="8"/>
       <c r="J163" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7550,25 +7586,25 @@
         <v>7</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="E164" s="6"/>
       <c r="F164" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H164" s="7"/>
       <c r="I164" s="8"/>
       <c r="J164" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7576,29 +7612,29 @@
         <v>7</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="E165" s="6" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="F165" s="8" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="G165" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H165" s="7" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="I165" s="8"/>
       <c r="J165" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="96" x14ac:dyDescent="0.2">
@@ -7606,29 +7642,29 @@
         <v>7</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="F166" s="8" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="G166" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H166" s="7" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="I166" s="8"/>
       <c r="J166" s="9" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7636,27 +7672,27 @@
         <v>7</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="E167" s="6" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="F167" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G167" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H167" s="7"/>
       <c r="I167" s="8"/>
       <c r="J167" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7664,29 +7700,29 @@
         <v>7</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="G168" s="6" t="s">
         <v>14</v>
       </c>
       <c r="H168" s="7" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="I168" s="8"/>
       <c r="J168" s="9" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7694,27 +7730,27 @@
         <v>7</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="E169" s="6" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="F169" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G169" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H169" s="7"/>
       <c r="I169" s="8"/>
       <c r="J169" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7722,27 +7758,27 @@
         <v>7</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="F170" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H170" s="7"/>
       <c r="I170" s="8"/>
       <c r="J170" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -7750,29 +7786,29 @@
         <v>7</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="E171" s="6" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="G171" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H171" s="7" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="I171" s="8"/>
       <c r="J171" s="9" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7780,27 +7816,27 @@
         <v>7</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H172" s="7"/>
       <c r="I172" s="8"/>
       <c r="J172" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7808,27 +7844,27 @@
         <v>7</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="E173" s="6" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G173" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H173" s="7"/>
       <c r="I173" s="8"/>
       <c r="J173" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7836,27 +7872,27 @@
         <v>7</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="E174" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="G174" s="6" t="s">
         <v>573</v>
-      </c>
-      <c r="F174" s="8" t="s">
-        <v>555</v>
-      </c>
-      <c r="G174" s="6" t="s">
-        <v>590</v>
       </c>
       <c r="H174" s="7"/>
       <c r="I174" s="8"/>
       <c r="J174" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="96" x14ac:dyDescent="0.2">
@@ -7864,29 +7900,29 @@
         <v>7</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="G175" s="6" t="s">
         <v>43</v>
       </c>
       <c r="H175" s="7" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="I175" s="8"/>
       <c r="J175" s="9" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="36" x14ac:dyDescent="0.2">
@@ -7894,27 +7930,27 @@
         <v>7</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="F176" s="8" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H176" s="7"/>
       <c r="I176" s="8"/>
       <c r="J176" s="9" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="48" x14ac:dyDescent="0.2">
@@ -7922,27 +7958,27 @@
         <v>7</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="F177" s="8" t="s">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="G177" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H177" s="7"/>
       <c r="I177" s="8"/>
       <c r="J177" s="9" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="60" x14ac:dyDescent="0.2">
@@ -7950,27 +7986,27 @@
         <v>7</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="F178" s="8" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="H178" s="7"/>
       <c r="I178" s="8"/>
       <c r="J178" s="9" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.2">
@@ -8007,89 +8043,89 @@
     <hyperlink ref="H26" r:id="rId25" xr:uid="{74D82626-2EC7-4C00-8FEE-C1C9503AB7F5}"/>
     <hyperlink ref="H27" r:id="rId26" xr:uid="{2856097F-68E3-4AE8-BD04-F04E76235807}"/>
     <hyperlink ref="H28" r:id="rId27" xr:uid="{813F8558-6D69-4016-8899-F283C96A57E8}"/>
-    <hyperlink ref="H29" r:id="rId28" xr:uid="{3A2DC81B-9CF1-40E7-8D87-A951C9F4DBDA}"/>
-    <hyperlink ref="H30" r:id="rId29" xr:uid="{D7378B86-3B49-452F-A692-5D2860DC2FC1}"/>
-    <hyperlink ref="H31" r:id="rId30" xr:uid="{B9384021-3B15-4801-B687-CFDF2611747A}"/>
-    <hyperlink ref="H32" r:id="rId31" xr:uid="{8417C8DD-9D4F-4490-9661-AD62DF6056EA}"/>
-    <hyperlink ref="H33" r:id="rId32" xr:uid="{E121510F-A00A-4D17-8211-63222A8DB9D6}"/>
-    <hyperlink ref="H34" r:id="rId33" xr:uid="{9F9421F6-49C0-4462-A34A-276B18891776}"/>
-    <hyperlink ref="H35" r:id="rId34" xr:uid="{25B88973-3B31-46F6-8126-18EA34C91409}"/>
-    <hyperlink ref="H36" r:id="rId35" xr:uid="{261BC724-5AEE-4B4C-81D7-535400F9D2F8}"/>
-    <hyperlink ref="H37" r:id="rId36" xr:uid="{02D7452F-7946-44E5-99B8-4E71BE935764}"/>
-    <hyperlink ref="H38" r:id="rId37" xr:uid="{56498468-E054-408B-8F3D-DDDAF7057D7F}"/>
-    <hyperlink ref="H39" r:id="rId38" xr:uid="{2FCCE772-B439-460A-97E5-B7F2B53FE2D3}"/>
-    <hyperlink ref="H40" r:id="rId39" xr:uid="{FC8EDA32-2623-485E-8265-EC629EEFE660}"/>
-    <hyperlink ref="H41" r:id="rId40" xr:uid="{04BC0C49-E324-4BB1-AE0E-2385DFC7EB2E}"/>
-    <hyperlink ref="H42" r:id="rId41" xr:uid="{72A0163F-5124-41D8-B3A9-4A42841F204C}"/>
-    <hyperlink ref="H43" r:id="rId42" xr:uid="{976EC75B-B16D-4BF3-B95E-7E1B9355DA2C}"/>
-    <hyperlink ref="H44" r:id="rId43" xr:uid="{DAF1546C-9362-4664-9EC4-637BE968E504}"/>
-    <hyperlink ref="H45" r:id="rId44" xr:uid="{D1AA6371-D576-48C1-8D84-B93CE022A1CF}"/>
-    <hyperlink ref="H46" r:id="rId45" xr:uid="{910988FD-E587-4B4C-ADF1-797316B85BAB}"/>
-    <hyperlink ref="H47" r:id="rId46" xr:uid="{9EA120A6-907F-469D-BD49-7F7294B15092}"/>
-    <hyperlink ref="H48" r:id="rId47" xr:uid="{26608684-26FF-4FDF-A729-DD838DFCA5C4}"/>
-    <hyperlink ref="H49" r:id="rId48" xr:uid="{A374800D-27A7-406E-AB32-30E8BEADBC7A}"/>
-    <hyperlink ref="H50" r:id="rId49" xr:uid="{18D6E241-3E56-4371-A6E9-D7780B58E3F9}"/>
-    <hyperlink ref="H51" r:id="rId50" xr:uid="{0BCE2CBD-1E54-459C-AA67-0F1AC051F968}"/>
-    <hyperlink ref="H52" r:id="rId51" xr:uid="{E59235C0-AEB3-402D-B3DB-67FF8D1DFBF6}"/>
-    <hyperlink ref="H53" r:id="rId52" xr:uid="{715055EC-5359-4693-90C3-273133773A9D}"/>
-    <hyperlink ref="H54" r:id="rId53" xr:uid="{C74A6DE9-E538-4D96-A9F9-834643580F34}"/>
-    <hyperlink ref="H55" r:id="rId54" xr:uid="{96E256A8-C732-4E6C-A32B-FEA1BE0FABAB}"/>
-    <hyperlink ref="H56" r:id="rId55" xr:uid="{6875304E-3027-45E4-B2D5-FEA25C59E82C}"/>
-    <hyperlink ref="H57" r:id="rId56" xr:uid="{04969C08-79AC-4D42-8CE3-CAFFB0537C10}"/>
-    <hyperlink ref="H58" r:id="rId57" xr:uid="{12F8AEE1-37F5-4BFF-A52A-BA7D4F889A6B}"/>
-    <hyperlink ref="H59" r:id="rId58" xr:uid="{D799EA0A-0DA8-4B3B-B8F8-17482E78DCC8}"/>
-    <hyperlink ref="H60" r:id="rId59" xr:uid="{9B183846-8DF7-4187-845E-590FF1370266}"/>
-    <hyperlink ref="H61" r:id="rId60" xr:uid="{153AAF8C-2EC1-4411-A070-FF48B25065C3}"/>
-    <hyperlink ref="H62" r:id="rId61" xr:uid="{32E85537-1ED2-493F-A8C5-EDC8C60F6ED8}"/>
-    <hyperlink ref="H63" r:id="rId62" xr:uid="{1E6871C4-3F46-4D10-98D0-DC27525C3061}"/>
-    <hyperlink ref="H64" r:id="rId63" xr:uid="{4B3A534E-36E6-4851-8AC7-B8C79C230793}"/>
-    <hyperlink ref="H65" r:id="rId64" xr:uid="{24F233BE-CDF0-4E26-B2C8-CAD0083CD5F6}"/>
-    <hyperlink ref="H66" r:id="rId65" xr:uid="{C71515BF-7B53-4054-B808-308C2777D525}"/>
-    <hyperlink ref="H67" r:id="rId66" xr:uid="{F78D8424-2C23-42FC-81CF-2E9350C1CF7C}"/>
-    <hyperlink ref="H68" r:id="rId67" xr:uid="{18977989-C1B6-4631-8DF0-D0D36D63C6D9}"/>
-    <hyperlink ref="H69" r:id="rId68" xr:uid="{AC457101-DFCF-469C-9A77-ADA88EB68879}"/>
-    <hyperlink ref="H70" r:id="rId69" xr:uid="{20158A9A-CEFD-4916-90D6-C5AD98AFBD85}"/>
-    <hyperlink ref="H71" r:id="rId70" xr:uid="{49958A06-D404-4950-B198-D5BDF2B41E81}"/>
-    <hyperlink ref="H72" r:id="rId71" xr:uid="{63A26A8F-A965-4292-8A87-D9EC14052412}"/>
-    <hyperlink ref="H73" r:id="rId72" xr:uid="{1E7667CB-7682-4E0B-A105-2FF8084F31B8}"/>
-    <hyperlink ref="H74" r:id="rId73" xr:uid="{90E4BAF5-29E7-4FDB-970D-CE6D7885E15A}"/>
-    <hyperlink ref="H75" r:id="rId74" xr:uid="{F0C5D31A-FDCB-412A-B519-99613C599937}"/>
-    <hyperlink ref="H76" r:id="rId75" xr:uid="{B0EAB310-4F3E-44E9-AEC6-05BF0A380B79}"/>
-    <hyperlink ref="H77" r:id="rId76" xr:uid="{D33D48A9-E237-4F41-B15E-6EC6EF4B681C}"/>
-    <hyperlink ref="H78" r:id="rId77" xr:uid="{C40B70D9-ACFD-44C1-907C-6ADD82D8CBE3}"/>
-    <hyperlink ref="H79" r:id="rId78" xr:uid="{D3DAE146-DF6A-4CEE-AA4B-96F29E336CB4}"/>
-    <hyperlink ref="H80" r:id="rId79" xr:uid="{C11E5D6A-6951-429D-BBC7-7883490FCB39}"/>
-    <hyperlink ref="H81" r:id="rId80" xr:uid="{AEE90FD7-B935-4C33-A431-F61B2D816C32}"/>
-    <hyperlink ref="H82" r:id="rId81" xr:uid="{54397E88-427E-4862-8A85-1B460753E65C}"/>
-    <hyperlink ref="H83" r:id="rId82" xr:uid="{44688D06-E3AE-4311-B4ED-34F9BDBDEDC1}"/>
-    <hyperlink ref="H84" r:id="rId83" xr:uid="{6C69B01C-1AAE-42DF-A500-D05E4D63A8DC}"/>
-    <hyperlink ref="H85" r:id="rId84" xr:uid="{1BEAAB77-FED0-4BCA-A041-90420988629F}"/>
-    <hyperlink ref="H86" r:id="rId85" xr:uid="{B1D98BD0-CE7C-4ED9-AD21-342A4561CBC4}"/>
-    <hyperlink ref="H87" r:id="rId86" xr:uid="{B226A949-56DB-4B3A-9C59-28272C8AADB8}"/>
-    <hyperlink ref="H88" r:id="rId87" xr:uid="{67170612-D4E5-4E96-B018-93BEFA4F6DC3}"/>
-    <hyperlink ref="H89" r:id="rId88" xr:uid="{85945315-C373-4E2E-B0CA-C66FD4C4A5F2}"/>
-    <hyperlink ref="H90" r:id="rId89" xr:uid="{04FB7947-2F56-47E1-8E10-B352AB995068}"/>
-    <hyperlink ref="H91" r:id="rId90" xr:uid="{DE0DD762-301C-4615-B99C-3E79293F85E2}"/>
-    <hyperlink ref="H92" r:id="rId91" xr:uid="{9634A449-8EB6-4458-AAA7-B94221284318}"/>
-    <hyperlink ref="H93" r:id="rId92" xr:uid="{AF176C46-5696-4D69-A382-C48D5EF68579}"/>
-    <hyperlink ref="H94" r:id="rId93" xr:uid="{9B51B4D6-4406-4CC5-9796-4FD997B404A9}"/>
-    <hyperlink ref="H95" r:id="rId94" xr:uid="{C5C29ED4-CB1C-446A-B5C2-22A7D14CA95D}"/>
-    <hyperlink ref="H96" r:id="rId95" xr:uid="{83BABB29-4AF2-4473-B606-A08B63EC3F74}"/>
-    <hyperlink ref="H97" r:id="rId96" xr:uid="{6DC0B8F4-C96F-486C-827B-68A2C69B2762}"/>
-    <hyperlink ref="H98" r:id="rId97" xr:uid="{496E7C9C-5A44-4BAB-A743-13D0CE434D1C}"/>
-    <hyperlink ref="H99" r:id="rId98" xr:uid="{2E786533-AE7A-4C2C-B0E1-38BDBF66146D}"/>
-    <hyperlink ref="H100" r:id="rId99" xr:uid="{4E00B300-AD16-4C2B-96B5-AE7EC6D537F9}"/>
-    <hyperlink ref="H101" r:id="rId100" xr:uid="{B7B72683-DA26-41D0-B0F6-E1080E403EE1}"/>
-    <hyperlink ref="H102" r:id="rId101" xr:uid="{5617433B-0321-4203-8D4E-EAD2EEEB1C77}"/>
-    <hyperlink ref="H103" r:id="rId102" xr:uid="{AA0FAE12-D064-42BA-9572-F9CF50C33FCE}"/>
-    <hyperlink ref="H104" r:id="rId103" xr:uid="{DAACD957-CFE6-444C-8A56-466141B26B96}"/>
-    <hyperlink ref="H161" r:id="rId104" location="/detallenorma/H1088463" xr:uid="{8EBF9CA3-DB23-40BD-A593-EBC1B8117F8E}"/>
-    <hyperlink ref="H162" r:id="rId105" xr:uid="{7C08EDB5-E571-4CAD-8243-550C11757BE2}"/>
-    <hyperlink ref="H163" r:id="rId106" xr:uid="{EB567D07-C77F-4A93-A42D-6F9252276305}"/>
-    <hyperlink ref="H107" r:id="rId107" location="/detallenorma/H1141065" xr:uid="{B0CB6F18-72F1-48BC-8D36-A46C5B119F25}"/>
-    <hyperlink ref="H109" r:id="rId108" xr:uid="{10D3EFA4-77EE-48A4-95DE-F3D6EA72E545}"/>
-    <hyperlink ref="H110" r:id="rId109" xr:uid="{DC07E4B2-9492-45BD-9C16-4D869CD05636}"/>
-    <hyperlink ref="H108" r:id="rId110" xr:uid="{09297BBE-789F-4040-A27A-CDBD6E16A9FA}"/>
+    <hyperlink ref="H30" r:id="rId28" xr:uid="{D7378B86-3B49-452F-A692-5D2860DC2FC1}"/>
+    <hyperlink ref="H31" r:id="rId29" xr:uid="{B9384021-3B15-4801-B687-CFDF2611747A}"/>
+    <hyperlink ref="H32" r:id="rId30" xr:uid="{8417C8DD-9D4F-4490-9661-AD62DF6056EA}"/>
+    <hyperlink ref="H33" r:id="rId31" xr:uid="{E121510F-A00A-4D17-8211-63222A8DB9D6}"/>
+    <hyperlink ref="H34" r:id="rId32" xr:uid="{9F9421F6-49C0-4462-A34A-276B18891776}"/>
+    <hyperlink ref="H35" r:id="rId33" xr:uid="{25B88973-3B31-46F6-8126-18EA34C91409}"/>
+    <hyperlink ref="H36" r:id="rId34" xr:uid="{261BC724-5AEE-4B4C-81D7-535400F9D2F8}"/>
+    <hyperlink ref="H37" r:id="rId35" xr:uid="{02D7452F-7946-44E5-99B8-4E71BE935764}"/>
+    <hyperlink ref="H38" r:id="rId36" xr:uid="{56498468-E054-408B-8F3D-DDDAF7057D7F}"/>
+    <hyperlink ref="H39" r:id="rId37" xr:uid="{2FCCE772-B439-460A-97E5-B7F2B53FE2D3}"/>
+    <hyperlink ref="H40" r:id="rId38" xr:uid="{FC8EDA32-2623-485E-8265-EC629EEFE660}"/>
+    <hyperlink ref="H41" r:id="rId39" xr:uid="{04BC0C49-E324-4BB1-AE0E-2385DFC7EB2E}"/>
+    <hyperlink ref="H42" r:id="rId40" xr:uid="{72A0163F-5124-41D8-B3A9-4A42841F204C}"/>
+    <hyperlink ref="H43" r:id="rId41" xr:uid="{976EC75B-B16D-4BF3-B95E-7E1B9355DA2C}"/>
+    <hyperlink ref="H44" r:id="rId42" xr:uid="{DAF1546C-9362-4664-9EC4-637BE968E504}"/>
+    <hyperlink ref="H45" r:id="rId43" xr:uid="{D1AA6371-D576-48C1-8D84-B93CE022A1CF}"/>
+    <hyperlink ref="H46" r:id="rId44" xr:uid="{910988FD-E587-4B4C-ADF1-797316B85BAB}"/>
+    <hyperlink ref="H47" r:id="rId45" xr:uid="{9EA120A6-907F-469D-BD49-7F7294B15092}"/>
+    <hyperlink ref="H48" r:id="rId46" xr:uid="{26608684-26FF-4FDF-A729-DD838DFCA5C4}"/>
+    <hyperlink ref="H49" r:id="rId47" xr:uid="{A374800D-27A7-406E-AB32-30E8BEADBC7A}"/>
+    <hyperlink ref="H50" r:id="rId48" xr:uid="{18D6E241-3E56-4371-A6E9-D7780B58E3F9}"/>
+    <hyperlink ref="H51" r:id="rId49" xr:uid="{0BCE2CBD-1E54-459C-AA67-0F1AC051F968}"/>
+    <hyperlink ref="H52" r:id="rId50" xr:uid="{E59235C0-AEB3-402D-B3DB-67FF8D1DFBF6}"/>
+    <hyperlink ref="H53" r:id="rId51" xr:uid="{715055EC-5359-4693-90C3-273133773A9D}"/>
+    <hyperlink ref="H54" r:id="rId52" xr:uid="{C74A6DE9-E538-4D96-A9F9-834643580F34}"/>
+    <hyperlink ref="H55" r:id="rId53" xr:uid="{96E256A8-C732-4E6C-A32B-FEA1BE0FABAB}"/>
+    <hyperlink ref="H56" r:id="rId54" xr:uid="{6875304E-3027-45E4-B2D5-FEA25C59E82C}"/>
+    <hyperlink ref="H57" r:id="rId55" xr:uid="{04969C08-79AC-4D42-8CE3-CAFFB0537C10}"/>
+    <hyperlink ref="H58" r:id="rId56" xr:uid="{12F8AEE1-37F5-4BFF-A52A-BA7D4F889A6B}"/>
+    <hyperlink ref="H59" r:id="rId57" xr:uid="{D799EA0A-0DA8-4B3B-B8F8-17482E78DCC8}"/>
+    <hyperlink ref="H60" r:id="rId58" xr:uid="{9B183846-8DF7-4187-845E-590FF1370266}"/>
+    <hyperlink ref="H61" r:id="rId59" xr:uid="{153AAF8C-2EC1-4411-A070-FF48B25065C3}"/>
+    <hyperlink ref="H62" r:id="rId60" xr:uid="{32E85537-1ED2-493F-A8C5-EDC8C60F6ED8}"/>
+    <hyperlink ref="H63" r:id="rId61" xr:uid="{1E6871C4-3F46-4D10-98D0-DC27525C3061}"/>
+    <hyperlink ref="H64" r:id="rId62" xr:uid="{4B3A534E-36E6-4851-8AC7-B8C79C230793}"/>
+    <hyperlink ref="H65" r:id="rId63" xr:uid="{24F233BE-CDF0-4E26-B2C8-CAD0083CD5F6}"/>
+    <hyperlink ref="H66" r:id="rId64" xr:uid="{C71515BF-7B53-4054-B808-308C2777D525}"/>
+    <hyperlink ref="H67" r:id="rId65" xr:uid="{F78D8424-2C23-42FC-81CF-2E9350C1CF7C}"/>
+    <hyperlink ref="H68" r:id="rId66" xr:uid="{18977989-C1B6-4631-8DF0-D0D36D63C6D9}"/>
+    <hyperlink ref="H69" r:id="rId67" xr:uid="{AC457101-DFCF-469C-9A77-ADA88EB68879}"/>
+    <hyperlink ref="H70" r:id="rId68" xr:uid="{20158A9A-CEFD-4916-90D6-C5AD98AFBD85}"/>
+    <hyperlink ref="H71" r:id="rId69" xr:uid="{49958A06-D404-4950-B198-D5BDF2B41E81}"/>
+    <hyperlink ref="H72" r:id="rId70" xr:uid="{63A26A8F-A965-4292-8A87-D9EC14052412}"/>
+    <hyperlink ref="H73" r:id="rId71" xr:uid="{1E7667CB-7682-4E0B-A105-2FF8084F31B8}"/>
+    <hyperlink ref="H74" r:id="rId72" xr:uid="{90E4BAF5-29E7-4FDB-970D-CE6D7885E15A}"/>
+    <hyperlink ref="H75" r:id="rId73" xr:uid="{F0C5D31A-FDCB-412A-B519-99613C599937}"/>
+    <hyperlink ref="H76" r:id="rId74" xr:uid="{B0EAB310-4F3E-44E9-AEC6-05BF0A380B79}"/>
+    <hyperlink ref="H77" r:id="rId75" xr:uid="{D33D48A9-E237-4F41-B15E-6EC6EF4B681C}"/>
+    <hyperlink ref="H78" r:id="rId76" xr:uid="{C40B70D9-ACFD-44C1-907C-6ADD82D8CBE3}"/>
+    <hyperlink ref="H79" r:id="rId77" xr:uid="{D3DAE146-DF6A-4CEE-AA4B-96F29E336CB4}"/>
+    <hyperlink ref="H80" r:id="rId78" xr:uid="{C11E5D6A-6951-429D-BBC7-7883490FCB39}"/>
+    <hyperlink ref="H81" r:id="rId79" xr:uid="{AEE90FD7-B935-4C33-A431-F61B2D816C32}"/>
+    <hyperlink ref="H82" r:id="rId80" xr:uid="{54397E88-427E-4862-8A85-1B460753E65C}"/>
+    <hyperlink ref="H83" r:id="rId81" xr:uid="{44688D06-E3AE-4311-B4ED-34F9BDBDEDC1}"/>
+    <hyperlink ref="H84" r:id="rId82" xr:uid="{6C69B01C-1AAE-42DF-A500-D05E4D63A8DC}"/>
+    <hyperlink ref="H85" r:id="rId83" xr:uid="{1BEAAB77-FED0-4BCA-A041-90420988629F}"/>
+    <hyperlink ref="H86" r:id="rId84" xr:uid="{B1D98BD0-CE7C-4ED9-AD21-342A4561CBC4}"/>
+    <hyperlink ref="H87" r:id="rId85" xr:uid="{B226A949-56DB-4B3A-9C59-28272C8AADB8}"/>
+    <hyperlink ref="H88" r:id="rId86" xr:uid="{67170612-D4E5-4E96-B018-93BEFA4F6DC3}"/>
+    <hyperlink ref="H89" r:id="rId87" xr:uid="{85945315-C373-4E2E-B0CA-C66FD4C4A5F2}"/>
+    <hyperlink ref="H90" r:id="rId88" xr:uid="{04FB7947-2F56-47E1-8E10-B352AB995068}"/>
+    <hyperlink ref="H91" r:id="rId89" xr:uid="{DE0DD762-301C-4615-B99C-3E79293F85E2}"/>
+    <hyperlink ref="H92" r:id="rId90" xr:uid="{9634A449-8EB6-4458-AAA7-B94221284318}"/>
+    <hyperlink ref="H93" r:id="rId91" xr:uid="{AF176C46-5696-4D69-A382-C48D5EF68579}"/>
+    <hyperlink ref="H94" r:id="rId92" xr:uid="{9B51B4D6-4406-4CC5-9796-4FD997B404A9}"/>
+    <hyperlink ref="H95" r:id="rId93" xr:uid="{C5C29ED4-CB1C-446A-B5C2-22A7D14CA95D}"/>
+    <hyperlink ref="H96" r:id="rId94" xr:uid="{83BABB29-4AF2-4473-B606-A08B63EC3F74}"/>
+    <hyperlink ref="H97" r:id="rId95" xr:uid="{6DC0B8F4-C96F-486C-827B-68A2C69B2762}"/>
+    <hyperlink ref="H98" r:id="rId96" xr:uid="{496E7C9C-5A44-4BAB-A743-13D0CE434D1C}"/>
+    <hyperlink ref="H99" r:id="rId97" xr:uid="{2E786533-AE7A-4C2C-B0E1-38BDBF66146D}"/>
+    <hyperlink ref="H100" r:id="rId98" xr:uid="{4E00B300-AD16-4C2B-96B5-AE7EC6D537F9}"/>
+    <hyperlink ref="H101" r:id="rId99" xr:uid="{B7B72683-DA26-41D0-B0F6-E1080E403EE1}"/>
+    <hyperlink ref="H102" r:id="rId100" xr:uid="{5617433B-0321-4203-8D4E-EAD2EEEB1C77}"/>
+    <hyperlink ref="H103" r:id="rId101" xr:uid="{AA0FAE12-D064-42BA-9572-F9CF50C33FCE}"/>
+    <hyperlink ref="H104" r:id="rId102" xr:uid="{DAACD957-CFE6-444C-8A56-466141B26B96}"/>
+    <hyperlink ref="H161" r:id="rId103" location="/detallenorma/H1088463" xr:uid="{8EBF9CA3-DB23-40BD-A593-EBC1B8117F8E}"/>
+    <hyperlink ref="H162" r:id="rId104" xr:uid="{7C08EDB5-E571-4CAD-8243-550C11757BE2}"/>
+    <hyperlink ref="H163" r:id="rId105" xr:uid="{EB567D07-C77F-4A93-A42D-6F9252276305}"/>
+    <hyperlink ref="H107" r:id="rId106" xr:uid="{B0CB6F18-72F1-48BC-8D36-A46C5B119F25}"/>
+    <hyperlink ref="H109" r:id="rId107" xr:uid="{10D3EFA4-77EE-48A4-95DE-F3D6EA72E545}"/>
+    <hyperlink ref="H110" r:id="rId108" xr:uid="{DC07E4B2-9492-45BD-9C16-4D869CD05636}"/>
+    <hyperlink ref="H108" r:id="rId109" xr:uid="{09297BBE-789F-4040-A27A-CDBD6E16A9FA}"/>
+    <hyperlink ref="H29" r:id="rId110" xr:uid="{EC854CAC-86C6-4C2B-9181-705C112A2D9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId111"/>

--- a/Tabulado normas.xlsx
+++ b/Tabulado normas.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\git_porjects\chatbot_normatividad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Minmuj\git_projects\chatbot_normatividad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98EF7A8F-0F71-4CA2-8DE4-AC53ABC8D179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B059AA20-9FFB-466A-AC4D-F95D60E46438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="30" windowWidth="15990" windowHeight="15315" xr2:uid="{A43CB7C4-613E-4394-9B0D-B8228CDDEEE6}"/>
+    <workbookView xWindow="14955" yWindow="420" windowWidth="12990" windowHeight="15270" xr2:uid="{A43CB7C4-613E-4394-9B0D-B8228CDDEEE6}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$I$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$K$178</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="785">
   <si>
     <t>Tema_CD</t>
   </si>
@@ -1903,6 +1903,501 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1pudijQBFD7x2fvmPZdr-leSweoANrEEr/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>Ley 31968</t>
+  </si>
+  <si>
+    <t>Reglamento de la Ley 30364</t>
+  </si>
+  <si>
+    <t>Evolución de la Ley 30364</t>
+  </si>
+  <si>
+    <t>Informe de Alto Comisionado de las Naciones Unidas para los Derechos Humanos</t>
+  </si>
+  <si>
+    <t>Ley 30364</t>
+  </si>
+  <si>
+    <t>Datos generales de la Ley 30364</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 009-2016-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 012-2024-JUS</t>
+  </si>
+  <si>
+    <t>Ley 32535</t>
+  </si>
+  <si>
+    <t>Ley 31153</t>
+  </si>
+  <si>
+    <t>Ley 30403</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 003-2018-MIMP</t>
+  </si>
+  <si>
+    <t>Ley 30926</t>
+  </si>
+  <si>
+    <t>Ley 30815</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 145-2021-PCM</t>
+  </si>
+  <si>
+    <t>Ley 27637</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 003-2003-MIMDES</t>
+  </si>
+  <si>
+    <t>Ley 30862</t>
+  </si>
+  <si>
+    <t>Ley 30068</t>
+  </si>
+  <si>
+    <t>Ley 30965</t>
+  </si>
+  <si>
+    <t>Ley 30963</t>
+  </si>
+  <si>
+    <t>Ley 30314</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 005-2022-MIMP</t>
+  </si>
+  <si>
+    <t>Ley 27942</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 014-2019-MIMP</t>
+  </si>
+  <si>
+    <t>Ley 31155</t>
+  </si>
+  <si>
+    <t>Ley 30096</t>
+  </si>
+  <si>
+    <t>Decreto Legislativo 1625</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 164-2022-MIMP</t>
+  </si>
+  <si>
+    <t>Ley 31685</t>
+  </si>
+  <si>
+    <t>Declaración Americana de los Derechos y Deberes del Hombre</t>
+  </si>
+  <si>
+    <t>Declaración sobre el feminicidio</t>
+  </si>
+  <si>
+    <t>Declaración de Pachuca</t>
+  </si>
+  <si>
+    <t>Declaración sobre la violencia contra las niñas, mujeres, y adolescentes y sus derechos sexuales y reproductivos</t>
+  </si>
+  <si>
+    <t>Declaración sobre la violencia y el acoso políticos contra las mujeres</t>
+  </si>
+  <si>
+    <t>Declaración Regional sobre la erradicación de los estereotipos de género en los espacios públicos que se traducen en violencia simbólica y violencia política contra las mujeres por motivos de género</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 006-2015-JUS</t>
+  </si>
+  <si>
+    <t>Convención sobre la eliminación de todas las formas de discriminación contra la mujer</t>
+  </si>
+  <si>
+    <t>Convención Interamericana sobre la concesión de los derechos civiles a la mujer</t>
+  </si>
+  <si>
+    <t>Convención Interamericana sobre concesión de los derechos políticos a la mujer</t>
+  </si>
+  <si>
+    <t>Convención Americana sobre Derechos Humanos</t>
+  </si>
+  <si>
+    <t>Convención Interamericana para prevenir y sancionar la tortura</t>
+  </si>
+  <si>
+    <t>Protocolo de San Salvador</t>
+  </si>
+  <si>
+    <t>Convención de Belém Do Pará</t>
+  </si>
+  <si>
+    <t>Convención Interamericana para la eliminación de todas las formas de discriminación contra las personas con discapacidad</t>
+  </si>
+  <si>
+    <t>Ciberviolencia y ciberacoso contra las mujeres y niñas en el marco de la Convención Belém do Pará</t>
+  </si>
+  <si>
+    <t>Convenio de Budapest</t>
+  </si>
+  <si>
+    <t>Observaciones finales sobre los informes periódicos Sexto y Séptimo combinados del Perú en el marco de la Convención sobre los Derechos del Niño</t>
+  </si>
+  <si>
+    <t>Observaciones finales sobre el Noveno informe periódico del Perú en el marco de la Convención para la Eliminación de todas las Formas de Discriminación contra la Mujer</t>
+  </si>
+  <si>
+    <t>Resolución 80/185</t>
+  </si>
+  <si>
+    <t>Resolución 77/193</t>
+  </si>
+  <si>
+    <t>Resolución 77/194</t>
+  </si>
+  <si>
+    <t>Resolución 75/161</t>
+  </si>
+  <si>
+    <t>Resolución 75/160</t>
+  </si>
+  <si>
+    <t>Resolución 73/146</t>
+  </si>
+  <si>
+    <t>Resolución 73/149</t>
+  </si>
+  <si>
+    <t>Resolución 73/148</t>
+  </si>
+  <si>
+    <t>Resolución 72/148</t>
+  </si>
+  <si>
+    <t>Resolución 60/136</t>
+  </si>
+  <si>
+    <t>Resolución 58/147</t>
+  </si>
+  <si>
+    <t>Decreto Legislativo 1323</t>
+  </si>
+  <si>
+    <t>Resolución 2493</t>
+  </si>
+  <si>
+    <t>Resolución 2467</t>
+  </si>
+  <si>
+    <t>Resolución 2242</t>
+  </si>
+  <si>
+    <t>Resolución 2122</t>
+  </si>
+  <si>
+    <t>Resolución 2106</t>
+  </si>
+  <si>
+    <t>Resolución 1960</t>
+  </si>
+  <si>
+    <t>Resolución 1888</t>
+  </si>
+  <si>
+    <t>Resolución 1820</t>
+  </si>
+  <si>
+    <t>Resolución 1325</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la trata de personas, especialmente mujeres y niños: Trabajadores domésticos migrantes y trata de personas: Prevención, protección de derechos y acceso a la justicia</t>
+  </si>
+  <si>
+    <t>Informe del Grupo de Trabajo sobre la cuestión de la discriminación contra las mujeres y niñas: Los derechos en materia de salud sexual y reproductiva de las mujeres y las niñas en situaciones de crisis</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la violencia contra la mujer, sus causas y consecuencias: La prostitución y la violencia contra las mujeres y las niñas</t>
+  </si>
+  <si>
+    <t>Informe de la Experta Independiente sobre el disfrute de todos los derechos humanos de las personas de edad: Violencia, maltrato y abandono que sufren las personas de edad</t>
+  </si>
+  <si>
+    <t>Recomendación general 38</t>
+  </si>
+  <si>
+    <t>Observación general 3</t>
+  </si>
+  <si>
+    <t>Recomendación general 35</t>
+  </si>
+  <si>
+    <t>Recomendación general 33</t>
+  </si>
+  <si>
+    <t>Recomendación general 31</t>
+  </si>
+  <si>
+    <t>Recomendación general 25</t>
+  </si>
+  <si>
+    <t>Recomendación general 19</t>
+  </si>
+  <si>
+    <t>Recomendaciones sobre la protección de las defensoras de los derechos humanos de las personas en situación de riesgo en contextos de migración</t>
+  </si>
+  <si>
+    <t>Recomendaciones para la acción contra los asesinatos de mujeres y niñas por motivos de género</t>
+  </si>
+  <si>
+    <t>Recomendación general del Comité de Expertas del MESECVI 3</t>
+  </si>
+  <si>
+    <t>Recomendación general del Comité de Expertas del MESECVI 4</t>
+  </si>
+  <si>
+    <t>Recomendación general del Comité de Expertas del MESECVI 5</t>
+  </si>
+  <si>
+    <t>Recomendación general del Comité de Expertas del MESECVI 6</t>
+  </si>
+  <si>
+    <t>Diagnóstico regional sobre datos de desapariciones y trata de mujeres. Recomendaciones de política pública</t>
+  </si>
+  <si>
+    <t>Recomendación general del Comité de Expertas del MESECVI 1</t>
+  </si>
+  <si>
+    <t>Recomendación general del Comité de Expertas del MESECVI 2</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 008-2019-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 018-2024-JUS</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 237-2024-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto de Urgencia 023-2020</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 003-2020-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 012-2019-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 006-2018-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 100-2021-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 001-2020-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 004-2018-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 307-2018-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Viceministerial 003-2009-MIMDES</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 007-2023-IN</t>
+  </si>
+  <si>
+    <t>Reglamento que regula el protocolo para la atención de casos de acoso sexual en el servicio público de transporte regular de competencia de la Autoridad de Transporte Urbano para Lima y Callao - ATU</t>
+  </si>
+  <si>
+    <t>Resolución Directorial 16-2019-MTC/18</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 262-2015-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 014-2019-TR</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 115-2020-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 091-2020-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 746-2005-MIMDES</t>
+  </si>
+  <si>
+    <t>Resolución de Superintendencia 257-2022-SUNAFIL</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 007-2023-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 288-2017-MIMP</t>
+  </si>
+  <si>
+    <t>Resolución Ministerial 071-2012-MIMP</t>
+  </si>
+  <si>
+    <t>Decreto Legislativo 1428</t>
+  </si>
+  <si>
+    <t>Decreto Supremo 002-2020-IN</t>
+  </si>
+  <si>
+    <t>Caso Penal Miguel Castro Castro vs. Perú</t>
+  </si>
+  <si>
+    <t>Caso J. vs. Perú</t>
+  </si>
+  <si>
+    <t>Caso Espinoza Gonzáles vs. Perú</t>
+  </si>
+  <si>
+    <t>Caso Azul Rojas Marín y otra vs. Perú</t>
+  </si>
+  <si>
+    <t>Informe "Violencia de género contra las niñas y mujeres con discapacidad"</t>
+  </si>
+  <si>
+    <t>Estudio focalizado multipaís sobre los refugios para las mujeres víctimas de violencia de género. Los casos de Brasil, Chile, Costa Rica, El Salvador y Perú</t>
+  </si>
+  <si>
+    <t>Dictamen del Comité de Derechos Humanos sobre el caso K.L.</t>
+  </si>
+  <si>
+    <t>Dictamen del Comité de los Derechos del Niño sobre el caso Camila</t>
+  </si>
+  <si>
+    <t>Dictamen del Comité CEDAW sobre el caso L.C.</t>
+  </si>
+  <si>
+    <t>Informe del Grupo de Trabajo sobre el Examen Periódico Universal: Perú</t>
+  </si>
+  <si>
+    <t>Informe del Grupo de Trabajo sobre la cuestión de la discriminación contra la mujer en la legislación y en la práctica: Misión al Perú</t>
+  </si>
+  <si>
+    <t>Dictamen del Comité CEDAW sobre el caso María Elena Carbajal et. Al</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre los derechos de las personas con discapacidad: La salud y los derechos en materia sexual y reproductiva de las niñas y las jóvenes con discapacidad</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la violencia contra la mujer, sus causas y consecuencias</t>
+  </si>
+  <si>
+    <t>Observaciones finales sobre el Sexto informe periódico del Perú en el marco del Pacto Internacional de Derechos Civiles y Políticos</t>
+  </si>
+  <si>
+    <t>Informe del Grupo de Alto Nivel: Justicia para las mujeres</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la violencia contra la mujer, sus causas y consecuencias: Violencia contra la mujer en la política</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la violencia contra la mujer, sus causas y consecuencias: Violencia en línea contra las mujeres y las niñas desde la perspectiva de los derechos humanos</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la violencia contra la mujer, sus causas y consecuencias: La violación como una vulneración grave, sistemática y generalizada de los derechos humanos, un delito y una manifestación de la violencia de género contra las mujeres y las niñas, y su prevención</t>
+  </si>
+  <si>
+    <t>Informe de la Relatora Especial sobre la violencia contra la mujer, sus causas y consecuencias: Custodia, violencia contra las mujeres y violencia contra los niños</t>
+  </si>
+  <si>
+    <t>Resolución 5/23</t>
+  </si>
+  <si>
+    <t>Opinión consultiva OC 24/17</t>
+  </si>
+  <si>
+    <t>Estándares jurídicos vinculados a la igualdad de género y a los derechos de las mujeres en el Sistema Interamericano de Derechos Humanos: Desarrollo y aplicación</t>
+  </si>
+  <si>
+    <t>Violencia contra personas lesbianas, gay, bisexuales, trans e intersex en América</t>
+  </si>
+  <si>
+    <t>Acceso a la información, violencia contra las mujeres y la administración de justicia en las Américas</t>
+  </si>
+  <si>
+    <t>Las mujeres indígenas y sus derechos humanos en las Américas</t>
+  </si>
+  <si>
+    <t>Violencia y discriminación contra mujeres, niñas y adolescentes: Buenas prácticas y desafíos en América Latina y en el Caribe</t>
+  </si>
+  <si>
+    <t>Capacidades estatales y brechas de atención en los servicios esenciales para mujeres y niñas que sufren violencia</t>
+  </si>
+  <si>
+    <t>Respuestas normativas para el cumplimiento de los estándares en materia de feminicidio. Desafíos y buenas prácticas en la legislación procesal penal de la región</t>
+  </si>
+  <si>
+    <t>RnlaceReferencial</t>
+  </si>
+  <si>
+    <t>https://www.gob.pe/75433-normatividad-normativa-nacional-marco-general</t>
+  </si>
+  <si>
+    <t>https://www.gob.pe/75467-normatividad-normativa-nacional-especifica-tipos-de-violencia</t>
+  </si>
+  <si>
+    <t>https://www.gob.pe/75468-normatividad-normativa-nacional-especifica-modalidades-de-violencia</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/sites/default/files/Headquarters/Attachments/Sections/CSW/BPA_S_Final_WEB.pdf</t>
+  </si>
+  <si>
+    <t>https://www.refworld.org/es/leg/resol/cij/2007/es/58135</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2024/10/intensificacion-de-los-esfuerzos-para-eliminar-todas-las-formas-de-violencia-contra-las-mujeres-y-las-ninas-informe-del-secretario-general-2024</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2024/10/trafficking-in-women-and-girls-report-of-the-secretary-general-2024</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2022/10/intensificacion-de-los-esfuerzos-para-eliminar-todas-las-formas-de-violencia-contra-las-mujeres-y-las-ninas-informe-del-secretario-general-2022</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2022/10/intensificacion-de-los-esfuerzos-mundiales-para-la-eliminacion-de-la-mutilacion-genital-femenina-informe-del-secretario-general-2022</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2020/07/a-75-289-sg-report-trafficking</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2020/07/a-75-279-sg-report-female-genital-mutilation</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2020/07/a-75-274-sg-report-ending-violence-against-women-and-girls</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2019/07/a-74-224-sg-report-women-and-girls-in-rural-areas</t>
+  </si>
+  <si>
+    <t>https://www.refworld.org/es/leg/resol/csonu/2015/es/107506</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2022/11/recommendations-on-the-protection-of-migrant-women-human-rights-defenders</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2020/03/justice-for-women-high-level-group-report</t>
+  </si>
+  <si>
+    <t>https://www.unwomen.org/es/digital-library/publications/2015/10/recommendations-for-action-against-gender-related-killing-of-women-and-girls</t>
+  </si>
+  <si>
+    <t>https://www.indh.cl/wp-content/uploads/2011/12/Informe-alta-comisionado-mujeres.pdf</t>
+  </si>
+  <si>
+    <t>NombreDocumento</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +2487,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2022,12 +2517,49 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2309,19 +2841,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{472FEE68-DD5E-4E49-A00A-14C0B59108D6}" name="Tabla1" displayName="Tabla1" ref="A1:J178" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
-  <autoFilter ref="A1:J178" xr:uid="{9BA9B8BD-E9E1-4E15-8E96-D0397AE788CA}"/>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7FE3D79C-8508-4D30-B806-8EFEABD24EF2}" name="Tema_CD" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{FBCC26B3-3774-4B76-9703-EE3DBD44E0E8}" name="Tema" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{1356AE20-A273-4077-B912-DEFEBE29C074}" name="Subtema_CD" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{84011F8E-0ABB-48AE-BA3B-3CB78ECBD4B5}" name="Subtema" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1041F295-792B-4608-9418-6A3F2428B337}" name="Doc_CD" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{168403A5-5301-47F8-B017-E5D1A8351E4A}" name="Documento" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{34047BBB-097D-4731-89C8-EC79D34AFBE4}" name="TipoDoc" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{ED08AC33-D2EF-4466-8807-037E84DCDA9B}" name="Enlace" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{EB9FD7A0-8A4B-469E-9BB3-07AB5EB0FCE3}" name="Observaciones" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{47BABDE4-C19A-4FEA-8918-912C448DBDBF}" name="Año" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{472FEE68-DD5E-4E49-A00A-14C0B59108D6}" name="Tabla1" displayName="Tabla1" ref="A1:L178" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L178" xr:uid="{9BA9B8BD-E9E1-4E15-8E96-D0397AE788CA}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{7FE3D79C-8508-4D30-B806-8EFEABD24EF2}" name="Tema_CD" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{FBCC26B3-3774-4B76-9703-EE3DBD44E0E8}" name="Tema" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{1356AE20-A273-4077-B912-DEFEBE29C074}" name="Subtema_CD" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{84011F8E-0ABB-48AE-BA3B-3CB78ECBD4B5}" name="Subtema" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{1041F295-792B-4608-9418-6A3F2428B337}" name="Doc_CD" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{168403A5-5301-47F8-B017-E5D1A8351E4A}" name="Documento" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{3285E073-95ED-45DF-8189-04E2ECCFBD03}" name="NombreDocumento" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{DD942B3B-C474-4FDB-A860-B0D53AC4FB2A}" name="RnlaceReferencial" dataDxfId="0" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="7" xr3:uid="{34047BBB-097D-4731-89C8-EC79D34AFBE4}" name="TipoDoc" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{ED08AC33-D2EF-4466-8807-037E84DCDA9B}" name="Enlace" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{EB9FD7A0-8A4B-469E-9BB3-07AB5EB0FCE3}" name="Observaciones" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{47BABDE4-C19A-4FEA-8918-912C448DBDBF}" name="Año" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2644,7 +3178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA9B8BD-E9E1-4E15-8E96-D0397AE788CA}">
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:L224"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -2652,14 +3186,14 @@
     <col min="3" max="3" width="6.83203125" customWidth="1"/>
     <col min="4" max="4" width="50.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="6" max="8" width="50.83203125" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" customWidth="1"/>
+    <col min="10" max="10" width="40.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2679,19 +3213,25 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2710,18 +3250,24 @@
       <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>14</v>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9" t="s">
+      <c r="I2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="9" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -2740,18 +3286,24 @@
       <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>18</v>
+      <c r="G3" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="9" t="s">
+      <c r="I3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="9" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -2770,18 +3322,24 @@
       <c r="F4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>18</v>
+      <c r="G4" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="8"/>
+      <c r="L4" s="9" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -2800,18 +3358,24 @@
       <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>18</v>
+      <c r="G5" s="4" t="s">
+        <v>657</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="L5" s="9" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -2830,18 +3394,24 @@
       <c r="F6" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>18</v>
+      <c r="G6" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="8"/>
+      <c r="L6" s="9" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -2860,18 +3430,24 @@
       <c r="F7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>18</v>
+      <c r="G7" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9" t="s">
+      <c r="I7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="8"/>
+      <c r="L7" s="9" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>1</v>
       </c>
@@ -2890,18 +3466,24 @@
       <c r="F8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>18</v>
+      <c r="G8" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="9" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>1</v>
       </c>
@@ -2920,18 +3502,24 @@
       <c r="F9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>18</v>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="8"/>
+      <c r="L9" s="9" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>1</v>
       </c>
@@ -2950,18 +3538,24 @@
       <c r="F10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>18</v>
+      <c r="G10" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9" t="s">
+      <c r="I10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K10" s="8"/>
+      <c r="L10" s="9" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="84" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="84" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -2980,18 +3574,24 @@
       <c r="F11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>43</v>
+      <c r="G11" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="8"/>
+      <c r="L11" s="9" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -3010,18 +3610,24 @@
       <c r="F12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>47</v>
+      <c r="G12" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="9" t="s">
+      <c r="I12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="8"/>
+      <c r="L12" s="9" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>1</v>
       </c>
@@ -3040,18 +3646,24 @@
       <c r="F13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>18</v>
+      <c r="G13" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9" t="s">
+      <c r="I13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K13" s="8"/>
+      <c r="L13" s="9" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -3070,20 +3682,26 @@
       <c r="F14" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>769</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="J14" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="K14" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="L14" s="9" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>1</v>
       </c>
@@ -3102,20 +3720,26 @@
       <c r="F15" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>770</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="J15" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="K15" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="L15" s="9" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>1</v>
       </c>
@@ -3134,18 +3758,24 @@
       <c r="F16" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>57</v>
+      <c r="G16" s="4" t="s">
+        <v>669</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="8"/>
-      <c r="J16" s="9" t="s">
+      <c r="I16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" s="8"/>
+      <c r="L16" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>1</v>
       </c>
@@ -3164,20 +3794,26 @@
       <c r="F17" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="J17" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="K17" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="L17" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>1</v>
       </c>
@@ -3196,20 +3832,26 @@
       <c r="F18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>772</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="J18" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="K18" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="L18" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>1</v>
       </c>
@@ -3228,20 +3870,26 @@
       <c r="F19" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="J19" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="L19" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>1</v>
       </c>
@@ -3260,20 +3908,26 @@
       <c r="F20" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="J20" s="10" t="s">
         <v>611</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="K20" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="L20" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>1</v>
       </c>
@@ -3292,20 +3946,26 @@
       <c r="F21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="J21" s="10" t="s">
         <v>609</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="K21" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="L21" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>1</v>
       </c>
@@ -3324,20 +3984,26 @@
       <c r="F22" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>776</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="J22" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="K22" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="L22" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>1</v>
       </c>
@@ -3356,20 +4022,26 @@
       <c r="F23" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="J23" s="10" t="s">
         <v>607</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="K23" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="L23" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>1</v>
       </c>
@@ -3388,20 +4060,26 @@
       <c r="F24" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="J24" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="K24" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="L24" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>1</v>
       </c>
@@ -3420,18 +4098,24 @@
       <c r="F25" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>47</v>
+      <c r="G25" s="4" t="s">
+        <v>678</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="8"/>
-      <c r="J25" s="9" t="s">
+      <c r="I25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="8"/>
+      <c r="L25" s="9" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>1</v>
       </c>
@@ -3450,18 +4134,24 @@
       <c r="F26" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>47</v>
+      <c r="G26" s="4" t="s">
+        <v>679</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="9" t="s">
+      <c r="I26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="8"/>
+      <c r="L26" s="9" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>1</v>
       </c>
@@ -3480,18 +4170,24 @@
       <c r="F27" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>47</v>
+      <c r="G27" s="4" t="s">
+        <v>681</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I27" s="8"/>
-      <c r="J27" s="9" t="s">
+      <c r="I27" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K27" s="8"/>
+      <c r="L27" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>1</v>
       </c>
@@ -3510,18 +4206,24 @@
       <c r="F28" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>47</v>
+      <c r="G28" s="4" t="s">
+        <v>682</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I28" s="8"/>
-      <c r="J28" s="9" t="s">
+      <c r="I28" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="K28" s="8"/>
+      <c r="L28" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>1</v>
       </c>
@@ -3540,20 +4242,26 @@
       <c r="F29" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>779</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="J29" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="K29" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="L29" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>1</v>
       </c>
@@ -3572,18 +4280,24 @@
       <c r="F30" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>47</v>
+      <c r="G30" s="4" t="s">
+        <v>684</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I30" s="8"/>
-      <c r="J30" s="9" t="s">
+      <c r="I30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K30" s="8"/>
+      <c r="L30" s="9" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>1</v>
       </c>
@@ -3602,18 +4316,24 @@
       <c r="F31" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>47</v>
+      <c r="G31" s="4" t="s">
+        <v>685</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I31" s="8"/>
-      <c r="J31" s="9" t="s">
+      <c r="I31" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="8"/>
+      <c r="L31" s="9" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>1</v>
       </c>
@@ -3632,18 +4352,24 @@
       <c r="F32" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>47</v>
+      <c r="G32" s="4" t="s">
+        <v>686</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="8"/>
-      <c r="J32" s="9" t="s">
+      <c r="I32" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="K32" s="8"/>
+      <c r="L32" s="9" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>1</v>
       </c>
@@ -3662,18 +4388,24 @@
       <c r="F33" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>47</v>
+      <c r="G33" s="4" t="s">
+        <v>687</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="8"/>
-      <c r="J33" s="9" t="s">
+      <c r="I33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="8"/>
+      <c r="L33" s="9" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>1</v>
       </c>
@@ -3692,18 +4424,24 @@
       <c r="F34" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>47</v>
+      <c r="G34" s="4" t="s">
+        <v>688</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="9" t="s">
+      <c r="I34" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="K34" s="8"/>
+      <c r="L34" s="9" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>1</v>
       </c>
@@ -3722,18 +4460,24 @@
       <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>47</v>
+      <c r="G35" s="4" t="s">
+        <v>689</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I35" s="8"/>
-      <c r="J35" s="9" t="s">
+      <c r="I35" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K35" s="8"/>
+      <c r="L35" s="9" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>1</v>
       </c>
@@ -3752,18 +4496,24 @@
       <c r="F36" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>47</v>
+      <c r="G36" s="4" t="s">
+        <v>690</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="9" t="s">
+      <c r="I36" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="K36" s="8"/>
+      <c r="L36" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>1</v>
       </c>
@@ -3782,18 +4532,24 @@
       <c r="F37" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>47</v>
+      <c r="G37" s="4" t="s">
+        <v>691</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I37" s="8"/>
-      <c r="J37" s="9" t="s">
+      <c r="I37" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="K37" s="8"/>
+      <c r="L37" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>1</v>
       </c>
@@ -3812,18 +4568,24 @@
       <c r="F38" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>43</v>
+      <c r="G38" s="4" t="s">
+        <v>694</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I38" s="8"/>
-      <c r="J38" s="9" t="s">
+      <c r="I38" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="K38" s="8"/>
+      <c r="L38" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>1</v>
       </c>
@@ -3842,18 +4604,24 @@
       <c r="F39" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>43</v>
+      <c r="G39" s="4" t="s">
+        <v>696</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I39" s="8"/>
-      <c r="J39" s="9" t="s">
+      <c r="I39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K39" s="8"/>
+      <c r="L39" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>1</v>
       </c>
@@ -3872,18 +4640,24 @@
       <c r="F40" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>43</v>
+      <c r="G40" s="4" t="s">
+        <v>695</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I40" s="8"/>
-      <c r="J40" s="9" t="s">
+      <c r="I40" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="K40" s="8"/>
+      <c r="L40" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>1</v>
       </c>
@@ -3902,18 +4676,24 @@
       <c r="F41" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>43</v>
+      <c r="G41" s="4" t="s">
+        <v>697</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I41" s="8"/>
-      <c r="J41" s="9" t="s">
+      <c r="I41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="K41" s="8"/>
+      <c r="L41" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>1</v>
       </c>
@@ -3932,18 +4712,24 @@
       <c r="F42" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>43</v>
+      <c r="G42" s="4" t="s">
+        <v>698</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="I42" s="8"/>
-      <c r="J42" s="9" t="s">
+      <c r="I42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="K42" s="8"/>
+      <c r="L42" s="9" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>1</v>
       </c>
@@ -3962,18 +4748,24 @@
       <c r="F43" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="G43" s="6" t="s">
-        <v>43</v>
+      <c r="G43" s="4" t="s">
+        <v>699</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="I43" s="8"/>
-      <c r="J43" s="9" t="s">
+      <c r="I43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="K43" s="8"/>
+      <c r="L43" s="9" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>1</v>
       </c>
@@ -3992,18 +4784,24 @@
       <c r="F44" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>43</v>
+      <c r="G44" s="4" t="s">
+        <v>700</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="I44" s="8"/>
-      <c r="J44" s="9" t="s">
+      <c r="I44" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K44" s="8"/>
+      <c r="L44" s="9" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>1</v>
       </c>
@@ -4022,18 +4820,24 @@
       <c r="F45" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>47</v>
+      <c r="G45" s="8" t="s">
+        <v>692</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="I45" s="8"/>
-      <c r="J45" s="9" t="s">
+      <c r="I45" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K45" s="8"/>
+      <c r="L45" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>1</v>
       </c>
@@ -4052,18 +4856,24 @@
       <c r="F46" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>47</v>
+      <c r="G46" s="8" t="s">
+        <v>693</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="I46" s="8"/>
-      <c r="J46" s="9" t="s">
+      <c r="I46" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="K46" s="8"/>
+      <c r="L46" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>1</v>
       </c>
@@ -4082,18 +4892,24 @@
       <c r="F47" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>47</v>
+      <c r="G47" s="8" t="s">
+        <v>755</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="I47" s="8"/>
-      <c r="J47" s="9" t="s">
+      <c r="I47" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K47" s="8"/>
+      <c r="L47" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
         <v>1</v>
       </c>
@@ -4112,20 +4928,26 @@
       <c r="F48" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="I48" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="J48" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="K48" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="L48" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
         <v>1</v>
       </c>
@@ -4144,18 +4966,24 @@
       <c r="F49" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G49" s="6" t="s">
-        <v>47</v>
+      <c r="G49" s="8" t="s">
+        <v>754</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I49" s="8"/>
-      <c r="J49" s="9" t="s">
+      <c r="I49" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="K49" s="8"/>
+      <c r="L49" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
         <v>1</v>
       </c>
@@ -4174,20 +5002,26 @@
       <c r="F50" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>781</v>
+      </c>
+      <c r="I50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H50" s="10" t="s">
+      <c r="J50" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="K50" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="L50" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
         <v>1</v>
       </c>
@@ -4206,18 +5040,24 @@
       <c r="F51" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>47</v>
+      <c r="G51" s="8" t="s">
+        <v>752</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="I51" s="8"/>
-      <c r="J51" s="9" t="s">
+      <c r="I51" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="K51" s="8"/>
+      <c r="L51" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A52" s="3">
         <v>1</v>
       </c>
@@ -4236,18 +5076,24 @@
       <c r="F52" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>47</v>
+      <c r="G52" s="8" t="s">
+        <v>753</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I52" s="8"/>
-      <c r="J52" s="9" t="s">
+      <c r="I52" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J52" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="K52" s="8"/>
+      <c r="L52" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A53" s="3">
         <v>1</v>
       </c>
@@ -4266,18 +5112,24 @@
       <c r="F53" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>47</v>
+      <c r="G53" s="8" t="s">
+        <v>748</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="I53" s="8"/>
-      <c r="J53" s="9" t="s">
+      <c r="I53" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="K53" s="8"/>
+      <c r="L53" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>1</v>
       </c>
@@ -4296,18 +5148,24 @@
       <c r="F54" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>47</v>
+      <c r="G54" s="8" t="s">
+        <v>749</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="I54" s="8"/>
-      <c r="J54" s="9" t="s">
+      <c r="I54" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="K54" s="8"/>
+      <c r="L54" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A55" s="3">
         <v>1</v>
       </c>
@@ -4326,20 +5184,26 @@
       <c r="F55" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="G55" s="6" t="s">
+      <c r="G55" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="I55" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="J55" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="K55" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J55" s="9" t="s">
+      <c r="L55" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A56" s="3">
         <v>1</v>
       </c>
@@ -4358,20 +5222,26 @@
       <c r="F56" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="G56" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>783</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="J56" s="10" t="s">
         <v>605</v>
       </c>
-      <c r="I56" s="8" t="s">
+      <c r="K56" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="L56" s="9" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A57" s="3">
         <v>1</v>
       </c>
@@ -4390,18 +5260,24 @@
       <c r="F57" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>43</v>
+      <c r="G57" s="8" t="s">
+        <v>667</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I57" s="8"/>
-      <c r="J57" s="9" t="s">
+      <c r="I57" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="K57" s="8"/>
+      <c r="L57" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A58" s="3">
         <v>1</v>
       </c>
@@ -4420,18 +5296,24 @@
       <c r="F58" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>43</v>
+      <c r="G58" s="8" t="s">
+        <v>750</v>
       </c>
       <c r="H58" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="I58" s="8"/>
-      <c r="J58" s="9" t="s">
+      <c r="I58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="K58" s="8"/>
+      <c r="L58" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A59" s="3">
         <v>1</v>
       </c>
@@ -4450,18 +5332,24 @@
       <c r="F59" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="G59" s="6" t="s">
-        <v>47</v>
+      <c r="G59" s="8" t="s">
+        <v>745</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I59" s="8"/>
-      <c r="J59" s="9" t="s">
+      <c r="I59" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="K59" s="8"/>
+      <c r="L59" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A60" s="3">
         <v>1</v>
       </c>
@@ -4480,18 +5368,24 @@
       <c r="F60" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>43</v>
+      <c r="G60" s="8" t="s">
+        <v>668</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="I60" s="8"/>
-      <c r="J60" s="9" t="s">
+      <c r="I60" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="K60" s="8"/>
+      <c r="L60" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A61" s="3">
         <v>1</v>
       </c>
@@ -4510,18 +5404,24 @@
       <c r="F61" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>47</v>
+      <c r="G61" s="8" t="s">
+        <v>746</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I61" s="8"/>
-      <c r="J61" s="9" t="s">
+      <c r="I61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="K61" s="8"/>
+      <c r="L61" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>1</v>
       </c>
@@ -4540,18 +5440,24 @@
       <c r="F62" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>43</v>
+      <c r="G62" s="8" t="s">
+        <v>747</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="I62" s="8"/>
-      <c r="J62" s="9" t="s">
+      <c r="I62" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="K62" s="8"/>
+      <c r="L62" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>1</v>
       </c>
@@ -4570,18 +5476,24 @@
       <c r="F63" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G63" s="6" t="s">
-        <v>43</v>
+      <c r="G63" s="8" t="s">
+        <v>743</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="I63" s="8"/>
-      <c r="J63" s="9" t="s">
+      <c r="I63" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="K63" s="8"/>
+      <c r="L63" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>1</v>
       </c>
@@ -4600,18 +5512,24 @@
       <c r="F64" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>43</v>
+      <c r="G64" s="8" t="s">
+        <v>744</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="I64" s="8"/>
-      <c r="J64" s="9" t="s">
+      <c r="I64" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="K64" s="8"/>
+      <c r="L64" s="9" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>1</v>
       </c>
@@ -4630,18 +5548,24 @@
       <c r="F65" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>43</v>
+      <c r="G65" s="8" t="s">
+        <v>742</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="I65" s="8"/>
-      <c r="J65" s="9" t="s">
+      <c r="I65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="K65" s="8"/>
+      <c r="L65" s="9" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A66" s="3">
         <v>2</v>
       </c>
@@ -4660,18 +5584,24 @@
       <c r="F66" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>14</v>
+      <c r="G66" s="8" t="s">
+        <v>650</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="I66" s="8"/>
-      <c r="J66" s="9" t="s">
+      <c r="I66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K66" s="8"/>
+      <c r="L66" s="9" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A67" s="3">
         <v>2</v>
       </c>
@@ -4690,18 +5620,24 @@
       <c r="F67" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G67" s="6" t="s">
-        <v>14</v>
+      <c r="G67" s="8" t="s">
+        <v>658</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="I67" s="8"/>
-      <c r="J67" s="9" t="s">
+      <c r="I67" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J67" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K67" s="8"/>
+      <c r="L67" s="9" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>2</v>
       </c>
@@ -4720,18 +5656,24 @@
       <c r="F68" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>210</v>
+      <c r="G68" s="8" t="s">
+        <v>659</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I68" s="8"/>
-      <c r="J68" s="9" t="s">
+      <c r="I68" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="K68" s="8"/>
+      <c r="L68" s="9" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>2</v>
       </c>
@@ -4750,20 +5692,26 @@
       <c r="F69" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="G69" s="6" t="s">
-        <v>14</v>
+      <c r="G69" s="8" t="s">
+        <v>660</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="K69" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J69" s="9" t="s">
+      <c r="L69" s="9" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>2</v>
       </c>
@@ -4782,18 +5730,24 @@
       <c r="F70" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>14</v>
+      <c r="G70" s="8" t="s">
+        <v>661</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="I70" s="8"/>
-      <c r="J70" s="9" t="s">
+      <c r="I70" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K70" s="8"/>
+      <c r="L70" s="9" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>2</v>
       </c>
@@ -4812,18 +5766,24 @@
       <c r="F71" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>14</v>
+      <c r="G71" s="8" t="s">
+        <v>662</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="I71" s="8"/>
-      <c r="J71" s="9" t="s">
+      <c r="I71" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="K71" s="8"/>
+      <c r="L71" s="9" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>2</v>
       </c>
@@ -4842,18 +5802,24 @@
       <c r="F72" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G72" s="6" t="s">
-        <v>14</v>
+      <c r="G72" s="8" t="s">
+        <v>663</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="I72" s="8"/>
-      <c r="J72" s="9" t="s">
+      <c r="I72" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K72" s="8"/>
+      <c r="L72" s="9" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A73" s="3">
         <v>2</v>
       </c>
@@ -4872,18 +5838,24 @@
       <c r="F73" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>14</v>
+      <c r="G73" s="8" t="s">
+        <v>664</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="I73" s="8"/>
-      <c r="J73" s="9" t="s">
+      <c r="I73" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="K73" s="8"/>
+      <c r="L73" s="9" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A74" s="3">
         <v>2</v>
       </c>
@@ -4902,18 +5874,24 @@
       <c r="F74" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="G74" s="6" t="s">
-        <v>47</v>
+      <c r="G74" s="8" t="s">
+        <v>756</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="I74" s="8"/>
-      <c r="J74" s="9" t="s">
+      <c r="I74" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J74" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="K74" s="8"/>
+      <c r="L74" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>2</v>
       </c>
@@ -4932,18 +5910,24 @@
       <c r="F75" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="G75" s="6" t="s">
-        <v>47</v>
+      <c r="G75" s="8" t="s">
+        <v>757</v>
       </c>
       <c r="H75" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="I75" s="8"/>
-      <c r="J75" s="9" t="s">
+      <c r="I75" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J75" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="K75" s="8"/>
+      <c r="L75" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A76" s="3">
         <v>2</v>
       </c>
@@ -4962,18 +5946,24 @@
       <c r="F76" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G76" s="6" t="s">
-        <v>47</v>
+      <c r="G76" s="8" t="s">
+        <v>758</v>
       </c>
       <c r="H76" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="I76" s="8"/>
-      <c r="J76" s="9" t="s">
+      <c r="I76" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K76" s="8"/>
+      <c r="L76" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A77" s="3">
         <v>2</v>
       </c>
@@ -4992,18 +5982,24 @@
       <c r="F77" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="G77" s="6" t="s">
-        <v>47</v>
+      <c r="G77" s="8" t="s">
+        <v>759</v>
       </c>
       <c r="H77" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="I77" s="8"/>
-      <c r="J77" s="9" t="s">
+      <c r="I77" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="K77" s="8"/>
+      <c r="L77" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>2</v>
       </c>
@@ -5022,18 +6018,24 @@
       <c r="F78" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>47</v>
+      <c r="G78" s="8" t="s">
+        <v>760</v>
       </c>
       <c r="H78" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="I78" s="8"/>
-      <c r="J78" s="9" t="s">
+      <c r="I78" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="K78" s="8"/>
+      <c r="L78" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>2</v>
       </c>
@@ -5052,18 +6054,24 @@
       <c r="F79" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="G79" s="6" t="s">
-        <v>47</v>
+      <c r="G79" s="8" t="s">
+        <v>761</v>
       </c>
       <c r="H79" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="I79" s="8"/>
-      <c r="J79" s="9" t="s">
+      <c r="I79" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="K79" s="8"/>
+      <c r="L79" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A80" s="3">
         <v>2</v>
       </c>
@@ -5082,18 +6090,24 @@
       <c r="F80" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="G80" s="6" t="s">
-        <v>47</v>
+      <c r="G80" s="8" t="s">
+        <v>762</v>
       </c>
       <c r="H80" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="I80" s="8"/>
-      <c r="J80" s="9" t="s">
+      <c r="I80" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="K80" s="8"/>
+      <c r="L80" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A81" s="3">
         <v>2</v>
       </c>
@@ -5112,18 +6126,24 @@
       <c r="F81" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>47</v>
+      <c r="G81" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="I81" s="8"/>
-      <c r="J81" s="9" t="s">
+      <c r="I81" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="K81" s="8"/>
+      <c r="L81" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A82" s="3">
         <v>2</v>
       </c>
@@ -5142,18 +6162,24 @@
       <c r="F82" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="G82" s="6" t="s">
-        <v>47</v>
+      <c r="G82" s="8" t="s">
+        <v>254</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="I82" s="8"/>
-      <c r="J82" s="9" t="s">
+      <c r="I82" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="K82" s="8"/>
+      <c r="L82" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A83" s="3">
         <v>2</v>
       </c>
@@ -5172,18 +6198,24 @@
       <c r="F83" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>47</v>
+      <c r="G83" s="8" t="s">
+        <v>651</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="I83" s="8"/>
-      <c r="J83" s="9" t="s">
+      <c r="I83" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="K83" s="8"/>
+      <c r="L83" s="9" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A84" s="3">
         <v>2</v>
       </c>
@@ -5202,18 +6234,24 @@
       <c r="F84" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="G84" s="6" t="s">
-        <v>47</v>
+      <c r="G84" s="8" t="s">
+        <v>652</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="I84" s="8"/>
-      <c r="J84" s="9" t="s">
+      <c r="I84" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="K84" s="8"/>
+      <c r="L84" s="9" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>2</v>
       </c>
@@ -5232,18 +6270,24 @@
       <c r="F85" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>47</v>
+      <c r="G85" s="8" t="s">
+        <v>653</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="I85" s="8"/>
-      <c r="J85" s="9" t="s">
+      <c r="I85" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="K85" s="8"/>
+      <c r="L85" s="9" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A86" s="3">
         <v>2</v>
       </c>
@@ -5262,18 +6306,24 @@
       <c r="F86" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>47</v>
+      <c r="G86" s="8" t="s">
+        <v>654</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="I86" s="8"/>
-      <c r="J86" s="9" t="s">
+      <c r="I86" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="K86" s="8"/>
+      <c r="L86" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>2</v>
       </c>
@@ -5292,18 +6342,24 @@
       <c r="F87" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>47</v>
+      <c r="G87" s="8" t="s">
+        <v>655</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="I87" s="8"/>
-      <c r="J87" s="9" t="s">
+      <c r="I87" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="K87" s="8"/>
+      <c r="L87" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A88" s="3">
         <v>2</v>
       </c>
@@ -5322,18 +6378,24 @@
       <c r="F88" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="G88" s="6" t="s">
-        <v>47</v>
+      <c r="G88" s="8" t="s">
+        <v>708</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="I88" s="8"/>
-      <c r="J88" s="9" t="s">
+      <c r="I88" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="K88" s="8"/>
+      <c r="L88" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>2</v>
       </c>
@@ -5352,18 +6414,24 @@
       <c r="F89" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="G89" s="6" t="s">
-        <v>47</v>
+      <c r="G89" s="8" t="s">
+        <v>709</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="I89" s="8"/>
-      <c r="J89" s="9" t="s">
+      <c r="I89" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="K89" s="8"/>
+      <c r="L89" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A90" s="3">
         <v>2</v>
       </c>
@@ -5382,18 +6450,24 @@
       <c r="F90" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="G90" s="6" t="s">
-        <v>43</v>
+      <c r="G90" s="8" t="s">
+        <v>703</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="I90" s="8"/>
-      <c r="J90" s="9" t="s">
+      <c r="I90" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="K90" s="8"/>
+      <c r="L90" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>2</v>
       </c>
@@ -5412,18 +6486,24 @@
       <c r="F91" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>47</v>
+      <c r="G91" s="8" t="s">
+        <v>704</v>
       </c>
       <c r="H91" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="I91" s="8"/>
-      <c r="J91" s="9" t="s">
+      <c r="I91" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="K91" s="8"/>
+      <c r="L91" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A92" s="3">
         <v>2</v>
       </c>
@@ -5442,18 +6522,24 @@
       <c r="F92" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>47</v>
+      <c r="G92" s="8" t="s">
+        <v>705</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="I92" s="8"/>
-      <c r="J92" s="9" t="s">
+      <c r="I92" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="K92" s="8"/>
+      <c r="L92" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A93" s="3">
         <v>2</v>
       </c>
@@ -5472,18 +6558,24 @@
       <c r="F93" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="G93" s="6" t="s">
-        <v>47</v>
+      <c r="G93" s="8" t="s">
+        <v>706</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="I93" s="8"/>
-      <c r="J93" s="9" t="s">
+      <c r="I93" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="K93" s="8"/>
+      <c r="L93" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>2</v>
       </c>
@@ -5502,18 +6594,24 @@
       <c r="F94" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="G94" s="6" t="s">
-        <v>47</v>
+      <c r="G94" s="8" t="s">
+        <v>763</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="I94" s="8"/>
-      <c r="J94" s="9" t="s">
+      <c r="I94" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="K94" s="8"/>
+      <c r="L94" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A95" s="3">
         <v>2</v>
       </c>
@@ -5532,18 +6630,24 @@
       <c r="F95" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="G95" s="6" t="s">
-        <v>47</v>
+      <c r="G95" s="8" t="s">
+        <v>707</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="I95" s="8"/>
-      <c r="J95" s="9" t="s">
+      <c r="I95" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J95" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="K95" s="8"/>
+      <c r="L95" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>2</v>
       </c>
@@ -5562,18 +6666,24 @@
       <c r="F96" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="G96" s="6" t="s">
-        <v>47</v>
+      <c r="G96" s="8" t="s">
+        <v>740</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="I96" s="8"/>
-      <c r="J96" s="9" t="s">
+      <c r="I96" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="K96" s="8"/>
+      <c r="L96" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A97" s="3">
         <v>2</v>
       </c>
@@ -5592,18 +6702,24 @@
       <c r="F97" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="G97" s="6" t="s">
-        <v>47</v>
+      <c r="G97" s="8" t="s">
+        <v>665</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="I97" s="8"/>
-      <c r="J97" s="9" t="s">
+      <c r="I97" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="K97" s="8"/>
+      <c r="L97" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A98" s="3">
         <v>2</v>
       </c>
@@ -5622,18 +6738,24 @@
       <c r="F98" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="G98" s="6" t="s">
-        <v>47</v>
+      <c r="G98" s="8" t="s">
+        <v>764</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="I98" s="8"/>
-      <c r="J98" s="9" t="s">
+      <c r="I98" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="K98" s="8"/>
+      <c r="L98" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>2</v>
       </c>
@@ -5652,18 +6774,24 @@
       <c r="F99" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="G99" s="6" t="s">
-        <v>47</v>
+      <c r="G99" s="8" t="s">
+        <v>741</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="I99" s="8"/>
-      <c r="J99" s="9" t="s">
+      <c r="I99" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J99" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="K99" s="8"/>
+      <c r="L99" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A100" s="3">
         <v>2</v>
       </c>
@@ -5682,18 +6810,24 @@
       <c r="F100" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="G100" s="6" t="s">
-        <v>14</v>
+      <c r="G100" s="8" t="s">
+        <v>736</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="I100" s="8"/>
-      <c r="J100" s="9" t="s">
+      <c r="I100" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K100" s="8"/>
+      <c r="L100" s="9" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A101" s="3">
         <v>2</v>
       </c>
@@ -5712,18 +6846,24 @@
       <c r="F101" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="G101" s="6" t="s">
-        <v>47</v>
+      <c r="G101" s="8" t="s">
+        <v>737</v>
       </c>
       <c r="H101" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="I101" s="8"/>
-      <c r="J101" s="9" t="s">
+      <c r="I101" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J101" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="K101" s="8"/>
+      <c r="L101" s="9" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A102" s="3">
         <v>2</v>
       </c>
@@ -5742,18 +6882,24 @@
       <c r="F102" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="G102" s="6" t="s">
-        <v>47</v>
+      <c r="G102" s="8" t="s">
+        <v>738</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="I102" s="8"/>
-      <c r="J102" s="9" t="s">
+      <c r="I102" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J102" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="K102" s="8"/>
+      <c r="L102" s="9" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>2</v>
       </c>
@@ -5772,18 +6918,24 @@
       <c r="F103" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="G103" s="6" t="s">
-        <v>47</v>
+      <c r="G103" s="8" t="s">
+        <v>739</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="I103" s="8"/>
-      <c r="J103" s="9" t="s">
+      <c r="I103" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J103" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="K103" s="8"/>
+      <c r="L103" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>3</v>
       </c>
@@ -5802,18 +6954,24 @@
       <c r="F104" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="G104" s="6" t="s">
-        <v>43</v>
+      <c r="G104" s="8" t="s">
+        <v>666</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="I104" s="8"/>
-      <c r="J104" s="9" t="s">
+      <c r="I104" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J104" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="K104" s="8"/>
+      <c r="L104" s="9" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>4</v>
       </c>
@@ -5832,16 +6990,22 @@
       <c r="F105" s="8" t="s">
         <v>572</v>
       </c>
-      <c r="G105" s="6" t="s">
+      <c r="G105" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="H105" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="I105" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H105" s="7"/>
-      <c r="I105" s="8"/>
-      <c r="J105" s="9" t="s">
+      <c r="J105" s="7"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="9" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="156" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="156" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>4</v>
       </c>
@@ -5860,16 +7024,22 @@
       <c r="F106" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="G106" s="6" t="s">
+      <c r="G106" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="I106" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H106" s="7"/>
-      <c r="I106" s="8"/>
-      <c r="J106" s="9" t="s">
+      <c r="J106" s="7"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="9" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A107" s="3">
         <v>4</v>
       </c>
@@ -5888,20 +7058,26 @@
       <c r="F107" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="G107" s="6" t="s">
+      <c r="G107" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H107" s="11" t="s">
+        <v>766</v>
+      </c>
+      <c r="I107" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H107" s="10" t="s">
+      <c r="J107" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="I107" s="8" t="s">
+      <c r="K107" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="J107" s="9" t="s">
+      <c r="L107" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
         <v>597</v>
       </c>
@@ -5920,20 +7096,26 @@
       <c r="F108" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G108" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="H108" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="I108" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H108" s="7" t="s">
+      <c r="J108" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="I108" s="8" t="s">
+      <c r="K108" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="J108" s="9" t="s">
+      <c r="L108" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
         <v>597</v>
       </c>
@@ -5952,20 +7134,26 @@
       <c r="F109" s="8" t="s">
         <v>594</v>
       </c>
-      <c r="G109" s="6" t="s">
+      <c r="G109" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="H109" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="I109" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H109" s="7" t="s">
+      <c r="J109" s="7" t="s">
         <v>595</v>
       </c>
-      <c r="I109" s="8" t="s">
+      <c r="K109" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="J109" s="9" t="s">
+      <c r="L109" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
         <v>597</v>
       </c>
@@ -5984,20 +7172,26 @@
       <c r="F110" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="G110" s="6" t="s">
+      <c r="G110" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="H110" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="I110" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="J110" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="I110" s="8" t="s">
+      <c r="K110" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="J110" s="9" t="s">
+      <c r="L110" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A111" s="3">
         <v>4</v>
       </c>
@@ -6016,18 +7210,24 @@
       <c r="F111" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="G111" s="6" t="s">
+      <c r="G111" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="H111" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="I111" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H111" s="7" t="s">
+      <c r="J111" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="I111" s="8"/>
-      <c r="J111" s="9" t="s">
+      <c r="K111" s="8"/>
+      <c r="L111" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>4</v>
       </c>
@@ -6046,18 +7246,24 @@
       <c r="F112" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="G112" s="6" t="s">
+      <c r="G112" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H112" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="I112" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H112" s="7" t="s">
+      <c r="J112" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="I112" s="8"/>
-      <c r="J112" s="9" t="s">
+      <c r="K112" s="8"/>
+      <c r="L112" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>4</v>
       </c>
@@ -6076,18 +7282,24 @@
       <c r="F113" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="G113" s="6" t="s">
+      <c r="G113" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="H113" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="I113" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H113" s="7" t="s">
+      <c r="J113" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="I113" s="8"/>
-      <c r="J113" s="9" t="s">
+      <c r="K113" s="8"/>
+      <c r="L113" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>4</v>
       </c>
@@ -6106,18 +7318,24 @@
       <c r="F114" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="G114" s="6" t="s">
+      <c r="G114" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="H114" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="I114" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H114" s="7" t="s">
+      <c r="J114" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="I114" s="8"/>
-      <c r="J114" s="9" t="s">
+      <c r="K114" s="8"/>
+      <c r="L114" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A115" s="3">
         <v>4</v>
       </c>
@@ -6136,18 +7354,24 @@
       <c r="F115" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="G115" s="6" t="s">
+      <c r="G115" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="I115" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H115" s="7" t="s">
+      <c r="J115" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="I115" s="8"/>
-      <c r="J115" s="9" t="s">
+      <c r="K115" s="8"/>
+      <c r="L115" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>5</v>
       </c>
@@ -6166,18 +7390,24 @@
       <c r="F116" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="G116" s="6" t="s">
+      <c r="G116" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="H116" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="I116" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H116" s="7" t="s">
+      <c r="J116" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="I116" s="8"/>
-      <c r="J116" s="9" t="s">
+      <c r="K116" s="8"/>
+      <c r="L116" s="9" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>5</v>
       </c>
@@ -6196,18 +7426,24 @@
       <c r="F117" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="G117" s="6" t="s">
+      <c r="G117" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="H117" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="I117" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H117" s="7" t="s">
+      <c r="J117" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="I117" s="8"/>
-      <c r="J117" s="9" t="s">
+      <c r="K117" s="8"/>
+      <c r="L117" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>5</v>
       </c>
@@ -6226,18 +7462,24 @@
       <c r="F118" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="G118" s="6" t="s">
+      <c r="G118" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="H118" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="I118" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H118" s="7" t="s">
+      <c r="J118" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="I118" s="8"/>
-      <c r="J118" s="9" t="s">
+      <c r="K118" s="8"/>
+      <c r="L118" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A119" s="3">
         <v>5</v>
       </c>
@@ -6256,18 +7498,24 @@
       <c r="F119" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="G119" s="6" t="s">
+      <c r="G119" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="H119" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="I119" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H119" s="7" t="s">
+      <c r="J119" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="I119" s="8"/>
-      <c r="J119" s="9" t="s">
+      <c r="K119" s="8"/>
+      <c r="L119" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A120" s="3">
         <v>5</v>
       </c>
@@ -6286,18 +7534,24 @@
       <c r="F120" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="G120" s="6" t="s">
+      <c r="G120" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="H120" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="I120" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H120" s="7" t="s">
+      <c r="J120" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="I120" s="8"/>
-      <c r="J120" s="9" t="s">
+      <c r="K120" s="8"/>
+      <c r="L120" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A121" s="3">
         <v>5</v>
       </c>
@@ -6316,18 +7570,24 @@
       <c r="F121" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="G121" s="6" t="s">
+      <c r="G121" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="H121" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="I121" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H121" s="7" t="s">
+      <c r="J121" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="I121" s="8"/>
-      <c r="J121" s="9" t="s">
+      <c r="K121" s="8"/>
+      <c r="L121" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A122" s="3">
         <v>5</v>
       </c>
@@ -6346,18 +7606,24 @@
       <c r="F122" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="G122" s="6" t="s">
+      <c r="G122" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H122" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="I122" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H122" s="7" t="s">
+      <c r="J122" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="I122" s="8"/>
-      <c r="J122" s="9" t="s">
+      <c r="K122" s="8"/>
+      <c r="L122" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A123" s="3">
         <v>5</v>
       </c>
@@ -6376,18 +7642,24 @@
       <c r="F123" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="G123" s="6" t="s">
+      <c r="G123" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="H123" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="I123" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H123" s="7" t="s">
+      <c r="J123" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="I123" s="8"/>
-      <c r="J123" s="9" t="s">
+      <c r="K123" s="8"/>
+      <c r="L123" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>5</v>
       </c>
@@ -6406,18 +7678,24 @@
       <c r="F124" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="G124" s="6" t="s">
+      <c r="G124" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="H124" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="I124" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H124" s="7" t="s">
+      <c r="J124" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="I124" s="8"/>
-      <c r="J124" s="9" t="s">
+      <c r="K124" s="8"/>
+      <c r="L124" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A125" s="3">
         <v>5</v>
       </c>
@@ -6436,18 +7714,24 @@
       <c r="F125" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="G125" s="6" t="s">
+      <c r="G125" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="H125" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="I125" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H125" s="7" t="s">
+      <c r="J125" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="I125" s="8"/>
-      <c r="J125" s="9" t="s">
+      <c r="K125" s="8"/>
+      <c r="L125" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A126" s="3">
         <v>5</v>
       </c>
@@ -6466,18 +7750,24 @@
       <c r="F126" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="G126" s="6" t="s">
+      <c r="G126" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="H126" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="I126" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="J126" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="I126" s="8"/>
-      <c r="J126" s="9" t="s">
+      <c r="K126" s="8"/>
+      <c r="L126" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A127" s="3">
         <v>5</v>
       </c>
@@ -6496,18 +7786,24 @@
       <c r="F127" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="G127" s="6" t="s">
+      <c r="G127" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="H127" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="I127" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H127" s="7" t="s">
+      <c r="J127" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="I127" s="8"/>
-      <c r="J127" s="9" t="s">
+      <c r="K127" s="8"/>
+      <c r="L127" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>5</v>
       </c>
@@ -6526,18 +7822,24 @@
       <c r="F128" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="G128" s="6" t="s">
+      <c r="G128" s="8" t="s">
+        <v>717</v>
+      </c>
+      <c r="H128" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="I128" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H128" s="7" t="s">
+      <c r="J128" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="I128" s="8"/>
-      <c r="J128" s="9" t="s">
+      <c r="K128" s="8"/>
+      <c r="L128" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A129" s="3">
         <v>6</v>
       </c>
@@ -6556,18 +7858,24 @@
       <c r="F129" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="G129" s="6" t="s">
+      <c r="G129" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="H129" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="I129" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H129" s="7" t="s">
+      <c r="J129" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="I129" s="8"/>
-      <c r="J129" s="9" t="s">
+      <c r="K129" s="8"/>
+      <c r="L129" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A130" s="3">
         <v>6</v>
       </c>
@@ -6586,18 +7894,24 @@
       <c r="F130" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="G130" s="6" t="s">
+      <c r="G130" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="H130" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="I130" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H130" s="7" t="s">
+      <c r="J130" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="I130" s="8"/>
-      <c r="J130" s="9" t="s">
+      <c r="K130" s="8"/>
+      <c r="L130" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A131" s="3">
         <v>6</v>
       </c>
@@ -6616,16 +7930,22 @@
       <c r="F131" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="G131" s="6" t="s">
+      <c r="G131" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="H131" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="I131" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H131" s="7"/>
-      <c r="I131" s="8"/>
-      <c r="J131" s="9" t="s">
+      <c r="J131" s="7"/>
+      <c r="K131" s="8"/>
+      <c r="L131" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A132" s="3">
         <v>6</v>
       </c>
@@ -6644,18 +7964,24 @@
       <c r="F132" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="G132" s="6" t="s">
+      <c r="G132" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="I132" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H132" s="7" t="s">
+      <c r="J132" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="I132" s="8"/>
-      <c r="J132" s="9" t="s">
+      <c r="K132" s="8"/>
+      <c r="L132" s="9" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A133" s="3">
         <v>6</v>
       </c>
@@ -6674,18 +8000,24 @@
       <c r="F133" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="G133" s="6" t="s">
+      <c r="G133" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="I133" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H133" s="7" t="s">
+      <c r="J133" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="I133" s="8"/>
-      <c r="J133" s="9" t="s">
+      <c r="K133" s="8"/>
+      <c r="L133" s="9" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A134" s="3">
         <v>6</v>
       </c>
@@ -6704,18 +8036,24 @@
       <c r="F134" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="G134" s="6" t="s">
+      <c r="G134" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="I134" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H134" s="7" t="s">
+      <c r="J134" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="I134" s="8"/>
-      <c r="J134" s="9" t="s">
+      <c r="K134" s="8"/>
+      <c r="L134" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A135" s="3">
         <v>7</v>
       </c>
@@ -6734,16 +8072,22 @@
       <c r="F135" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G135" s="6" t="s">
+      <c r="G135" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I135" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H135" s="7"/>
-      <c r="I135" s="8"/>
-      <c r="J135" s="9" t="s">
+      <c r="J135" s="7"/>
+      <c r="K135" s="8"/>
+      <c r="L135" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A136" s="3">
         <v>7</v>
       </c>
@@ -6762,18 +8106,24 @@
       <c r="F136" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="G136" s="6" t="s">
+      <c r="G136" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="I136" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H136" s="7" t="s">
+      <c r="J136" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="I136" s="8"/>
-      <c r="J136" s="9" t="s">
+      <c r="K136" s="8"/>
+      <c r="L136" s="9" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>7</v>
       </c>
@@ -6792,18 +8142,24 @@
       <c r="F137" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="G137" s="6" t="s">
+      <c r="G137" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="I137" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H137" s="7" t="s">
+      <c r="J137" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="I137" s="8"/>
-      <c r="J137" s="9" t="s">
+      <c r="K137" s="8"/>
+      <c r="L137" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="72" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="72" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>7</v>
       </c>
@@ -6822,18 +8178,24 @@
       <c r="F138" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="G138" s="6" t="s">
+      <c r="G138" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="H138" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="I138" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H138" s="7" t="s">
+      <c r="J138" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="I138" s="8"/>
-      <c r="J138" s="9" t="s">
+      <c r="K138" s="8"/>
+      <c r="L138" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>7</v>
       </c>
@@ -6852,18 +8214,24 @@
       <c r="F139" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="G139" s="6" t="s">
+      <c r="G139" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="H139" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="I139" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H139" s="7" t="s">
+      <c r="J139" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="I139" s="8"/>
-      <c r="J139" s="9" t="s">
+      <c r="K139" s="8"/>
+      <c r="L139" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>7</v>
       </c>
@@ -6882,18 +8250,24 @@
       <c r="F140" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="G140" s="6" t="s">
+      <c r="G140" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="I140" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H140" s="7" t="s">
+      <c r="J140" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="I140" s="8"/>
-      <c r="J140" s="9" t="s">
+      <c r="K140" s="8"/>
+      <c r="L140" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A141" s="3">
         <v>7</v>
       </c>
@@ -6912,18 +8286,24 @@
       <c r="F141" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G141" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="H141" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="I141" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H141" s="7" t="s">
+      <c r="J141" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="I141" s="8"/>
-      <c r="J141" s="9" t="s">
+      <c r="K141" s="8"/>
+      <c r="L141" s="9" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>7</v>
       </c>
@@ -6942,18 +8322,24 @@
       <c r="F142" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="G142" s="6" t="s">
+      <c r="G142" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="H142" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="I142" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H142" s="7" t="s">
+      <c r="J142" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="I142" s="8"/>
-      <c r="J142" s="9" t="s">
+      <c r="K142" s="8"/>
+      <c r="L142" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>7</v>
       </c>
@@ -6972,18 +8358,24 @@
       <c r="F143" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="G143" s="6" t="s">
+      <c r="G143" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="I143" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H143" s="7" t="s">
+      <c r="J143" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="I143" s="8"/>
-      <c r="J143" s="9" t="s">
+      <c r="K143" s="8"/>
+      <c r="L143" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>7</v>
       </c>
@@ -7002,18 +8394,24 @@
       <c r="F144" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="G144" s="6" t="s">
+      <c r="G144" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="I144" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H144" s="7" t="s">
+      <c r="J144" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="I144" s="8"/>
-      <c r="J144" s="9" t="s">
+      <c r="K144" s="8"/>
+      <c r="L144" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A145" s="3">
         <v>7</v>
       </c>
@@ -7032,18 +8430,24 @@
       <c r="F145" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="G145" s="6" t="s">
+      <c r="G145" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="H145" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="I145" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H145" s="7" t="s">
+      <c r="J145" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="I145" s="8"/>
-      <c r="J145" s="9" t="s">
+      <c r="K145" s="8"/>
+      <c r="L145" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>7</v>
       </c>
@@ -7062,18 +8466,24 @@
       <c r="F146" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="G146" s="6" t="s">
+      <c r="G146" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="H146" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="I146" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H146" s="7" t="s">
+      <c r="J146" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="I146" s="8"/>
-      <c r="J146" s="9" t="s">
+      <c r="K146" s="8"/>
+      <c r="L146" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="84" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="84" x14ac:dyDescent="0.2">
       <c r="A147" s="3">
         <v>7</v>
       </c>
@@ -7092,18 +8502,24 @@
       <c r="F147" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G147" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="H147" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="I147" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H147" s="7" t="s">
+      <c r="J147" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="I147" s="8"/>
-      <c r="J147" s="9" t="s">
+      <c r="K147" s="8"/>
+      <c r="L147" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="96" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>7</v>
       </c>
@@ -7122,18 +8538,24 @@
       <c r="F148" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="G148" s="6" t="s">
+      <c r="G148" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="H148" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="I148" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H148" s="7" t="s">
+      <c r="J148" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="I148" s="8"/>
-      <c r="J148" s="9" t="s">
+      <c r="K148" s="8"/>
+      <c r="L148" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A149" s="3">
         <v>7</v>
       </c>
@@ -7152,20 +8574,26 @@
       <c r="F149" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="G149" s="6" t="s">
+      <c r="G149" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="H149" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="I149" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="I149" s="8" t="s">
+      <c r="K149" s="8" t="s">
         <v>582</v>
       </c>
-      <c r="J149" s="9" t="s">
+      <c r="L149" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A150" s="3">
         <v>7</v>
       </c>
@@ -7184,18 +8612,24 @@
       <c r="F150" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="G150" s="6" t="s">
+      <c r="G150" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="H150" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="I150" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="I150" s="8"/>
-      <c r="J150" s="9" t="s">
+      <c r="K150" s="8"/>
+      <c r="L150" s="9" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A151" s="3">
         <v>7</v>
       </c>
@@ -7214,18 +8648,24 @@
       <c r="F151" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="G151" s="6" t="s">
+      <c r="G151" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="H151" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="I151" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="I151" s="8"/>
-      <c r="J151" s="9" t="s">
+      <c r="K151" s="8"/>
+      <c r="L151" s="9" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>7</v>
       </c>
@@ -7244,18 +8684,24 @@
       <c r="F152" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="G152" s="6" t="s">
+      <c r="G152" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="H152" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="I152" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="I152" s="8"/>
-      <c r="J152" s="9" t="s">
+      <c r="K152" s="8"/>
+      <c r="L152" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>7</v>
       </c>
@@ -7274,18 +8720,24 @@
       <c r="F153" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="G153" s="6" t="s">
+      <c r="G153" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="H153" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="I153" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H153" s="7" t="s">
+      <c r="J153" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="I153" s="8"/>
-      <c r="J153" s="9" t="s">
+      <c r="K153" s="8"/>
+      <c r="L153" s="9" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A154" s="3">
         <v>7</v>
       </c>
@@ -7304,18 +8756,24 @@
       <c r="F154" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G154" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="H154" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="I154" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H154" s="7" t="s">
+      <c r="J154" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="I154" s="8"/>
-      <c r="J154" s="9" t="s">
+      <c r="K154" s="8"/>
+      <c r="L154" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>7</v>
       </c>
@@ -7334,18 +8792,24 @@
       <c r="F155" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="G155" s="6" t="s">
+      <c r="G155" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="H155" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="I155" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H155" s="7" t="s">
+      <c r="J155" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="I155" s="8"/>
-      <c r="J155" s="9" t="s">
+      <c r="K155" s="8"/>
+      <c r="L155" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>7</v>
       </c>
@@ -7364,18 +8828,24 @@
       <c r="F156" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="G156" s="6" t="s">
+      <c r="G156" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="H156" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="I156" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H156" s="7" t="s">
+      <c r="J156" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="I156" s="8"/>
-      <c r="J156" s="9" t="s">
+      <c r="K156" s="8"/>
+      <c r="L156" s="9" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A157" s="3">
         <v>7</v>
       </c>
@@ -7394,18 +8864,24 @@
       <c r="F157" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="G157" s="6" t="s">
+      <c r="G157" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="H157" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="I157" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H157" s="7" t="s">
+      <c r="J157" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="I157" s="8"/>
-      <c r="J157" s="9" t="s">
+      <c r="K157" s="8"/>
+      <c r="L157" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="24" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="24" x14ac:dyDescent="0.2">
       <c r="A158" s="3">
         <v>7</v>
       </c>
@@ -7424,18 +8900,24 @@
       <c r="F158" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="G158" s="6" t="s">
+      <c r="G158" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="H158" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="I158" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H158" s="7" t="s">
+      <c r="J158" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="I158" s="8"/>
-      <c r="J158" s="9" t="s">
+      <c r="K158" s="8"/>
+      <c r="L158" s="9" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A159" s="3">
         <v>7</v>
       </c>
@@ -7454,16 +8936,22 @@
       <c r="F159" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G159" s="6" t="s">
+      <c r="G159" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H159" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I159" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H159" s="7"/>
-      <c r="I159" s="8"/>
-      <c r="J159" s="9" t="s">
+      <c r="J159" s="7"/>
+      <c r="K159" s="8"/>
+      <c r="L159" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>7</v>
       </c>
@@ -7482,16 +8970,22 @@
       <c r="F160" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G160" s="6" t="s">
+      <c r="G160" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H160" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I160" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H160" s="7"/>
-      <c r="I160" s="8"/>
-      <c r="J160" s="9" t="s">
+      <c r="J160" s="7"/>
+      <c r="K160" s="8"/>
+      <c r="L160" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>7</v>
       </c>
@@ -7510,18 +9004,24 @@
       <c r="F161" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="G161" s="6" t="s">
+      <c r="G161" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>531</v>
+      </c>
+      <c r="I161" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H161" s="7" t="s">
+      <c r="J161" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="I161" s="8"/>
-      <c r="J161" s="9" t="s">
+      <c r="K161" s="8"/>
+      <c r="L161" s="9" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="96" x14ac:dyDescent="0.2">
       <c r="A162" s="3">
         <v>7</v>
       </c>
@@ -7540,18 +9040,24 @@
       <c r="F162" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="G162" s="6" t="s">
+      <c r="G162" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="I162" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H162" s="7" t="s">
+      <c r="J162" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="I162" s="8"/>
-      <c r="J162" s="9" t="s">
+      <c r="K162" s="8"/>
+      <c r="L162" s="9" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="108" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="108" x14ac:dyDescent="0.2">
       <c r="A163" s="3">
         <v>7</v>
       </c>
@@ -7570,18 +9076,24 @@
       <c r="F163" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="G163" s="6" t="s">
+      <c r="G163" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="H163" s="11" t="s">
+        <v>533</v>
+      </c>
+      <c r="I163" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H163" s="7" t="s">
+      <c r="J163" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="I163" s="8"/>
-      <c r="J163" s="9" t="s">
+      <c r="K163" s="8"/>
+      <c r="L163" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A164" s="3">
         <v>7</v>
       </c>
@@ -7598,16 +9110,22 @@
       <c r="F164" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G164" s="6" t="s">
+      <c r="G164" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H164" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I164" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H164" s="7"/>
-      <c r="I164" s="8"/>
-      <c r="J164" s="9" t="s">
+      <c r="J164" s="7"/>
+      <c r="K164" s="8"/>
+      <c r="L164" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>7</v>
       </c>
@@ -7626,18 +9144,24 @@
       <c r="F165" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="G165" s="6" t="s">
+      <c r="G165" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="H165" s="11" t="s">
+        <v>543</v>
+      </c>
+      <c r="I165" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H165" s="7" t="s">
+      <c r="J165" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="I165" s="8"/>
-      <c r="J165" s="9" t="s">
+      <c r="K165" s="8"/>
+      <c r="L165" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="96" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>7</v>
       </c>
@@ -7656,18 +9180,24 @@
       <c r="F166" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="G166" s="6" t="s">
+      <c r="G166" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="H166" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="I166" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H166" s="7" t="s">
+      <c r="J166" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="I166" s="8"/>
-      <c r="J166" s="9" t="s">
+      <c r="K166" s="8"/>
+      <c r="L166" s="9" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A167" s="3">
         <v>7</v>
       </c>
@@ -7686,16 +9216,22 @@
       <c r="F167" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G167" s="6" t="s">
+      <c r="G167" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H167" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I167" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H167" s="7"/>
-      <c r="I167" s="8"/>
-      <c r="J167" s="9" t="s">
+      <c r="J167" s="7"/>
+      <c r="K167" s="8"/>
+      <c r="L167" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A168" s="3">
         <v>7</v>
       </c>
@@ -7714,18 +9250,24 @@
       <c r="F168" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="G168" s="6" t="s">
+      <c r="G168" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="H168" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="I168" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H168" s="7" t="s">
+      <c r="J168" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="I168" s="8"/>
-      <c r="J168" s="9" t="s">
+      <c r="K168" s="8"/>
+      <c r="L168" s="9" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A169" s="3">
         <v>7</v>
       </c>
@@ -7744,16 +9286,22 @@
       <c r="F169" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G169" s="6" t="s">
+      <c r="G169" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H169" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I169" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H169" s="7"/>
-      <c r="I169" s="8"/>
-      <c r="J169" s="9" t="s">
+      <c r="J169" s="7"/>
+      <c r="K169" s="8"/>
+      <c r="L169" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A170" s="3">
         <v>7</v>
       </c>
@@ -7772,16 +9320,22 @@
       <c r="F170" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G170" s="6" t="s">
+      <c r="G170" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H170" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I170" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H170" s="7"/>
-      <c r="I170" s="8"/>
-      <c r="J170" s="9" t="s">
+      <c r="J170" s="7"/>
+      <c r="K170" s="8"/>
+      <c r="L170" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A171" s="3">
         <v>7</v>
       </c>
@@ -7800,18 +9354,24 @@
       <c r="F171" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="G171" s="6" t="s">
+      <c r="G171" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="H171" s="11" t="s">
+        <v>554</v>
+      </c>
+      <c r="I171" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H171" s="7" t="s">
+      <c r="J171" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="I171" s="8"/>
-      <c r="J171" s="9" t="s">
+      <c r="K171" s="8"/>
+      <c r="L171" s="9" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A172" s="3">
         <v>7</v>
       </c>
@@ -7830,16 +9390,22 @@
       <c r="F172" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G172" s="6" t="s">
+      <c r="G172" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H172" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I172" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H172" s="7"/>
-      <c r="I172" s="8"/>
-      <c r="J172" s="9" t="s">
+      <c r="J172" s="7"/>
+      <c r="K172" s="8"/>
+      <c r="L172" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A173" s="3">
         <v>7</v>
       </c>
@@ -7858,16 +9424,22 @@
       <c r="F173" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G173" s="6" t="s">
+      <c r="G173" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H173" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I173" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H173" s="7"/>
-      <c r="I173" s="8"/>
-      <c r="J173" s="9" t="s">
+      <c r="J173" s="7"/>
+      <c r="K173" s="8"/>
+      <c r="L173" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A174" s="3">
         <v>7</v>
       </c>
@@ -7886,16 +9458,22 @@
       <c r="F174" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G174" s="6" t="s">
+      <c r="G174" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H174" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I174" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H174" s="7"/>
-      <c r="I174" s="8"/>
-      <c r="J174" s="9" t="s">
+      <c r="J174" s="7"/>
+      <c r="K174" s="8"/>
+      <c r="L174" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="96" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="96" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>7</v>
       </c>
@@ -7914,18 +9492,24 @@
       <c r="F175" s="8" t="s">
         <v>557</v>
       </c>
-      <c r="G175" s="6" t="s">
+      <c r="G175" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="H175" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="I175" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H175" s="7" t="s">
+      <c r="J175" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="I175" s="8"/>
-      <c r="J175" s="9" t="s">
+      <c r="K175" s="8"/>
+      <c r="L175" s="9" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="36" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="36" x14ac:dyDescent="0.2">
       <c r="A176" s="3">
         <v>7</v>
       </c>
@@ -7944,16 +9528,22 @@
       <c r="F176" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="G176" s="6" t="s">
+      <c r="G176" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="H176" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I176" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H176" s="7"/>
-      <c r="I176" s="8"/>
-      <c r="J176" s="9" t="s">
+      <c r="J176" s="7"/>
+      <c r="K176" s="8"/>
+      <c r="L176" s="9" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="48" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A177" s="3">
         <v>7</v>
       </c>
@@ -7972,16 +9562,22 @@
       <c r="F177" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="G177" s="6" t="s">
+      <c r="G177" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="H177" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I177" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H177" s="7"/>
-      <c r="I177" s="8"/>
-      <c r="J177" s="9" t="s">
+      <c r="J177" s="7"/>
+      <c r="K177" s="8"/>
+      <c r="L177" s="9" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="60" x14ac:dyDescent="0.2">
       <c r="A178" s="3">
         <v>7</v>
       </c>
@@ -8000,137 +9596,376 @@
       <c r="F178" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="G178" s="6" t="s">
+      <c r="G178" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="H178" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="I178" s="6" t="s">
         <v>573</v>
       </c>
-      <c r="H178" s="7"/>
-      <c r="I178" s="8"/>
-      <c r="J178" s="9" t="s">
+      <c r="J178" s="7"/>
+      <c r="K178" s="8"/>
+      <c r="L178" s="9" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
+      <c r="H179" s="12"/>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H180" s="12"/>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H181" s="12"/>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H182" s="12"/>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H183" s="12"/>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H184" s="12"/>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H185" s="12"/>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H186" s="12"/>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H187" s="12"/>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H188" s="12"/>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H189" s="12"/>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H190" s="12"/>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H191" s="12"/>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H192" s="12"/>
+    </row>
+    <row r="193" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H193" s="12"/>
+    </row>
+    <row r="194" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H194" s="12"/>
+    </row>
+    <row r="195" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H195" s="12"/>
+    </row>
+    <row r="196" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H196" s="12"/>
+    </row>
+    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H197" s="12"/>
+    </row>
+    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H198" s="12"/>
+    </row>
+    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H199" s="12"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H200" s="12"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="12"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="12"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="12"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="12"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="12"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="12"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="12"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H208" s="12"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H209" s="12"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H210" s="12"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H211" s="12"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H212" s="12"/>
+    </row>
+    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H213" s="12"/>
+    </row>
+    <row r="214" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H214" s="12"/>
+    </row>
+    <row r="215" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H215" s="12"/>
+    </row>
+    <row r="216" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H216" s="12"/>
+    </row>
+    <row r="217" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H217" s="12"/>
+    </row>
+    <row r="218" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H218" s="12"/>
+    </row>
+    <row r="219" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H219" s="12"/>
+    </row>
+    <row r="220" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H220" s="12"/>
+    </row>
+    <row r="221" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H221" s="12"/>
+    </row>
+    <row r="222" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H222" s="12"/>
+    </row>
+    <row r="223" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H223" s="12"/>
+    </row>
+    <row r="224" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H224" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{54EF7D33-5235-474B-AA03-9ABAB05DA260}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{C7F53B2C-1D9C-44F2-B48E-727F9CCF1DC1}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{EFA87718-1230-4E2C-8C4C-E34AF0640DEF}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{39F1A9B9-61D4-4512-8A95-445B032B96FD}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{CE53A517-670A-42DB-B2E2-A5AD974E021E}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{243AFC52-F9C1-4A6B-B8FB-C15A8493D13A}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{A217B418-5147-4A4A-8625-B6141030AC2E}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{73B2D1E2-FB73-46A8-A48B-70E740A31F8A}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{57C63E33-E478-48AD-9588-87DFFA6E939C}"/>
-    <hyperlink ref="H11" r:id="rId10" display="https://www.gob.pe/institucion/mpfn/informes-publicaciones/1520345-protocolo-para-prevenir-reprimir-y-sancionar-la-trata-de-personas-especialmente-mujeres-y-ninos-que-complementa-la-convencion-de-las-naciones-unidas-contra-la-delincuencia-organizada-transnacional" xr:uid="{A43FBC22-36E9-45C9-BA76-FFAE516F84CA}"/>
-    <hyperlink ref="H12" r:id="rId11" xr:uid="{3BF485D5-CECE-49C6-A916-C8D26E20478F}"/>
-    <hyperlink ref="H13" r:id="rId12" xr:uid="{E82E4F94-6250-4357-AC21-FF02DE5879B1}"/>
-    <hyperlink ref="H14" r:id="rId13" xr:uid="{8A32A8AE-BEBA-4883-BD50-D6EFDE9EBCF1}"/>
-    <hyperlink ref="H15" r:id="rId14" xr:uid="{939ECB60-7086-423B-9744-5E10706236AB}"/>
-    <hyperlink ref="H16" r:id="rId15" xr:uid="{0EB2C99C-622D-4C5F-B977-44DE99918EC5}"/>
-    <hyperlink ref="H17" r:id="rId16" xr:uid="{C8512751-A5D7-4DF9-A442-5BABD77A13CF}"/>
-    <hyperlink ref="H18" r:id="rId17" xr:uid="{3468747D-048F-43E6-8E9D-48A769B023C1}"/>
-    <hyperlink ref="H19" r:id="rId18" xr:uid="{24447306-072D-4160-8E1C-8CB1C7B3905C}"/>
-    <hyperlink ref="H20" r:id="rId19" xr:uid="{100E7BB5-48D0-47D3-8AAE-7A5FC72AC4D5}"/>
-    <hyperlink ref="H21" r:id="rId20" xr:uid="{42384F73-CA77-438A-B697-69B4E0A4F82D}"/>
-    <hyperlink ref="H22" r:id="rId21" xr:uid="{51A85FBD-BC49-40E1-AB86-9AD8094E7A77}"/>
-    <hyperlink ref="H23" r:id="rId22" xr:uid="{5F57E922-67CF-4D12-8F2D-D4B570CB20A5}"/>
-    <hyperlink ref="H24" r:id="rId23" xr:uid="{8DF30F33-E49F-40B1-91CA-2A6BD58F1890}"/>
-    <hyperlink ref="H25" r:id="rId24" xr:uid="{D9261AC0-BB34-4CEF-B168-52719555E484}"/>
-    <hyperlink ref="H26" r:id="rId25" xr:uid="{74D82626-2EC7-4C00-8FEE-C1C9503AB7F5}"/>
-    <hyperlink ref="H27" r:id="rId26" xr:uid="{2856097F-68E3-4AE8-BD04-F04E76235807}"/>
-    <hyperlink ref="H28" r:id="rId27" xr:uid="{813F8558-6D69-4016-8899-F283C96A57E8}"/>
-    <hyperlink ref="H30" r:id="rId28" xr:uid="{D7378B86-3B49-452F-A692-5D2860DC2FC1}"/>
-    <hyperlink ref="H31" r:id="rId29" xr:uid="{B9384021-3B15-4801-B687-CFDF2611747A}"/>
-    <hyperlink ref="H32" r:id="rId30" xr:uid="{8417C8DD-9D4F-4490-9661-AD62DF6056EA}"/>
-    <hyperlink ref="H33" r:id="rId31" xr:uid="{E121510F-A00A-4D17-8211-63222A8DB9D6}"/>
-    <hyperlink ref="H34" r:id="rId32" xr:uid="{9F9421F6-49C0-4462-A34A-276B18891776}"/>
-    <hyperlink ref="H35" r:id="rId33" xr:uid="{25B88973-3B31-46F6-8126-18EA34C91409}"/>
-    <hyperlink ref="H36" r:id="rId34" xr:uid="{261BC724-5AEE-4B4C-81D7-535400F9D2F8}"/>
-    <hyperlink ref="H37" r:id="rId35" xr:uid="{02D7452F-7946-44E5-99B8-4E71BE935764}"/>
-    <hyperlink ref="H38" r:id="rId36" xr:uid="{56498468-E054-408B-8F3D-DDDAF7057D7F}"/>
-    <hyperlink ref="H39" r:id="rId37" xr:uid="{2FCCE772-B439-460A-97E5-B7F2B53FE2D3}"/>
-    <hyperlink ref="H40" r:id="rId38" xr:uid="{FC8EDA32-2623-485E-8265-EC629EEFE660}"/>
-    <hyperlink ref="H41" r:id="rId39" xr:uid="{04BC0C49-E324-4BB1-AE0E-2385DFC7EB2E}"/>
-    <hyperlink ref="H42" r:id="rId40" xr:uid="{72A0163F-5124-41D8-B3A9-4A42841F204C}"/>
-    <hyperlink ref="H43" r:id="rId41" xr:uid="{976EC75B-B16D-4BF3-B95E-7E1B9355DA2C}"/>
-    <hyperlink ref="H44" r:id="rId42" xr:uid="{DAF1546C-9362-4664-9EC4-637BE968E504}"/>
-    <hyperlink ref="H45" r:id="rId43" xr:uid="{D1AA6371-D576-48C1-8D84-B93CE022A1CF}"/>
-    <hyperlink ref="H46" r:id="rId44" xr:uid="{910988FD-E587-4B4C-ADF1-797316B85BAB}"/>
-    <hyperlink ref="H47" r:id="rId45" xr:uid="{9EA120A6-907F-469D-BD49-7F7294B15092}"/>
-    <hyperlink ref="H48" r:id="rId46" xr:uid="{26608684-26FF-4FDF-A729-DD838DFCA5C4}"/>
-    <hyperlink ref="H49" r:id="rId47" xr:uid="{A374800D-27A7-406E-AB32-30E8BEADBC7A}"/>
-    <hyperlink ref="H50" r:id="rId48" xr:uid="{18D6E241-3E56-4371-A6E9-D7780B58E3F9}"/>
-    <hyperlink ref="H51" r:id="rId49" xr:uid="{0BCE2CBD-1E54-459C-AA67-0F1AC051F968}"/>
-    <hyperlink ref="H52" r:id="rId50" xr:uid="{E59235C0-AEB3-402D-B3DB-67FF8D1DFBF6}"/>
-    <hyperlink ref="H53" r:id="rId51" xr:uid="{715055EC-5359-4693-90C3-273133773A9D}"/>
-    <hyperlink ref="H54" r:id="rId52" xr:uid="{C74A6DE9-E538-4D96-A9F9-834643580F34}"/>
-    <hyperlink ref="H55" r:id="rId53" xr:uid="{96E256A8-C732-4E6C-A32B-FEA1BE0FABAB}"/>
-    <hyperlink ref="H56" r:id="rId54" xr:uid="{6875304E-3027-45E4-B2D5-FEA25C59E82C}"/>
-    <hyperlink ref="H57" r:id="rId55" xr:uid="{04969C08-79AC-4D42-8CE3-CAFFB0537C10}"/>
-    <hyperlink ref="H58" r:id="rId56" xr:uid="{12F8AEE1-37F5-4BFF-A52A-BA7D4F889A6B}"/>
-    <hyperlink ref="H59" r:id="rId57" xr:uid="{D799EA0A-0DA8-4B3B-B8F8-17482E78DCC8}"/>
-    <hyperlink ref="H60" r:id="rId58" xr:uid="{9B183846-8DF7-4187-845E-590FF1370266}"/>
-    <hyperlink ref="H61" r:id="rId59" xr:uid="{153AAF8C-2EC1-4411-A070-FF48B25065C3}"/>
-    <hyperlink ref="H62" r:id="rId60" xr:uid="{32E85537-1ED2-493F-A8C5-EDC8C60F6ED8}"/>
-    <hyperlink ref="H63" r:id="rId61" xr:uid="{1E6871C4-3F46-4D10-98D0-DC27525C3061}"/>
-    <hyperlink ref="H64" r:id="rId62" xr:uid="{4B3A534E-36E6-4851-8AC7-B8C79C230793}"/>
-    <hyperlink ref="H65" r:id="rId63" xr:uid="{24F233BE-CDF0-4E26-B2C8-CAD0083CD5F6}"/>
-    <hyperlink ref="H66" r:id="rId64" xr:uid="{C71515BF-7B53-4054-B808-308C2777D525}"/>
-    <hyperlink ref="H67" r:id="rId65" xr:uid="{F78D8424-2C23-42FC-81CF-2E9350C1CF7C}"/>
-    <hyperlink ref="H68" r:id="rId66" xr:uid="{18977989-C1B6-4631-8DF0-D0D36D63C6D9}"/>
-    <hyperlink ref="H69" r:id="rId67" xr:uid="{AC457101-DFCF-469C-9A77-ADA88EB68879}"/>
-    <hyperlink ref="H70" r:id="rId68" xr:uid="{20158A9A-CEFD-4916-90D6-C5AD98AFBD85}"/>
-    <hyperlink ref="H71" r:id="rId69" xr:uid="{49958A06-D404-4950-B198-D5BDF2B41E81}"/>
-    <hyperlink ref="H72" r:id="rId70" xr:uid="{63A26A8F-A965-4292-8A87-D9EC14052412}"/>
-    <hyperlink ref="H73" r:id="rId71" xr:uid="{1E7667CB-7682-4E0B-A105-2FF8084F31B8}"/>
-    <hyperlink ref="H74" r:id="rId72" xr:uid="{90E4BAF5-29E7-4FDB-970D-CE6D7885E15A}"/>
-    <hyperlink ref="H75" r:id="rId73" xr:uid="{F0C5D31A-FDCB-412A-B519-99613C599937}"/>
-    <hyperlink ref="H76" r:id="rId74" xr:uid="{B0EAB310-4F3E-44E9-AEC6-05BF0A380B79}"/>
-    <hyperlink ref="H77" r:id="rId75" xr:uid="{D33D48A9-E237-4F41-B15E-6EC6EF4B681C}"/>
-    <hyperlink ref="H78" r:id="rId76" xr:uid="{C40B70D9-ACFD-44C1-907C-6ADD82D8CBE3}"/>
-    <hyperlink ref="H79" r:id="rId77" xr:uid="{D3DAE146-DF6A-4CEE-AA4B-96F29E336CB4}"/>
-    <hyperlink ref="H80" r:id="rId78" xr:uid="{C11E5D6A-6951-429D-BBC7-7883490FCB39}"/>
-    <hyperlink ref="H81" r:id="rId79" xr:uid="{AEE90FD7-B935-4C33-A431-F61B2D816C32}"/>
-    <hyperlink ref="H82" r:id="rId80" xr:uid="{54397E88-427E-4862-8A85-1B460753E65C}"/>
-    <hyperlink ref="H83" r:id="rId81" xr:uid="{44688D06-E3AE-4311-B4ED-34F9BDBDEDC1}"/>
-    <hyperlink ref="H84" r:id="rId82" xr:uid="{6C69B01C-1AAE-42DF-A500-D05E4D63A8DC}"/>
-    <hyperlink ref="H85" r:id="rId83" xr:uid="{1BEAAB77-FED0-4BCA-A041-90420988629F}"/>
-    <hyperlink ref="H86" r:id="rId84" xr:uid="{B1D98BD0-CE7C-4ED9-AD21-342A4561CBC4}"/>
-    <hyperlink ref="H87" r:id="rId85" xr:uid="{B226A949-56DB-4B3A-9C59-28272C8AADB8}"/>
-    <hyperlink ref="H88" r:id="rId86" xr:uid="{67170612-D4E5-4E96-B018-93BEFA4F6DC3}"/>
-    <hyperlink ref="H89" r:id="rId87" xr:uid="{85945315-C373-4E2E-B0CA-C66FD4C4A5F2}"/>
-    <hyperlink ref="H90" r:id="rId88" xr:uid="{04FB7947-2F56-47E1-8E10-B352AB995068}"/>
-    <hyperlink ref="H91" r:id="rId89" xr:uid="{DE0DD762-301C-4615-B99C-3E79293F85E2}"/>
-    <hyperlink ref="H92" r:id="rId90" xr:uid="{9634A449-8EB6-4458-AAA7-B94221284318}"/>
-    <hyperlink ref="H93" r:id="rId91" xr:uid="{AF176C46-5696-4D69-A382-C48D5EF68579}"/>
-    <hyperlink ref="H94" r:id="rId92" xr:uid="{9B51B4D6-4406-4CC5-9796-4FD997B404A9}"/>
-    <hyperlink ref="H95" r:id="rId93" xr:uid="{C5C29ED4-CB1C-446A-B5C2-22A7D14CA95D}"/>
-    <hyperlink ref="H96" r:id="rId94" xr:uid="{83BABB29-4AF2-4473-B606-A08B63EC3F74}"/>
-    <hyperlink ref="H97" r:id="rId95" xr:uid="{6DC0B8F4-C96F-486C-827B-68A2C69B2762}"/>
-    <hyperlink ref="H98" r:id="rId96" xr:uid="{496E7C9C-5A44-4BAB-A743-13D0CE434D1C}"/>
-    <hyperlink ref="H99" r:id="rId97" xr:uid="{2E786533-AE7A-4C2C-B0E1-38BDBF66146D}"/>
-    <hyperlink ref="H100" r:id="rId98" xr:uid="{4E00B300-AD16-4C2B-96B5-AE7EC6D537F9}"/>
-    <hyperlink ref="H101" r:id="rId99" xr:uid="{B7B72683-DA26-41D0-B0F6-E1080E403EE1}"/>
-    <hyperlink ref="H102" r:id="rId100" xr:uid="{5617433B-0321-4203-8D4E-EAD2EEEB1C77}"/>
-    <hyperlink ref="H103" r:id="rId101" xr:uid="{AA0FAE12-D064-42BA-9572-F9CF50C33FCE}"/>
-    <hyperlink ref="H104" r:id="rId102" xr:uid="{DAACD957-CFE6-444C-8A56-466141B26B96}"/>
-    <hyperlink ref="H161" r:id="rId103" location="/detallenorma/H1088463" xr:uid="{8EBF9CA3-DB23-40BD-A593-EBC1B8117F8E}"/>
-    <hyperlink ref="H162" r:id="rId104" xr:uid="{7C08EDB5-E571-4CAD-8243-550C11757BE2}"/>
-    <hyperlink ref="H163" r:id="rId105" xr:uid="{EB567D07-C77F-4A93-A42D-6F9252276305}"/>
-    <hyperlink ref="H107" r:id="rId106" xr:uid="{B0CB6F18-72F1-48BC-8D36-A46C5B119F25}"/>
-    <hyperlink ref="H109" r:id="rId107" xr:uid="{10D3EFA4-77EE-48A4-95DE-F3D6EA72E545}"/>
-    <hyperlink ref="H110" r:id="rId108" xr:uid="{DC07E4B2-9492-45BD-9C16-4D869CD05636}"/>
-    <hyperlink ref="H108" r:id="rId109" xr:uid="{09297BBE-789F-4040-A27A-CDBD6E16A9FA}"/>
-    <hyperlink ref="H29" r:id="rId110" xr:uid="{EC854CAC-86C6-4C2B-9181-705C112A2D9E}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{54EF7D33-5235-474B-AA03-9ABAB05DA260}"/>
+    <hyperlink ref="J3" r:id="rId2" xr:uid="{C7F53B2C-1D9C-44F2-B48E-727F9CCF1DC1}"/>
+    <hyperlink ref="J4" r:id="rId3" xr:uid="{EFA87718-1230-4E2C-8C4C-E34AF0640DEF}"/>
+    <hyperlink ref="J5" r:id="rId4" xr:uid="{39F1A9B9-61D4-4512-8A95-445B032B96FD}"/>
+    <hyperlink ref="J6" r:id="rId5" xr:uid="{CE53A517-670A-42DB-B2E2-A5AD974E021E}"/>
+    <hyperlink ref="J7" r:id="rId6" xr:uid="{243AFC52-F9C1-4A6B-B8FB-C15A8493D13A}"/>
+    <hyperlink ref="J8" r:id="rId7" xr:uid="{A217B418-5147-4A4A-8625-B6141030AC2E}"/>
+    <hyperlink ref="J9" r:id="rId8" xr:uid="{73B2D1E2-FB73-46A8-A48B-70E740A31F8A}"/>
+    <hyperlink ref="J10" r:id="rId9" xr:uid="{57C63E33-E478-48AD-9588-87DFFA6E939C}"/>
+    <hyperlink ref="J11" r:id="rId10" display="https://www.gob.pe/institucion/mpfn/informes-publicaciones/1520345-protocolo-para-prevenir-reprimir-y-sancionar-la-trata-de-personas-especialmente-mujeres-y-ninos-que-complementa-la-convencion-de-las-naciones-unidas-contra-la-delincuencia-organizada-transnacional" xr:uid="{A43FBC22-36E9-45C9-BA76-FFAE516F84CA}"/>
+    <hyperlink ref="J12" r:id="rId11" xr:uid="{3BF485D5-CECE-49C6-A916-C8D26E20478F}"/>
+    <hyperlink ref="J13" r:id="rId12" xr:uid="{E82E4F94-6250-4357-AC21-FF02DE5879B1}"/>
+    <hyperlink ref="J14" r:id="rId13" xr:uid="{8A32A8AE-BEBA-4883-BD50-D6EFDE9EBCF1}"/>
+    <hyperlink ref="J15" r:id="rId14" xr:uid="{939ECB60-7086-423B-9744-5E10706236AB}"/>
+    <hyperlink ref="J16" r:id="rId15" xr:uid="{0EB2C99C-622D-4C5F-B977-44DE99918EC5}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{C8512751-A5D7-4DF9-A442-5BABD77A13CF}"/>
+    <hyperlink ref="J18" r:id="rId17" xr:uid="{3468747D-048F-43E6-8E9D-48A769B023C1}"/>
+    <hyperlink ref="J19" r:id="rId18" xr:uid="{24447306-072D-4160-8E1C-8CB1C7B3905C}"/>
+    <hyperlink ref="J20" r:id="rId19" xr:uid="{100E7BB5-48D0-47D3-8AAE-7A5FC72AC4D5}"/>
+    <hyperlink ref="J21" r:id="rId20" xr:uid="{42384F73-CA77-438A-B697-69B4E0A4F82D}"/>
+    <hyperlink ref="J22" r:id="rId21" xr:uid="{51A85FBD-BC49-40E1-AB86-9AD8094E7A77}"/>
+    <hyperlink ref="J23" r:id="rId22" xr:uid="{5F57E922-67CF-4D12-8F2D-D4B570CB20A5}"/>
+    <hyperlink ref="J24" r:id="rId23" xr:uid="{8DF30F33-E49F-40B1-91CA-2A6BD58F1890}"/>
+    <hyperlink ref="J25" r:id="rId24" xr:uid="{D9261AC0-BB34-4CEF-B168-52719555E484}"/>
+    <hyperlink ref="J26" r:id="rId25" xr:uid="{74D82626-2EC7-4C00-8FEE-C1C9503AB7F5}"/>
+    <hyperlink ref="J27" r:id="rId26" xr:uid="{2856097F-68E3-4AE8-BD04-F04E76235807}"/>
+    <hyperlink ref="J28" r:id="rId27" xr:uid="{813F8558-6D69-4016-8899-F283C96A57E8}"/>
+    <hyperlink ref="J30" r:id="rId28" xr:uid="{D7378B86-3B49-452F-A692-5D2860DC2FC1}"/>
+    <hyperlink ref="J31" r:id="rId29" xr:uid="{B9384021-3B15-4801-B687-CFDF2611747A}"/>
+    <hyperlink ref="J32" r:id="rId30" xr:uid="{8417C8DD-9D4F-4490-9661-AD62DF6056EA}"/>
+    <hyperlink ref="J33" r:id="rId31" xr:uid="{E121510F-A00A-4D17-8211-63222A8DB9D6}"/>
+    <hyperlink ref="J34" r:id="rId32" xr:uid="{9F9421F6-49C0-4462-A34A-276B18891776}"/>
+    <hyperlink ref="J35" r:id="rId33" xr:uid="{25B88973-3B31-46F6-8126-18EA34C91409}"/>
+    <hyperlink ref="J36" r:id="rId34" xr:uid="{261BC724-5AEE-4B4C-81D7-535400F9D2F8}"/>
+    <hyperlink ref="J37" r:id="rId35" xr:uid="{02D7452F-7946-44E5-99B8-4E71BE935764}"/>
+    <hyperlink ref="J38" r:id="rId36" xr:uid="{56498468-E054-408B-8F3D-DDDAF7057D7F}"/>
+    <hyperlink ref="J39" r:id="rId37" xr:uid="{2FCCE772-B439-460A-97E5-B7F2B53FE2D3}"/>
+    <hyperlink ref="J40" r:id="rId38" xr:uid="{FC8EDA32-2623-485E-8265-EC629EEFE660}"/>
+    <hyperlink ref="J41" r:id="rId39" xr:uid="{04BC0C49-E324-4BB1-AE0E-2385DFC7EB2E}"/>
+    <hyperlink ref="J42" r:id="rId40" xr:uid="{72A0163F-5124-41D8-B3A9-4A42841F204C}"/>
+    <hyperlink ref="J43" r:id="rId41" xr:uid="{976EC75B-B16D-4BF3-B95E-7E1B9355DA2C}"/>
+    <hyperlink ref="J44" r:id="rId42" xr:uid="{DAF1546C-9362-4664-9EC4-637BE968E504}"/>
+    <hyperlink ref="J45" r:id="rId43" xr:uid="{D1AA6371-D576-48C1-8D84-B93CE022A1CF}"/>
+    <hyperlink ref="J46" r:id="rId44" xr:uid="{910988FD-E587-4B4C-ADF1-797316B85BAB}"/>
+    <hyperlink ref="J47" r:id="rId45" xr:uid="{9EA120A6-907F-469D-BD49-7F7294B15092}"/>
+    <hyperlink ref="J48" r:id="rId46" xr:uid="{26608684-26FF-4FDF-A729-DD838DFCA5C4}"/>
+    <hyperlink ref="J49" r:id="rId47" xr:uid="{A374800D-27A7-406E-AB32-30E8BEADBC7A}"/>
+    <hyperlink ref="J50" r:id="rId48" xr:uid="{18D6E241-3E56-4371-A6E9-D7780B58E3F9}"/>
+    <hyperlink ref="J51" r:id="rId49" xr:uid="{0BCE2CBD-1E54-459C-AA67-0F1AC051F968}"/>
+    <hyperlink ref="J52" r:id="rId50" xr:uid="{E59235C0-AEB3-402D-B3DB-67FF8D1DFBF6}"/>
+    <hyperlink ref="J53" r:id="rId51" xr:uid="{715055EC-5359-4693-90C3-273133773A9D}"/>
+    <hyperlink ref="J54" r:id="rId52" xr:uid="{C74A6DE9-E538-4D96-A9F9-834643580F34}"/>
+    <hyperlink ref="J55" r:id="rId53" xr:uid="{96E256A8-C732-4E6C-A32B-FEA1BE0FABAB}"/>
+    <hyperlink ref="J56" r:id="rId54" xr:uid="{6875304E-3027-45E4-B2D5-FEA25C59E82C}"/>
+    <hyperlink ref="J57" r:id="rId55" xr:uid="{04969C08-79AC-4D42-8CE3-CAFFB0537C10}"/>
+    <hyperlink ref="J58" r:id="rId56" xr:uid="{12F8AEE1-37F5-4BFF-A52A-BA7D4F889A6B}"/>
+    <hyperlink ref="J59" r:id="rId57" xr:uid="{D799EA0A-0DA8-4B3B-B8F8-17482E78DCC8}"/>
+    <hyperlink ref="J60" r:id="rId58" xr:uid="{9B183846-8DF7-4187-845E-590FF1370266}"/>
+    <hyperlink ref="J61" r:id="rId59" xr:uid="{153AAF8C-2EC1-4411-A070-FF48B25065C3}"/>
+    <hyperlink ref="J62" r:id="rId60" xr:uid="{32E85537-1ED2-493F-A8C5-EDC8C60F6ED8}"/>
+    <hyperlink ref="J63" r:id="rId61" xr:uid="{1E6871C4-3F46-4D10-98D0-DC27525C3061}"/>
+    <hyperlink ref="J64" r:id="rId62" xr:uid="{4B3A534E-36E6-4851-8AC7-B8C79C230793}"/>
+    <hyperlink ref="J65" r:id="rId63" xr:uid="{24F233BE-CDF0-4E26-B2C8-CAD0083CD5F6}"/>
+    <hyperlink ref="J66" r:id="rId64" xr:uid="{C71515BF-7B53-4054-B808-308C2777D525}"/>
+    <hyperlink ref="J67" r:id="rId65" xr:uid="{F78D8424-2C23-42FC-81CF-2E9350C1CF7C}"/>
+    <hyperlink ref="J68" r:id="rId66" xr:uid="{18977989-C1B6-4631-8DF0-D0D36D63C6D9}"/>
+    <hyperlink ref="J69" r:id="rId67" xr:uid="{AC457101-DFCF-469C-9A77-ADA88EB68879}"/>
+    <hyperlink ref="J70" r:id="rId68" xr:uid="{20158A9A-CEFD-4916-90D6-C5AD98AFBD85}"/>
+    <hyperlink ref="J71" r:id="rId69" xr:uid="{49958A06-D404-4950-B198-D5BDF2B41E81}"/>
+    <hyperlink ref="J72" r:id="rId70" xr:uid="{63A26A8F-A965-4292-8A87-D9EC14052412}"/>
+    <hyperlink ref="J73" r:id="rId71" xr:uid="{1E7667CB-7682-4E0B-A105-2FF8084F31B8}"/>
+    <hyperlink ref="J74" r:id="rId72" xr:uid="{90E4BAF5-29E7-4FDB-970D-CE6D7885E15A}"/>
+    <hyperlink ref="J75" r:id="rId73" xr:uid="{F0C5D31A-FDCB-412A-B519-99613C599937}"/>
+    <hyperlink ref="J76" r:id="rId74" xr:uid="{B0EAB310-4F3E-44E9-AEC6-05BF0A380B79}"/>
+    <hyperlink ref="J77" r:id="rId75" xr:uid="{D33D48A9-E237-4F41-B15E-6EC6EF4B681C}"/>
+    <hyperlink ref="J78" r:id="rId76" xr:uid="{C40B70D9-ACFD-44C1-907C-6ADD82D8CBE3}"/>
+    <hyperlink ref="J79" r:id="rId77" xr:uid="{D3DAE146-DF6A-4CEE-AA4B-96F29E336CB4}"/>
+    <hyperlink ref="J80" r:id="rId78" xr:uid="{C11E5D6A-6951-429D-BBC7-7883490FCB39}"/>
+    <hyperlink ref="J81" r:id="rId79" xr:uid="{AEE90FD7-B935-4C33-A431-F61B2D816C32}"/>
+    <hyperlink ref="J82" r:id="rId80" xr:uid="{54397E88-427E-4862-8A85-1B460753E65C}"/>
+    <hyperlink ref="J83" r:id="rId81" xr:uid="{44688D06-E3AE-4311-B4ED-34F9BDBDEDC1}"/>
+    <hyperlink ref="J84" r:id="rId82" xr:uid="{6C69B01C-1AAE-42DF-A500-D05E4D63A8DC}"/>
+    <hyperlink ref="J85" r:id="rId83" xr:uid="{1BEAAB77-FED0-4BCA-A041-90420988629F}"/>
+    <hyperlink ref="J86" r:id="rId84" xr:uid="{B1D98BD0-CE7C-4ED9-AD21-342A4561CBC4}"/>
+    <hyperlink ref="J87" r:id="rId85" xr:uid="{B226A949-56DB-4B3A-9C59-28272C8AADB8}"/>
+    <hyperlink ref="J88" r:id="rId86" xr:uid="{67170612-D4E5-4E96-B018-93BEFA4F6DC3}"/>
+    <hyperlink ref="J89" r:id="rId87" xr:uid="{85945315-C373-4E2E-B0CA-C66FD4C4A5F2}"/>
+    <hyperlink ref="J90" r:id="rId88" xr:uid="{04FB7947-2F56-47E1-8E10-B352AB995068}"/>
+    <hyperlink ref="J91" r:id="rId89" xr:uid="{DE0DD762-301C-4615-B99C-3E79293F85E2}"/>
+    <hyperlink ref="J92" r:id="rId90" xr:uid="{9634A449-8EB6-4458-AAA7-B94221284318}"/>
+    <hyperlink ref="J93" r:id="rId91" xr:uid="{AF176C46-5696-4D69-A382-C48D5EF68579}"/>
+    <hyperlink ref="J94" r:id="rId92" xr:uid="{9B51B4D6-4406-4CC5-9796-4FD997B404A9}"/>
+    <hyperlink ref="J95" r:id="rId93" xr:uid="{C5C29ED4-CB1C-446A-B5C2-22A7D14CA95D}"/>
+    <hyperlink ref="J96" r:id="rId94" xr:uid="{83BABB29-4AF2-4473-B606-A08B63EC3F74}"/>
+    <hyperlink ref="J97" r:id="rId95" xr:uid="{6DC0B8F4-C96F-486C-827B-68A2C69B2762}"/>
+    <hyperlink ref="J98" r:id="rId96" xr:uid="{496E7C9C-5A44-4BAB-A743-13D0CE434D1C}"/>
+    <hyperlink ref="J99" r:id="rId97" xr:uid="{2E786533-AE7A-4C2C-B0E1-38BDBF66146D}"/>
+    <hyperlink ref="J100" r:id="rId98" xr:uid="{4E00B300-AD16-4C2B-96B5-AE7EC6D537F9}"/>
+    <hyperlink ref="J101" r:id="rId99" xr:uid="{B7B72683-DA26-41D0-B0F6-E1080E403EE1}"/>
+    <hyperlink ref="J102" r:id="rId100" xr:uid="{5617433B-0321-4203-8D4E-EAD2EEEB1C77}"/>
+    <hyperlink ref="J103" r:id="rId101" xr:uid="{AA0FAE12-D064-42BA-9572-F9CF50C33FCE}"/>
+    <hyperlink ref="J104" r:id="rId102" xr:uid="{DAACD957-CFE6-444C-8A56-466141B26B96}"/>
+    <hyperlink ref="J161" r:id="rId103" location="/detallenorma/H1088463" xr:uid="{8EBF9CA3-DB23-40BD-A593-EBC1B8117F8E}"/>
+    <hyperlink ref="J162" r:id="rId104" xr:uid="{7C08EDB5-E571-4CAD-8243-550C11757BE2}"/>
+    <hyperlink ref="J163" r:id="rId105" xr:uid="{EB567D07-C77F-4A93-A42D-6F9252276305}"/>
+    <hyperlink ref="J107" r:id="rId106" xr:uid="{B0CB6F18-72F1-48BC-8D36-A46C5B119F25}"/>
+    <hyperlink ref="J109" r:id="rId107" xr:uid="{10D3EFA4-77EE-48A4-95DE-F3D6EA72E545}"/>
+    <hyperlink ref="J110" r:id="rId108" xr:uid="{DC07E4B2-9492-45BD-9C16-4D869CD05636}"/>
+    <hyperlink ref="J108" r:id="rId109" xr:uid="{09297BBE-789F-4040-A27A-CDBD6E16A9FA}"/>
+    <hyperlink ref="J29" r:id="rId110" xr:uid="{EC854CAC-86C6-4C2B-9181-705C112A2D9E}"/>
+    <hyperlink ref="H2" r:id="rId111" xr:uid="{55B16D63-5107-42EF-AE11-EA4AAB3D84E7}"/>
+    <hyperlink ref="H3" r:id="rId112" xr:uid="{15F81454-227B-49AF-8B81-16E819BDD842}"/>
+    <hyperlink ref="H4" r:id="rId113" xr:uid="{EE52EE64-B85D-486B-AED2-EB1C3F056115}"/>
+    <hyperlink ref="H5" r:id="rId114" xr:uid="{7B5B01E6-23B9-4CAE-981B-1B510CDBC2B7}"/>
+    <hyperlink ref="H6" r:id="rId115" xr:uid="{CADADB2B-AA90-4C2F-B165-BBB0157D6EA1}"/>
+    <hyperlink ref="H7" r:id="rId116" xr:uid="{3F8D569E-ED0D-4E96-9D16-742FE544C07A}"/>
+    <hyperlink ref="H8" r:id="rId117" xr:uid="{EBBF690E-932E-41C7-9B14-1FA904C6510F}"/>
+    <hyperlink ref="H9" r:id="rId118" xr:uid="{F2A1BD46-8BED-42E6-BE22-A4CF962C9355}"/>
+    <hyperlink ref="H10" r:id="rId119" xr:uid="{1D34A87A-2421-44B1-9E47-11269EA9291F}"/>
+    <hyperlink ref="H11" r:id="rId120" display="https://www.gob.pe/institucion/mpfn/informes-publicaciones/1520345-protocolo-para-prevenir-reprimir-y-sancionar-la-trata-de-personas-especialmente-mujeres-y-ninos-que-complementa-la-convencion-de-las-naciones-unidas-contra-la-delincuencia-organizada-transnacional" xr:uid="{AC45FDDA-B726-42F3-B692-13770E42D8E9}"/>
+    <hyperlink ref="H12" r:id="rId121" xr:uid="{F8A06EC1-1C5C-490A-89BA-8A5447CB811B}"/>
+    <hyperlink ref="H13" r:id="rId122" xr:uid="{83132AD6-138B-4A0F-8C54-ADC85B90470C}"/>
+    <hyperlink ref="H14" r:id="rId123" display="https://drive.google.com/file/d/1E_edu5jvm0IEv4BHq2RsAyjNOXHCNWqV/view?usp=sharing" xr:uid="{A80E49C4-3114-471A-8EFF-DB5DC3D990E6}"/>
+    <hyperlink ref="H15" r:id="rId124" display="https://drive.google.com/file/d/1R4ut7x1brama8_7gnSr3B7liCzqzCz0g/view?usp=sharing" xr:uid="{ED11A04F-0389-4B34-A9D0-7908FDC69AA2}"/>
+    <hyperlink ref="H16" r:id="rId125" xr:uid="{26F5A527-6518-4BAE-ACC1-36F7231E341D}"/>
+    <hyperlink ref="H25" r:id="rId126" xr:uid="{A94BA23D-D639-43F4-B262-2E79CD3F87C1}"/>
+    <hyperlink ref="H26" r:id="rId127" xr:uid="{CD69C6EF-8352-4EB1-A160-E748D9013392}"/>
+    <hyperlink ref="H27" r:id="rId128" xr:uid="{7D3025AB-DD2B-4903-AB03-B0F95E446870}"/>
+    <hyperlink ref="H28" r:id="rId129" xr:uid="{3E7143C9-1C37-4C71-B5E4-89DF1E2B1C96}"/>
+    <hyperlink ref="H30" r:id="rId130" xr:uid="{54376ACB-CD90-4D26-8FAF-AB1760C05AA8}"/>
+    <hyperlink ref="H31" r:id="rId131" xr:uid="{D7BF15F1-DC08-45D8-B4CC-2C5B6ACE4FEC}"/>
+    <hyperlink ref="H32" r:id="rId132" xr:uid="{E0778FCA-DE53-4CF7-8FE1-1F4C75799DBE}"/>
+    <hyperlink ref="H33" r:id="rId133" xr:uid="{28EE4F7B-D3C3-484B-A2C5-C3E794F80E21}"/>
+    <hyperlink ref="H34" r:id="rId134" xr:uid="{8417286B-E23A-4BF1-9E13-EBC5698CBECB}"/>
+    <hyperlink ref="H35" r:id="rId135" xr:uid="{CE40B63D-A1CE-4719-9583-C4D1A5F40003}"/>
+    <hyperlink ref="H36" r:id="rId136" xr:uid="{D38F7F33-1847-4797-A8E9-5B563E77AB6F}"/>
+    <hyperlink ref="H37" r:id="rId137" xr:uid="{D8302921-1688-4104-A3B3-4A1121F9289B}"/>
+    <hyperlink ref="H38" r:id="rId138" xr:uid="{9DA5747D-5941-4D62-8BD5-4EDA305359E9}"/>
+    <hyperlink ref="H39" r:id="rId139" xr:uid="{8B3EBD4F-0067-4023-830D-77AA7AB0C399}"/>
+    <hyperlink ref="H40" r:id="rId140" xr:uid="{0BAA5530-39ED-4F00-8768-2DA7847C50A0}"/>
+    <hyperlink ref="H41" r:id="rId141" xr:uid="{ED6F9F6F-E8B9-4296-845B-682EF739A385}"/>
+    <hyperlink ref="H42" r:id="rId142" xr:uid="{7DF19E55-0E46-402E-A7C2-DEFE1BC5FD23}"/>
+    <hyperlink ref="H43" r:id="rId143" xr:uid="{AE9860B0-698D-4A1D-BB67-6297415F48AF}"/>
+    <hyperlink ref="H44" r:id="rId144" xr:uid="{3DDE3B93-6624-4870-998F-273C4C10A34F}"/>
+    <hyperlink ref="H45" r:id="rId145" xr:uid="{0E50C801-1AC3-4257-9960-0218E70C018C}"/>
+    <hyperlink ref="H46" r:id="rId146" xr:uid="{9C865BD5-FFB2-4320-B649-61AC11AD1908}"/>
+    <hyperlink ref="H47" r:id="rId147" xr:uid="{09410240-6995-421C-A6A4-5FDC16A52285}"/>
+    <hyperlink ref="H49" r:id="rId148" xr:uid="{5A4A86FC-FE2A-42CC-8FE3-FC1608B7C6A9}"/>
+    <hyperlink ref="H51" r:id="rId149" xr:uid="{1747267B-A5B0-4347-B308-402BA7425FD2}"/>
+    <hyperlink ref="H52" r:id="rId150" xr:uid="{9884640E-C6C7-45DF-9174-8579E5926DE0}"/>
+    <hyperlink ref="H53" r:id="rId151" xr:uid="{C89F5AD6-07C4-4CBE-A291-5D8A202A8811}"/>
+    <hyperlink ref="H54" r:id="rId152" xr:uid="{333A747E-A6A2-45AB-A54C-E16803EDB912}"/>
+    <hyperlink ref="H57" r:id="rId153" xr:uid="{6E658287-81DC-4937-861D-4141321BF5B9}"/>
+    <hyperlink ref="H58" r:id="rId154" xr:uid="{3FE502D7-4D70-4C4E-96D1-56BB31996FDE}"/>
+    <hyperlink ref="H59" r:id="rId155" xr:uid="{8A0C4E9E-521F-42D9-A38E-CE36DBF2C1EA}"/>
+    <hyperlink ref="H60" r:id="rId156" xr:uid="{08EA70AF-C7B8-4873-94D0-F664FEFEBDA3}"/>
+    <hyperlink ref="H61" r:id="rId157" xr:uid="{CA09511F-3422-47B8-8B55-7E12D5637A23}"/>
+    <hyperlink ref="H62" r:id="rId158" xr:uid="{E471EB97-A143-413B-997A-EA476EBB951D}"/>
+    <hyperlink ref="H63" r:id="rId159" xr:uid="{2B58B9E1-5466-4508-AD4E-989C2B01F06E}"/>
+    <hyperlink ref="H64" r:id="rId160" xr:uid="{5477CADB-5FDF-4475-84FF-1DB184C93AC4}"/>
+    <hyperlink ref="H65" r:id="rId161" xr:uid="{432877EA-FF3D-41DC-B90E-866400EAD2FA}"/>
+    <hyperlink ref="H66" r:id="rId162" xr:uid="{D274ABB2-1F49-4185-A5C4-ED4F42F38670}"/>
+    <hyperlink ref="H67" r:id="rId163" xr:uid="{D2DA1A14-C8B0-4747-AE90-B1D253F72588}"/>
+    <hyperlink ref="H68" r:id="rId164" xr:uid="{154BE297-1030-4037-A340-F41930D31616}"/>
+    <hyperlink ref="H69" r:id="rId165" xr:uid="{F8E181B9-5E79-4C58-83A9-38DEA8F7EB0E}"/>
+    <hyperlink ref="H70" r:id="rId166" xr:uid="{4B86D8C5-DE55-4F4C-BC43-1D517517A06F}"/>
+    <hyperlink ref="H71" r:id="rId167" xr:uid="{CEDE4F92-4F58-4B2B-8D8C-F8071224D793}"/>
+    <hyperlink ref="H72" r:id="rId168" xr:uid="{36188402-11C3-4BA2-8374-814AD3F0C4CF}"/>
+    <hyperlink ref="H73" r:id="rId169" xr:uid="{57AE1487-B3D6-4D34-9213-E189E5D0754C}"/>
+    <hyperlink ref="H74" r:id="rId170" xr:uid="{20007965-4E08-4FD0-AB3B-366B58EE177B}"/>
+    <hyperlink ref="H75" r:id="rId171" xr:uid="{916A93CD-CFB6-474C-9605-8594F117783C}"/>
+    <hyperlink ref="H76" r:id="rId172" xr:uid="{BB29956D-89D4-43FD-804C-E79737463A9F}"/>
+    <hyperlink ref="H77" r:id="rId173" xr:uid="{4D153343-4522-4200-AF1E-E28AEEBBD40A}"/>
+    <hyperlink ref="H78" r:id="rId174" xr:uid="{48430F76-940E-4642-A262-BC0A7EA9AB75}"/>
+    <hyperlink ref="H79" r:id="rId175" xr:uid="{EC22C2AD-881C-4AB5-9AC5-35F4E21ABA07}"/>
+    <hyperlink ref="H80" r:id="rId176" xr:uid="{30637268-3BC6-40B0-BA8D-F28506F58978}"/>
+    <hyperlink ref="H81" r:id="rId177" xr:uid="{B1EBA426-3B31-40F5-B6AB-EA5644573654}"/>
+    <hyperlink ref="H82" r:id="rId178" xr:uid="{880BB072-5D5E-48AB-81EE-097721506250}"/>
+    <hyperlink ref="H83" r:id="rId179" xr:uid="{BB0C8563-0903-4546-B79C-57BDCF6C37D1}"/>
+    <hyperlink ref="H84" r:id="rId180" xr:uid="{C36621B4-8AA4-48AB-B2AB-71D88F4C31D1}"/>
+    <hyperlink ref="H85" r:id="rId181" xr:uid="{71A7615D-7122-4A09-9C44-0DE77C8F8F25}"/>
+    <hyperlink ref="H86" r:id="rId182" xr:uid="{9B913573-2673-403B-AF1D-EBFF6FEAC36E}"/>
+    <hyperlink ref="H87" r:id="rId183" xr:uid="{F19F74CB-6326-49F3-B425-E9EA22CEFD17}"/>
+    <hyperlink ref="H88" r:id="rId184" xr:uid="{8747822A-E836-4A28-88E5-B7C590785C1C}"/>
+    <hyperlink ref="H89" r:id="rId185" xr:uid="{31F76B18-F6FA-45CD-B104-22A1C9240D68}"/>
+    <hyperlink ref="H90" r:id="rId186" xr:uid="{281A6A33-F4A5-4316-9267-4B1EDA6BC98B}"/>
+    <hyperlink ref="H91" r:id="rId187" xr:uid="{8E435147-141A-4D69-A4F6-D6348345A216}"/>
+    <hyperlink ref="H92" r:id="rId188" xr:uid="{3ED10392-CD07-4EE1-9F58-A7F40719A180}"/>
+    <hyperlink ref="H93" r:id="rId189" xr:uid="{4CC5BC47-5E6C-464C-AC1C-B124673FE08F}"/>
+    <hyperlink ref="H94" r:id="rId190" xr:uid="{6559C622-7F60-4BAA-A417-FB768AF92611}"/>
+    <hyperlink ref="H95" r:id="rId191" xr:uid="{0D5359C9-FF29-4676-8600-EF73CA086268}"/>
+    <hyperlink ref="H96" r:id="rId192" xr:uid="{6B788392-A961-44FF-9678-6C25929901A3}"/>
+    <hyperlink ref="H97" r:id="rId193" xr:uid="{3B7B1EAC-3476-4669-A791-905C48EB8B5C}"/>
+    <hyperlink ref="H98" r:id="rId194" xr:uid="{4D9A003E-6BEA-4AD4-84D7-A665F327A9E2}"/>
+    <hyperlink ref="H99" r:id="rId195" xr:uid="{50962532-68BC-41C8-AD69-403F22B46AE9}"/>
+    <hyperlink ref="H100" r:id="rId196" xr:uid="{EB819951-632E-4538-8291-C4C140FB55E8}"/>
+    <hyperlink ref="H101" r:id="rId197" xr:uid="{9DEB7F63-BBF4-4883-8AD3-4D7CD220169E}"/>
+    <hyperlink ref="H102" r:id="rId198" xr:uid="{C8946A96-6A4E-4263-858D-52C298357FA9}"/>
+    <hyperlink ref="H103" r:id="rId199" xr:uid="{DC533B78-7752-4645-BDCA-A59BE73B6D9A}"/>
+    <hyperlink ref="H104" r:id="rId200" xr:uid="{EAE342AB-55B8-48E2-B8DC-2509E2E6D065}"/>
+    <hyperlink ref="H161" r:id="rId201" location="/detallenorma/H1088463" xr:uid="{A6037D3D-00CE-4628-B36A-21C676CE7D58}"/>
+    <hyperlink ref="H162" r:id="rId202" xr:uid="{F44C8AAF-5373-4DEC-AE30-1192534B40D1}"/>
+    <hyperlink ref="H163" r:id="rId203" xr:uid="{E7461597-0189-4AFE-9CDB-EA9F0648C97B}"/>
+    <hyperlink ref="H107" r:id="rId204" display="https://drive.google.com/file/d/1AWG2-ptlfBYeywc-ycszhZVUgR2smNy1/view?usp=sharing" xr:uid="{69883006-9AF4-4F79-B1D9-21B411CA4590}"/>
+    <hyperlink ref="H109" r:id="rId205" xr:uid="{E7413700-C77A-44C9-AC69-2FF250770138}"/>
+    <hyperlink ref="H110" r:id="rId206" xr:uid="{9246A037-4A49-4D55-8239-79E2CDCC37BC}"/>
+    <hyperlink ref="H108" r:id="rId207" xr:uid="{6406CC52-98A2-47AE-9055-541DBF8837B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId111"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId208"/>
   <tableParts count="1">
-    <tablePart r:id="rId112"/>
+    <tablePart r:id="rId209"/>
   </tableParts>
 </worksheet>
 </file>